--- a/doc/Layout.xlsx
+++ b/doc/Layout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Arma 3 Modding\21_ZeusJukebox\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551BBC6F-E7DF-4931-8CC5-8E81B805E7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7A9FDC-BCE3-450B-84AA-E222FA7A0D98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{682E6184-E15B-4402-836A-91257A3551C0}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{682E6184-E15B-4402-836A-91257A3551C0}"/>
   </bookViews>
   <sheets>
     <sheet name="v1.2.0" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="51">
   <si>
     <t>*</t>
   </si>
@@ -187,6 +187,9 @@
   </si>
   <si>
     <t>Played Music History</t>
+  </si>
+  <si>
+    <t>Show:</t>
   </si>
 </sst>
 </file>
@@ -422,7 +425,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -592,6 +595,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -610,6 +622,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -626,45 +647,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2701,18 +2683,18 @@
         <v>11</v>
       </c>
       <c r="V18" s="12"/>
-      <c r="W18" s="63" t="s">
+      <c r="W18" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="X18" s="64"/>
-      <c r="Y18" s="64"/>
-      <c r="Z18" s="64"/>
-      <c r="AA18" s="64"/>
-      <c r="AB18" s="64"/>
-      <c r="AC18" s="64"/>
-      <c r="AD18" s="64"/>
-      <c r="AE18" s="64"/>
-      <c r="AF18" s="65"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="70"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="71"/>
       <c r="AG18" s="20"/>
       <c r="AH18" s="20"/>
       <c r="AI18" s="20"/>
@@ -2720,18 +2702,18 @@
       <c r="AK18" s="20"/>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AO18" s="63" t="s">
+      <c r="AO18" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="AP18" s="64"/>
-      <c r="AQ18" s="64"/>
-      <c r="AR18" s="64"/>
-      <c r="AS18" s="64"/>
-      <c r="AT18" s="64"/>
-      <c r="AU18" s="64"/>
-      <c r="AV18" s="64"/>
-      <c r="AW18" s="64"/>
-      <c r="AX18" s="65"/>
+      <c r="AP18" s="70"/>
+      <c r="AQ18" s="70"/>
+      <c r="AR18" s="70"/>
+      <c r="AS18" s="70"/>
+      <c r="AT18" s="70"/>
+      <c r="AU18" s="70"/>
+      <c r="AV18" s="70"/>
+      <c r="AW18" s="70"/>
+      <c r="AX18" s="71"/>
       <c r="AY18" s="20"/>
       <c r="AZ18" s="20"/>
       <c r="BA18" s="20"/>
@@ -2742,33 +2724,33 @@
       <c r="BF18" s="20"/>
       <c r="BG18" s="20"/>
       <c r="BK18" s="20"/>
-      <c r="BL18" s="57" t="s">
+      <c r="BL18" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="BM18" s="58"/>
-      <c r="BN18" s="58"/>
-      <c r="BO18" s="58"/>
-      <c r="BP18" s="58"/>
-      <c r="BQ18" s="59"/>
-      <c r="BR18" s="57" t="s">
+      <c r="BM18" s="61"/>
+      <c r="BN18" s="61"/>
+      <c r="BO18" s="61"/>
+      <c r="BP18" s="61"/>
+      <c r="BQ18" s="62"/>
+      <c r="BR18" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="BS18" s="58"/>
-      <c r="BT18" s="58"/>
-      <c r="BU18" s="58"/>
-      <c r="BV18" s="59"/>
-      <c r="BX18" s="63" t="s">
+      <c r="BS18" s="61"/>
+      <c r="BT18" s="61"/>
+      <c r="BU18" s="61"/>
+      <c r="BV18" s="62"/>
+      <c r="BX18" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="BY18" s="64"/>
-      <c r="BZ18" s="64"/>
-      <c r="CA18" s="64"/>
-      <c r="CB18" s="64"/>
-      <c r="CC18" s="64"/>
-      <c r="CD18" s="64"/>
-      <c r="CE18" s="64"/>
-      <c r="CF18" s="64"/>
-      <c r="CG18" s="65"/>
+      <c r="BY18" s="70"/>
+      <c r="BZ18" s="70"/>
+      <c r="CA18" s="70"/>
+      <c r="CB18" s="70"/>
+      <c r="CC18" s="70"/>
+      <c r="CD18" s="70"/>
+      <c r="CE18" s="70"/>
+      <c r="CF18" s="70"/>
+      <c r="CG18" s="71"/>
       <c r="CH18" s="20"/>
       <c r="CI18" s="20"/>
       <c r="CJ18" s="20"/>
@@ -2806,16 +2788,16 @@
         <v>12</v>
       </c>
       <c r="V19" s="12"/>
-      <c r="W19" s="66"/>
-      <c r="X19" s="67"/>
-      <c r="Y19" s="67"/>
-      <c r="Z19" s="67"/>
-      <c r="AA19" s="67"/>
-      <c r="AB19" s="67"/>
-      <c r="AC19" s="67"/>
-      <c r="AD19" s="67"/>
-      <c r="AE19" s="67"/>
-      <c r="AF19" s="68"/>
+      <c r="W19" s="72"/>
+      <c r="X19" s="73"/>
+      <c r="Y19" s="73"/>
+      <c r="Z19" s="73"/>
+      <c r="AA19" s="73"/>
+      <c r="AB19" s="73"/>
+      <c r="AC19" s="73"/>
+      <c r="AD19" s="73"/>
+      <c r="AE19" s="73"/>
+      <c r="AF19" s="74"/>
       <c r="AG19" s="20"/>
       <c r="AH19" s="20"/>
       <c r="AI19" s="20"/>
@@ -2823,16 +2805,16 @@
       <c r="AK19" s="20"/>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AO19" s="66"/>
-      <c r="AP19" s="67"/>
-      <c r="AQ19" s="67"/>
-      <c r="AR19" s="67"/>
-      <c r="AS19" s="67"/>
-      <c r="AT19" s="67"/>
-      <c r="AU19" s="67"/>
-      <c r="AV19" s="67"/>
-      <c r="AW19" s="67"/>
-      <c r="AX19" s="68"/>
+      <c r="AO19" s="72"/>
+      <c r="AP19" s="73"/>
+      <c r="AQ19" s="73"/>
+      <c r="AR19" s="73"/>
+      <c r="AS19" s="73"/>
+      <c r="AT19" s="73"/>
+      <c r="AU19" s="73"/>
+      <c r="AV19" s="73"/>
+      <c r="AW19" s="73"/>
+      <c r="AX19" s="74"/>
       <c r="AY19" s="20"/>
       <c r="AZ19" s="20"/>
       <c r="BA19" s="20"/>
@@ -2843,27 +2825,27 @@
       <c r="BF19" s="20"/>
       <c r="BG19" s="20"/>
       <c r="BK19" s="20"/>
-      <c r="BL19" s="60"/>
-      <c r="BM19" s="61"/>
-      <c r="BN19" s="61"/>
-      <c r="BO19" s="61"/>
-      <c r="BP19" s="61"/>
-      <c r="BQ19" s="62"/>
-      <c r="BR19" s="60"/>
-      <c r="BS19" s="61"/>
-      <c r="BT19" s="61"/>
-      <c r="BU19" s="61"/>
-      <c r="BV19" s="62"/>
-      <c r="BX19" s="66"/>
-      <c r="BY19" s="67"/>
-      <c r="BZ19" s="67"/>
-      <c r="CA19" s="67"/>
-      <c r="CB19" s="67"/>
-      <c r="CC19" s="67"/>
-      <c r="CD19" s="67"/>
-      <c r="CE19" s="67"/>
-      <c r="CF19" s="67"/>
-      <c r="CG19" s="68"/>
+      <c r="BL19" s="63"/>
+      <c r="BM19" s="64"/>
+      <c r="BN19" s="64"/>
+      <c r="BO19" s="64"/>
+      <c r="BP19" s="64"/>
+      <c r="BQ19" s="65"/>
+      <c r="BR19" s="63"/>
+      <c r="BS19" s="64"/>
+      <c r="BT19" s="64"/>
+      <c r="BU19" s="64"/>
+      <c r="BV19" s="65"/>
+      <c r="BX19" s="72"/>
+      <c r="BY19" s="73"/>
+      <c r="BZ19" s="73"/>
+      <c r="CA19" s="73"/>
+      <c r="CB19" s="73"/>
+      <c r="CC19" s="73"/>
+      <c r="CD19" s="73"/>
+      <c r="CE19" s="73"/>
+      <c r="CF19" s="73"/>
+      <c r="CG19" s="74"/>
       <c r="CH19" s="20"/>
       <c r="CI19" s="20"/>
       <c r="CJ19" s="20"/>
@@ -3032,64 +3014,64 @@
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
-      <c r="X22" s="63" t="s">
+      <c r="X22" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="Y22" s="64"/>
-      <c r="Z22" s="64"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="63" t="s">
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AC22" s="64"/>
-      <c r="AD22" s="64"/>
-      <c r="AE22" s="64"/>
-      <c r="AF22" s="64"/>
-      <c r="AG22" s="64"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="64"/>
-      <c r="AK22" s="64"/>
-      <c r="AL22" s="65"/>
+      <c r="AC22" s="70"/>
+      <c r="AD22" s="70"/>
+      <c r="AE22" s="70"/>
+      <c r="AF22" s="70"/>
+      <c r="AG22" s="70"/>
+      <c r="AH22" s="70"/>
+      <c r="AI22" s="70"/>
+      <c r="AJ22" s="70"/>
+      <c r="AK22" s="70"/>
+      <c r="AL22" s="71"/>
       <c r="AM22" s="13"/>
       <c r="AO22" s="12"/>
-      <c r="AP22" s="63" t="s">
+      <c r="AP22" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="AQ22" s="64"/>
-      <c r="AR22" s="64"/>
-      <c r="AS22" s="64"/>
-      <c r="AT22" s="64"/>
-      <c r="AU22" s="64"/>
-      <c r="AV22" s="64"/>
-      <c r="AW22" s="64"/>
-      <c r="AX22" s="64"/>
-      <c r="AY22" s="64"/>
-      <c r="AZ22" s="64"/>
-      <c r="BA22" s="64"/>
-      <c r="BB22" s="64"/>
-      <c r="BC22" s="64"/>
-      <c r="BD22" s="64"/>
-      <c r="BE22" s="64"/>
-      <c r="BF22" s="64"/>
-      <c r="BG22" s="64"/>
-      <c r="BH22" s="65"/>
+      <c r="AQ22" s="70"/>
+      <c r="AR22" s="70"/>
+      <c r="AS22" s="70"/>
+      <c r="AT22" s="70"/>
+      <c r="AU22" s="70"/>
+      <c r="AV22" s="70"/>
+      <c r="AW22" s="70"/>
+      <c r="AX22" s="70"/>
+      <c r="AY22" s="70"/>
+      <c r="AZ22" s="70"/>
+      <c r="BA22" s="70"/>
+      <c r="BB22" s="70"/>
+      <c r="BC22" s="70"/>
+      <c r="BD22" s="70"/>
+      <c r="BE22" s="70"/>
+      <c r="BF22" s="70"/>
+      <c r="BG22" s="70"/>
+      <c r="BH22" s="71"/>
       <c r="BV22" s="13"/>
       <c r="BX22" s="12"/>
-      <c r="BY22" s="63" t="s">
+      <c r="BY22" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="BZ22" s="64"/>
-      <c r="CA22" s="64"/>
-      <c r="CB22" s="65"/>
-      <c r="CF22" s="57" t="s">
+      <c r="BZ22" s="70"/>
+      <c r="CA22" s="70"/>
+      <c r="CB22" s="71"/>
+      <c r="CF22" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="CG22" s="59"/>
-      <c r="CJ22" s="57" t="s">
+      <c r="CG22" s="62"/>
+      <c r="CJ22" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="CK22" s="59"/>
+      <c r="CK22" s="62"/>
       <c r="CL22" s="13"/>
       <c r="CM22" s="13"/>
       <c r="CN22" s="2">
@@ -3124,52 +3106,52 @@
       </c>
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="67"/>
-      <c r="Z23" s="67"/>
-      <c r="AA23" s="68"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="67"/>
-      <c r="AD23" s="67"/>
-      <c r="AE23" s="67"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="67"/>
-      <c r="AH23" s="67"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="67"/>
-      <c r="AL23" s="68"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="73"/>
+      <c r="Z23" s="73"/>
+      <c r="AA23" s="74"/>
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="73"/>
+      <c r="AD23" s="73"/>
+      <c r="AE23" s="73"/>
+      <c r="AF23" s="73"/>
+      <c r="AG23" s="73"/>
+      <c r="AH23" s="73"/>
+      <c r="AI23" s="73"/>
+      <c r="AJ23" s="73"/>
+      <c r="AK23" s="73"/>
+      <c r="AL23" s="74"/>
       <c r="AM23" s="13"/>
       <c r="AO23" s="12"/>
-      <c r="AP23" s="66"/>
-      <c r="AQ23" s="67"/>
-      <c r="AR23" s="67"/>
-      <c r="AS23" s="67"/>
-      <c r="AT23" s="67"/>
-      <c r="AU23" s="67"/>
-      <c r="AV23" s="67"/>
-      <c r="AW23" s="67"/>
-      <c r="AX23" s="67"/>
-      <c r="AY23" s="67"/>
-      <c r="AZ23" s="67"/>
-      <c r="BA23" s="67"/>
-      <c r="BB23" s="67"/>
-      <c r="BC23" s="67"/>
-      <c r="BD23" s="67"/>
-      <c r="BE23" s="67"/>
-      <c r="BF23" s="67"/>
-      <c r="BG23" s="67"/>
-      <c r="BH23" s="68"/>
+      <c r="AP23" s="72"/>
+      <c r="AQ23" s="73"/>
+      <c r="AR23" s="73"/>
+      <c r="AS23" s="73"/>
+      <c r="AT23" s="73"/>
+      <c r="AU23" s="73"/>
+      <c r="AV23" s="73"/>
+      <c r="AW23" s="73"/>
+      <c r="AX23" s="73"/>
+      <c r="AY23" s="73"/>
+      <c r="AZ23" s="73"/>
+      <c r="BA23" s="73"/>
+      <c r="BB23" s="73"/>
+      <c r="BC23" s="73"/>
+      <c r="BD23" s="73"/>
+      <c r="BE23" s="73"/>
+      <c r="BF23" s="73"/>
+      <c r="BG23" s="73"/>
+      <c r="BH23" s="74"/>
       <c r="BV23" s="13"/>
       <c r="BX23" s="12"/>
-      <c r="BY23" s="66"/>
-      <c r="BZ23" s="67"/>
-      <c r="CA23" s="67"/>
-      <c r="CB23" s="68"/>
-      <c r="CF23" s="60"/>
-      <c r="CG23" s="62"/>
-      <c r="CJ23" s="60"/>
-      <c r="CK23" s="62"/>
+      <c r="BY23" s="72"/>
+      <c r="BZ23" s="73"/>
+      <c r="CA23" s="73"/>
+      <c r="CB23" s="74"/>
+      <c r="CF23" s="63"/>
+      <c r="CG23" s="65"/>
+      <c r="CJ23" s="63"/>
+      <c r="CK23" s="65"/>
       <c r="CL23" s="13"/>
       <c r="CM23" s="13"/>
       <c r="CN23" s="2">
@@ -3242,61 +3224,61 @@
       </c>
       <c r="V25" s="12"/>
       <c r="W25" s="12"/>
-      <c r="X25" s="63" t="s">
+      <c r="X25" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="Y25" s="64"/>
-      <c r="Z25" s="64"/>
-      <c r="AA25" s="65"/>
-      <c r="AB25" s="63" t="s">
+      <c r="Y25" s="70"/>
+      <c r="Z25" s="70"/>
+      <c r="AA25" s="71"/>
+      <c r="AB25" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AC25" s="64"/>
-      <c r="AD25" s="64"/>
-      <c r="AE25" s="64"/>
-      <c r="AF25" s="64"/>
-      <c r="AG25" s="64"/>
-      <c r="AH25" s="64"/>
-      <c r="AI25" s="64"/>
-      <c r="AJ25" s="64"/>
-      <c r="AK25" s="64"/>
-      <c r="AL25" s="65"/>
+      <c r="AC25" s="70"/>
+      <c r="AD25" s="70"/>
+      <c r="AE25" s="70"/>
+      <c r="AF25" s="70"/>
+      <c r="AG25" s="70"/>
+      <c r="AH25" s="70"/>
+      <c r="AI25" s="70"/>
+      <c r="AJ25" s="70"/>
+      <c r="AK25" s="70"/>
+      <c r="AL25" s="71"/>
       <c r="AM25" s="13"/>
       <c r="AO25" s="12"/>
-      <c r="AP25" s="57" t="s">
+      <c r="AP25" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="AQ25" s="58"/>
-      <c r="AR25" s="58"/>
-      <c r="AS25" s="58"/>
-      <c r="AT25" s="58"/>
-      <c r="AU25" s="58"/>
-      <c r="AV25" s="58"/>
-      <c r="AW25" s="58"/>
-      <c r="AX25" s="58"/>
-      <c r="AY25" s="58"/>
-      <c r="AZ25" s="58"/>
-      <c r="BA25" s="58"/>
-      <c r="BB25" s="58"/>
-      <c r="BC25" s="58"/>
-      <c r="BD25" s="58"/>
-      <c r="BE25" s="58"/>
-      <c r="BF25" s="58"/>
-      <c r="BG25" s="58"/>
-      <c r="BH25" s="58"/>
-      <c r="BI25" s="58"/>
-      <c r="BJ25" s="58"/>
-      <c r="BK25" s="58"/>
-      <c r="BL25" s="58"/>
-      <c r="BM25" s="58"/>
-      <c r="BN25" s="58"/>
-      <c r="BO25" s="58"/>
-      <c r="BP25" s="58"/>
-      <c r="BQ25" s="58"/>
-      <c r="BR25" s="58"/>
-      <c r="BS25" s="58"/>
-      <c r="BT25" s="58"/>
-      <c r="BU25" s="59"/>
+      <c r="AQ25" s="61"/>
+      <c r="AR25" s="61"/>
+      <c r="AS25" s="61"/>
+      <c r="AT25" s="61"/>
+      <c r="AU25" s="61"/>
+      <c r="AV25" s="61"/>
+      <c r="AW25" s="61"/>
+      <c r="AX25" s="61"/>
+      <c r="AY25" s="61"/>
+      <c r="AZ25" s="61"/>
+      <c r="BA25" s="61"/>
+      <c r="BB25" s="61"/>
+      <c r="BC25" s="61"/>
+      <c r="BD25" s="61"/>
+      <c r="BE25" s="61"/>
+      <c r="BF25" s="61"/>
+      <c r="BG25" s="61"/>
+      <c r="BH25" s="61"/>
+      <c r="BI25" s="61"/>
+      <c r="BJ25" s="61"/>
+      <c r="BK25" s="61"/>
+      <c r="BL25" s="61"/>
+      <c r="BM25" s="61"/>
+      <c r="BN25" s="61"/>
+      <c r="BO25" s="61"/>
+      <c r="BP25" s="61"/>
+      <c r="BQ25" s="61"/>
+      <c r="BR25" s="61"/>
+      <c r="BS25" s="61"/>
+      <c r="BT25" s="61"/>
+      <c r="BU25" s="62"/>
       <c r="BV25" s="13"/>
       <c r="BX25" s="12"/>
       <c r="CL25" s="13"/>
@@ -3333,55 +3315,55 @@
       </c>
       <c r="V26" s="12"/>
       <c r="W26" s="12"/>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="67"/>
-      <c r="Z26" s="67"/>
-      <c r="AA26" s="68"/>
-      <c r="AB26" s="66"/>
-      <c r="AC26" s="67"/>
-      <c r="AD26" s="67"/>
-      <c r="AE26" s="67"/>
-      <c r="AF26" s="67"/>
-      <c r="AG26" s="67"/>
-      <c r="AH26" s="67"/>
-      <c r="AI26" s="67"/>
-      <c r="AJ26" s="67"/>
-      <c r="AK26" s="67"/>
-      <c r="AL26" s="68"/>
+      <c r="X26" s="72"/>
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="74"/>
+      <c r="AB26" s="72"/>
+      <c r="AC26" s="73"/>
+      <c r="AD26" s="73"/>
+      <c r="AE26" s="73"/>
+      <c r="AF26" s="73"/>
+      <c r="AG26" s="73"/>
+      <c r="AH26" s="73"/>
+      <c r="AI26" s="73"/>
+      <c r="AJ26" s="73"/>
+      <c r="AK26" s="73"/>
+      <c r="AL26" s="74"/>
       <c r="AM26" s="13"/>
       <c r="AO26" s="12"/>
-      <c r="AP26" s="60"/>
-      <c r="AQ26" s="61"/>
-      <c r="AR26" s="61"/>
-      <c r="AS26" s="61"/>
-      <c r="AT26" s="61"/>
-      <c r="AU26" s="61"/>
-      <c r="AV26" s="61"/>
-      <c r="AW26" s="61"/>
-      <c r="AX26" s="61"/>
-      <c r="AY26" s="61"/>
-      <c r="AZ26" s="61"/>
-      <c r="BA26" s="61"/>
-      <c r="BB26" s="61"/>
-      <c r="BC26" s="61"/>
-      <c r="BD26" s="61"/>
-      <c r="BE26" s="61"/>
-      <c r="BF26" s="61"/>
-      <c r="BG26" s="61"/>
-      <c r="BH26" s="61"/>
-      <c r="BI26" s="61"/>
-      <c r="BJ26" s="61"/>
-      <c r="BK26" s="61"/>
-      <c r="BL26" s="61"/>
-      <c r="BM26" s="61"/>
-      <c r="BN26" s="61"/>
-      <c r="BO26" s="61"/>
-      <c r="BP26" s="61"/>
-      <c r="BQ26" s="61"/>
-      <c r="BR26" s="61"/>
-      <c r="BS26" s="61"/>
-      <c r="BT26" s="61"/>
-      <c r="BU26" s="62"/>
+      <c r="AP26" s="63"/>
+      <c r="AQ26" s="64"/>
+      <c r="AR26" s="64"/>
+      <c r="AS26" s="64"/>
+      <c r="AT26" s="64"/>
+      <c r="AU26" s="64"/>
+      <c r="AV26" s="64"/>
+      <c r="AW26" s="64"/>
+      <c r="AX26" s="64"/>
+      <c r="AY26" s="64"/>
+      <c r="AZ26" s="64"/>
+      <c r="BA26" s="64"/>
+      <c r="BB26" s="64"/>
+      <c r="BC26" s="64"/>
+      <c r="BD26" s="64"/>
+      <c r="BE26" s="64"/>
+      <c r="BF26" s="64"/>
+      <c r="BG26" s="64"/>
+      <c r="BH26" s="64"/>
+      <c r="BI26" s="64"/>
+      <c r="BJ26" s="64"/>
+      <c r="BK26" s="64"/>
+      <c r="BL26" s="64"/>
+      <c r="BM26" s="64"/>
+      <c r="BN26" s="64"/>
+      <c r="BO26" s="64"/>
+      <c r="BP26" s="64"/>
+      <c r="BQ26" s="64"/>
+      <c r="BR26" s="64"/>
+      <c r="BS26" s="64"/>
+      <c r="BT26" s="64"/>
+      <c r="BU26" s="65"/>
       <c r="BV26" s="13"/>
       <c r="BX26" s="12"/>
       <c r="CL26" s="13"/>
@@ -3456,39 +3438,39 @@
       </c>
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
-      <c r="X28" s="63" t="s">
+      <c r="X28" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="Y28" s="64"/>
-      <c r="Z28" s="64"/>
-      <c r="AA28" s="65"/>
-      <c r="AB28" s="63" t="s">
+      <c r="Y28" s="70"/>
+      <c r="Z28" s="70"/>
+      <c r="AA28" s="71"/>
+      <c r="AB28" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AC28" s="64"/>
-      <c r="AD28" s="64"/>
-      <c r="AE28" s="64"/>
-      <c r="AF28" s="64"/>
-      <c r="AG28" s="64"/>
-      <c r="AH28" s="64"/>
-      <c r="AI28" s="64"/>
-      <c r="AJ28" s="64"/>
-      <c r="AK28" s="64"/>
-      <c r="AL28" s="65"/>
+      <c r="AC28" s="70"/>
+      <c r="AD28" s="70"/>
+      <c r="AE28" s="70"/>
+      <c r="AF28" s="70"/>
+      <c r="AG28" s="70"/>
+      <c r="AH28" s="70"/>
+      <c r="AI28" s="70"/>
+      <c r="AJ28" s="70"/>
+      <c r="AK28" s="70"/>
+      <c r="AL28" s="71"/>
       <c r="AM28" s="13"/>
       <c r="AO28" s="12"/>
-      <c r="AP28" s="63" t="s">
+      <c r="AP28" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="AQ28" s="64"/>
-      <c r="AR28" s="64"/>
-      <c r="AS28" s="64"/>
-      <c r="AT28" s="64"/>
-      <c r="AU28" s="64"/>
-      <c r="AV28" s="64"/>
-      <c r="AW28" s="64"/>
-      <c r="AX28" s="64"/>
-      <c r="AY28" s="65"/>
+      <c r="AQ28" s="70"/>
+      <c r="AR28" s="70"/>
+      <c r="AS28" s="70"/>
+      <c r="AT28" s="70"/>
+      <c r="AU28" s="70"/>
+      <c r="AV28" s="70"/>
+      <c r="AW28" s="70"/>
+      <c r="AX28" s="70"/>
+      <c r="AY28" s="71"/>
       <c r="AZ28" s="20"/>
       <c r="BB28" s="20"/>
       <c r="BC28" s="20"/>
@@ -3504,22 +3486,22 @@
       <c r="BN28" s="20"/>
       <c r="BV28" s="13"/>
       <c r="BX28" s="12"/>
-      <c r="BY28" s="57" t="s">
+      <c r="BY28" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="BZ28" s="58"/>
-      <c r="CA28" s="58"/>
-      <c r="CB28" s="58"/>
-      <c r="CC28" s="58"/>
-      <c r="CD28" s="59"/>
-      <c r="CF28" s="57" t="s">
+      <c r="BZ28" s="61"/>
+      <c r="CA28" s="61"/>
+      <c r="CB28" s="61"/>
+      <c r="CC28" s="61"/>
+      <c r="CD28" s="62"/>
+      <c r="CF28" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="CG28" s="58"/>
-      <c r="CH28" s="58"/>
-      <c r="CI28" s="58"/>
-      <c r="CJ28" s="58"/>
-      <c r="CK28" s="59"/>
+      <c r="CG28" s="61"/>
+      <c r="CH28" s="61"/>
+      <c r="CI28" s="61"/>
+      <c r="CJ28" s="61"/>
+      <c r="CK28" s="62"/>
       <c r="CL28" s="13"/>
       <c r="CM28" s="13"/>
       <c r="CN28" s="2">
@@ -3554,33 +3536,33 @@
       </c>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
-      <c r="X29" s="66"/>
-      <c r="Y29" s="67"/>
-      <c r="Z29" s="67"/>
-      <c r="AA29" s="68"/>
-      <c r="AB29" s="66"/>
-      <c r="AC29" s="67"/>
-      <c r="AD29" s="67"/>
-      <c r="AE29" s="67"/>
-      <c r="AF29" s="67"/>
-      <c r="AG29" s="67"/>
-      <c r="AH29" s="67"/>
-      <c r="AI29" s="67"/>
-      <c r="AJ29" s="67"/>
-      <c r="AK29" s="67"/>
-      <c r="AL29" s="68"/>
+      <c r="X29" s="72"/>
+      <c r="Y29" s="73"/>
+      <c r="Z29" s="73"/>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="72"/>
+      <c r="AC29" s="73"/>
+      <c r="AD29" s="73"/>
+      <c r="AE29" s="73"/>
+      <c r="AF29" s="73"/>
+      <c r="AG29" s="73"/>
+      <c r="AH29" s="73"/>
+      <c r="AI29" s="73"/>
+      <c r="AJ29" s="73"/>
+      <c r="AK29" s="73"/>
+      <c r="AL29" s="74"/>
       <c r="AM29" s="13"/>
       <c r="AO29" s="12"/>
-      <c r="AP29" s="66"/>
-      <c r="AQ29" s="67"/>
-      <c r="AR29" s="67"/>
-      <c r="AS29" s="67"/>
-      <c r="AT29" s="67"/>
-      <c r="AU29" s="67"/>
-      <c r="AV29" s="67"/>
-      <c r="AW29" s="67"/>
-      <c r="AX29" s="67"/>
-      <c r="AY29" s="68"/>
+      <c r="AP29" s="72"/>
+      <c r="AQ29" s="73"/>
+      <c r="AR29" s="73"/>
+      <c r="AS29" s="73"/>
+      <c r="AT29" s="73"/>
+      <c r="AU29" s="73"/>
+      <c r="AV29" s="73"/>
+      <c r="AW29" s="73"/>
+      <c r="AX29" s="73"/>
+      <c r="AY29" s="74"/>
       <c r="AZ29" s="20"/>
       <c r="BB29" s="20"/>
       <c r="BC29" s="20"/>
@@ -3596,18 +3578,18 @@
       <c r="BN29" s="20"/>
       <c r="BV29" s="13"/>
       <c r="BX29" s="12"/>
-      <c r="BY29" s="60"/>
-      <c r="BZ29" s="61"/>
-      <c r="CA29" s="61"/>
-      <c r="CB29" s="61"/>
-      <c r="CC29" s="61"/>
-      <c r="CD29" s="62"/>
-      <c r="CF29" s="60"/>
-      <c r="CG29" s="61"/>
-      <c r="CH29" s="61"/>
-      <c r="CI29" s="61"/>
-      <c r="CJ29" s="61"/>
-      <c r="CK29" s="62"/>
+      <c r="BY29" s="63"/>
+      <c r="BZ29" s="64"/>
+      <c r="CA29" s="64"/>
+      <c r="CB29" s="64"/>
+      <c r="CC29" s="64"/>
+      <c r="CD29" s="65"/>
+      <c r="CF29" s="63"/>
+      <c r="CG29" s="64"/>
+      <c r="CH29" s="64"/>
+      <c r="CI29" s="64"/>
+      <c r="CJ29" s="64"/>
+      <c r="CK29" s="65"/>
       <c r="CL29" s="13"/>
       <c r="CM29" s="13"/>
       <c r="CN29" s="2">
@@ -3698,76 +3680,76 @@
       </c>
       <c r="V31" s="12"/>
       <c r="W31" s="12"/>
-      <c r="X31" s="63" t="s">
+      <c r="X31" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="Y31" s="64"/>
-      <c r="Z31" s="64"/>
-      <c r="AA31" s="65"/>
-      <c r="AB31" s="63" t="s">
+      <c r="Y31" s="70"/>
+      <c r="Z31" s="70"/>
+      <c r="AA31" s="71"/>
+      <c r="AB31" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AC31" s="64"/>
-      <c r="AD31" s="64"/>
-      <c r="AE31" s="64"/>
-      <c r="AF31" s="64"/>
-      <c r="AG31" s="64"/>
-      <c r="AH31" s="64"/>
-      <c r="AI31" s="64"/>
-      <c r="AJ31" s="64"/>
-      <c r="AK31" s="64"/>
-      <c r="AL31" s="65"/>
+      <c r="AC31" s="70"/>
+      <c r="AD31" s="70"/>
+      <c r="AE31" s="70"/>
+      <c r="AF31" s="70"/>
+      <c r="AG31" s="70"/>
+      <c r="AH31" s="70"/>
+      <c r="AI31" s="70"/>
+      <c r="AJ31" s="70"/>
+      <c r="AK31" s="70"/>
+      <c r="AL31" s="71"/>
       <c r="AM31" s="13"/>
       <c r="AO31" s="12"/>
       <c r="AS31" s="20"/>
       <c r="AT31" s="20"/>
       <c r="AU31" s="20"/>
-      <c r="AV31" s="57" t="s">
+      <c r="AV31" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="AW31" s="58"/>
-      <c r="AX31" s="58"/>
-      <c r="AY31" s="58"/>
-      <c r="AZ31" s="58"/>
-      <c r="BA31" s="59"/>
+      <c r="AW31" s="61"/>
+      <c r="AX31" s="61"/>
+      <c r="AY31" s="61"/>
+      <c r="AZ31" s="61"/>
+      <c r="BA31" s="62"/>
       <c r="BB31" s="20"/>
-      <c r="BC31" s="57" t="s">
+      <c r="BC31" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="BD31" s="58"/>
-      <c r="BE31" s="58"/>
-      <c r="BF31" s="58"/>
-      <c r="BG31" s="58"/>
-      <c r="BH31" s="59"/>
+      <c r="BD31" s="61"/>
+      <c r="BE31" s="61"/>
+      <c r="BF31" s="61"/>
+      <c r="BG31" s="61"/>
+      <c r="BH31" s="62"/>
       <c r="BI31" s="20"/>
-      <c r="BJ31" s="57" t="s">
+      <c r="BJ31" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="BK31" s="58"/>
-      <c r="BL31" s="58"/>
-      <c r="BM31" s="58"/>
-      <c r="BN31" s="58"/>
-      <c r="BO31" s="59"/>
+      <c r="BK31" s="61"/>
+      <c r="BL31" s="61"/>
+      <c r="BM31" s="61"/>
+      <c r="BN31" s="61"/>
+      <c r="BO31" s="62"/>
       <c r="BP31" s="20"/>
       <c r="BQ31" s="20"/>
       <c r="BR31" s="20"/>
       <c r="BV31" s="13"/>
       <c r="BX31" s="12"/>
-      <c r="BY31" s="57" t="s">
+      <c r="BY31" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="BZ31" s="58"/>
-      <c r="CA31" s="58"/>
-      <c r="CB31" s="58"/>
-      <c r="CC31" s="58"/>
-      <c r="CD31" s="58"/>
-      <c r="CE31" s="58"/>
-      <c r="CF31" s="58"/>
-      <c r="CG31" s="58"/>
-      <c r="CH31" s="58"/>
-      <c r="CI31" s="58"/>
-      <c r="CJ31" s="58"/>
-      <c r="CK31" s="59"/>
+      <c r="BZ31" s="61"/>
+      <c r="CA31" s="61"/>
+      <c r="CB31" s="61"/>
+      <c r="CC31" s="61"/>
+      <c r="CD31" s="61"/>
+      <c r="CE31" s="61"/>
+      <c r="CF31" s="61"/>
+      <c r="CG31" s="61"/>
+      <c r="CH31" s="61"/>
+      <c r="CI31" s="61"/>
+      <c r="CJ31" s="61"/>
+      <c r="CK31" s="62"/>
       <c r="CL31" s="13"/>
       <c r="CM31" s="13"/>
       <c r="CN31" s="2">
@@ -3802,64 +3784,64 @@
       </c>
       <c r="V32" s="12"/>
       <c r="W32" s="12"/>
-      <c r="X32" s="66"/>
-      <c r="Y32" s="67"/>
-      <c r="Z32" s="67"/>
-      <c r="AA32" s="68"/>
-      <c r="AB32" s="66"/>
-      <c r="AC32" s="67"/>
-      <c r="AD32" s="67"/>
-      <c r="AE32" s="67"/>
-      <c r="AF32" s="67"/>
-      <c r="AG32" s="67"/>
-      <c r="AH32" s="67"/>
-      <c r="AI32" s="67"/>
-      <c r="AJ32" s="67"/>
-      <c r="AK32" s="67"/>
-      <c r="AL32" s="68"/>
+      <c r="X32" s="72"/>
+      <c r="Y32" s="73"/>
+      <c r="Z32" s="73"/>
+      <c r="AA32" s="74"/>
+      <c r="AB32" s="72"/>
+      <c r="AC32" s="73"/>
+      <c r="AD32" s="73"/>
+      <c r="AE32" s="73"/>
+      <c r="AF32" s="73"/>
+      <c r="AG32" s="73"/>
+      <c r="AH32" s="73"/>
+      <c r="AI32" s="73"/>
+      <c r="AJ32" s="73"/>
+      <c r="AK32" s="73"/>
+      <c r="AL32" s="74"/>
       <c r="AM32" s="13"/>
       <c r="AO32" s="12"/>
       <c r="AS32" s="20"/>
       <c r="AT32" s="20"/>
       <c r="AU32" s="20"/>
-      <c r="AV32" s="60"/>
-      <c r="AW32" s="61"/>
-      <c r="AX32" s="61"/>
-      <c r="AY32" s="61"/>
-      <c r="AZ32" s="61"/>
-      <c r="BA32" s="62"/>
+      <c r="AV32" s="63"/>
+      <c r="AW32" s="64"/>
+      <c r="AX32" s="64"/>
+      <c r="AY32" s="64"/>
+      <c r="AZ32" s="64"/>
+      <c r="BA32" s="65"/>
       <c r="BB32" s="20"/>
-      <c r="BC32" s="60"/>
-      <c r="BD32" s="61"/>
-      <c r="BE32" s="61"/>
-      <c r="BF32" s="61"/>
-      <c r="BG32" s="61"/>
-      <c r="BH32" s="62"/>
+      <c r="BC32" s="63"/>
+      <c r="BD32" s="64"/>
+      <c r="BE32" s="64"/>
+      <c r="BF32" s="64"/>
+      <c r="BG32" s="64"/>
+      <c r="BH32" s="65"/>
       <c r="BI32" s="20"/>
-      <c r="BJ32" s="60"/>
-      <c r="BK32" s="61"/>
-      <c r="BL32" s="61"/>
-      <c r="BM32" s="61"/>
-      <c r="BN32" s="61"/>
-      <c r="BO32" s="62"/>
+      <c r="BJ32" s="63"/>
+      <c r="BK32" s="64"/>
+      <c r="BL32" s="64"/>
+      <c r="BM32" s="64"/>
+      <c r="BN32" s="64"/>
+      <c r="BO32" s="65"/>
       <c r="BP32" s="20"/>
       <c r="BQ32" s="20"/>
       <c r="BR32" s="20"/>
       <c r="BV32" s="13"/>
       <c r="BX32" s="12"/>
-      <c r="BY32" s="69"/>
-      <c r="BZ32" s="70"/>
-      <c r="CA32" s="70"/>
-      <c r="CB32" s="70"/>
-      <c r="CC32" s="70"/>
-      <c r="CD32" s="70"/>
-      <c r="CE32" s="70"/>
-      <c r="CF32" s="70"/>
-      <c r="CG32" s="70"/>
-      <c r="CH32" s="70"/>
-      <c r="CI32" s="70"/>
-      <c r="CJ32" s="70"/>
-      <c r="CK32" s="71"/>
+      <c r="BY32" s="66"/>
+      <c r="BZ32" s="67"/>
+      <c r="CA32" s="67"/>
+      <c r="CB32" s="67"/>
+      <c r="CC32" s="67"/>
+      <c r="CD32" s="67"/>
+      <c r="CE32" s="67"/>
+      <c r="CF32" s="67"/>
+      <c r="CG32" s="67"/>
+      <c r="CH32" s="67"/>
+      <c r="CI32" s="67"/>
+      <c r="CJ32" s="67"/>
+      <c r="CK32" s="68"/>
       <c r="CL32" s="13"/>
       <c r="CM32" s="13"/>
       <c r="CN32" s="2">
@@ -3898,19 +3880,19 @@
       <c r="AO33" s="12"/>
       <c r="BV33" s="13"/>
       <c r="BX33" s="12"/>
-      <c r="BY33" s="60"/>
-      <c r="BZ33" s="61"/>
-      <c r="CA33" s="61"/>
-      <c r="CB33" s="61"/>
-      <c r="CC33" s="61"/>
-      <c r="CD33" s="61"/>
-      <c r="CE33" s="61"/>
-      <c r="CF33" s="61"/>
-      <c r="CG33" s="61"/>
-      <c r="CH33" s="61"/>
-      <c r="CI33" s="61"/>
-      <c r="CJ33" s="61"/>
-      <c r="CK33" s="62"/>
+      <c r="BY33" s="63"/>
+      <c r="BZ33" s="64"/>
+      <c r="CA33" s="64"/>
+      <c r="CB33" s="64"/>
+      <c r="CC33" s="64"/>
+      <c r="CD33" s="64"/>
+      <c r="CE33" s="64"/>
+      <c r="CF33" s="64"/>
+      <c r="CG33" s="64"/>
+      <c r="CH33" s="64"/>
+      <c r="CI33" s="64"/>
+      <c r="CJ33" s="64"/>
+      <c r="CK33" s="65"/>
       <c r="CL33" s="13"/>
       <c r="CM33" s="13"/>
       <c r="CN33" s="2">
@@ -4074,63 +4056,63 @@
         <v>29</v>
       </c>
       <c r="V36" s="12"/>
-      <c r="W36" s="63" t="s">
+      <c r="W36" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="X36" s="64"/>
-      <c r="Y36" s="64"/>
-      <c r="Z36" s="64"/>
-      <c r="AA36" s="64"/>
-      <c r="AB36" s="64"/>
-      <c r="AC36" s="64"/>
-      <c r="AD36" s="64"/>
-      <c r="AE36" s="64"/>
-      <c r="AF36" s="65"/>
+      <c r="X36" s="70"/>
+      <c r="Y36" s="70"/>
+      <c r="Z36" s="70"/>
+      <c r="AA36" s="70"/>
+      <c r="AB36" s="70"/>
+      <c r="AC36" s="70"/>
+      <c r="AD36" s="70"/>
+      <c r="AE36" s="70"/>
+      <c r="AF36" s="71"/>
       <c r="AG36" s="20"/>
-      <c r="AH36" s="63" t="s">
+      <c r="AH36" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="AI36" s="64"/>
-      <c r="AJ36" s="65"/>
-      <c r="AK36" s="57" t="s">
+      <c r="AI36" s="70"/>
+      <c r="AJ36" s="71"/>
+      <c r="AK36" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="AL36" s="58"/>
-      <c r="AM36" s="58"/>
-      <c r="AN36" s="59"/>
+      <c r="AL36" s="61"/>
+      <c r="AM36" s="61"/>
+      <c r="AN36" s="62"/>
       <c r="AO36" s="20"/>
-      <c r="AP36" s="57" t="s">
+      <c r="AP36" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="AQ36" s="59"/>
+      <c r="AQ36" s="62"/>
       <c r="AS36" s="20"/>
-      <c r="AT36" s="63" t="s">
+      <c r="AT36" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="AU36" s="64"/>
-      <c r="AV36" s="65"/>
-      <c r="AW36" s="58" t="s">
+      <c r="AU36" s="70"/>
+      <c r="AV36" s="71"/>
+      <c r="AW36" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AX36" s="58"/>
-      <c r="AY36" s="58"/>
-      <c r="AZ36" s="58"/>
-      <c r="BA36" s="58"/>
-      <c r="BB36" s="58"/>
-      <c r="BC36" s="58"/>
-      <c r="BD36" s="59"/>
-      <c r="BF36" s="63" t="s">
+      <c r="AX36" s="61"/>
+      <c r="AY36" s="61"/>
+      <c r="AZ36" s="61"/>
+      <c r="BA36" s="61"/>
+      <c r="BB36" s="61"/>
+      <c r="BC36" s="61"/>
+      <c r="BD36" s="62"/>
+      <c r="BF36" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="BG36" s="64"/>
-      <c r="BH36" s="64"/>
-      <c r="BI36" s="64"/>
-      <c r="BJ36" s="64"/>
-      <c r="BK36" s="64"/>
-      <c r="BL36" s="64"/>
-      <c r="BM36" s="64"/>
-      <c r="BN36" s="64"/>
-      <c r="BO36" s="65"/>
+      <c r="BG36" s="70"/>
+      <c r="BH36" s="70"/>
+      <c r="BI36" s="70"/>
+      <c r="BJ36" s="70"/>
+      <c r="BK36" s="70"/>
+      <c r="BL36" s="70"/>
+      <c r="BM36" s="70"/>
+      <c r="BN36" s="70"/>
+      <c r="BO36" s="71"/>
       <c r="BP36" s="20"/>
       <c r="BQ36" s="20"/>
       <c r="BR36" s="20"/>
@@ -4186,49 +4168,49 @@
         <v>30</v>
       </c>
       <c r="V37" s="12"/>
-      <c r="W37" s="66"/>
-      <c r="X37" s="67"/>
-      <c r="Y37" s="67"/>
-      <c r="Z37" s="67"/>
-      <c r="AA37" s="67"/>
-      <c r="AB37" s="67"/>
-      <c r="AC37" s="67"/>
-      <c r="AD37" s="67"/>
-      <c r="AE37" s="67"/>
-      <c r="AF37" s="68"/>
+      <c r="W37" s="72"/>
+      <c r="X37" s="73"/>
+      <c r="Y37" s="73"/>
+      <c r="Z37" s="73"/>
+      <c r="AA37" s="73"/>
+      <c r="AB37" s="73"/>
+      <c r="AC37" s="73"/>
+      <c r="AD37" s="73"/>
+      <c r="AE37" s="73"/>
+      <c r="AF37" s="74"/>
       <c r="AG37" s="20"/>
-      <c r="AH37" s="66"/>
-      <c r="AI37" s="67"/>
-      <c r="AJ37" s="68"/>
-      <c r="AK37" s="60"/>
-      <c r="AL37" s="61"/>
-      <c r="AM37" s="61"/>
-      <c r="AN37" s="62"/>
+      <c r="AH37" s="72"/>
+      <c r="AI37" s="73"/>
+      <c r="AJ37" s="74"/>
+      <c r="AK37" s="63"/>
+      <c r="AL37" s="64"/>
+      <c r="AM37" s="64"/>
+      <c r="AN37" s="65"/>
       <c r="AO37" s="20"/>
-      <c r="AP37" s="60"/>
-      <c r="AQ37" s="62"/>
+      <c r="AP37" s="63"/>
+      <c r="AQ37" s="65"/>
       <c r="AS37" s="20"/>
-      <c r="AT37" s="66"/>
-      <c r="AU37" s="67"/>
-      <c r="AV37" s="68"/>
-      <c r="AW37" s="61"/>
-      <c r="AX37" s="61"/>
-      <c r="AY37" s="61"/>
-      <c r="AZ37" s="61"/>
-      <c r="BA37" s="61"/>
-      <c r="BB37" s="61"/>
-      <c r="BC37" s="61"/>
-      <c r="BD37" s="62"/>
-      <c r="BF37" s="66"/>
-      <c r="BG37" s="67"/>
-      <c r="BH37" s="67"/>
-      <c r="BI37" s="67"/>
-      <c r="BJ37" s="67"/>
-      <c r="BK37" s="67"/>
-      <c r="BL37" s="67"/>
-      <c r="BM37" s="67"/>
-      <c r="BN37" s="67"/>
-      <c r="BO37" s="68"/>
+      <c r="AT37" s="72"/>
+      <c r="AU37" s="73"/>
+      <c r="AV37" s="74"/>
+      <c r="AW37" s="64"/>
+      <c r="AX37" s="64"/>
+      <c r="AY37" s="64"/>
+      <c r="AZ37" s="64"/>
+      <c r="BA37" s="64"/>
+      <c r="BB37" s="64"/>
+      <c r="BC37" s="64"/>
+      <c r="BD37" s="65"/>
+      <c r="BF37" s="72"/>
+      <c r="BG37" s="73"/>
+      <c r="BH37" s="73"/>
+      <c r="BI37" s="73"/>
+      <c r="BJ37" s="73"/>
+      <c r="BK37" s="73"/>
+      <c r="BL37" s="73"/>
+      <c r="BM37" s="73"/>
+      <c r="BN37" s="73"/>
+      <c r="BO37" s="74"/>
       <c r="BP37" s="20"/>
       <c r="BQ37" s="20"/>
       <c r="BR37" s="20"/>
@@ -4418,42 +4400,42 @@
       <c r="W40" s="12"/>
       <c r="BD40" s="13"/>
       <c r="BF40" s="12"/>
-      <c r="BG40" s="63" t="s">
+      <c r="BG40" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="BH40" s="64"/>
-      <c r="BI40" s="64"/>
-      <c r="BJ40" s="64"/>
-      <c r="BK40" s="64"/>
-      <c r="BL40" s="64"/>
-      <c r="BM40" s="64"/>
-      <c r="BN40" s="64"/>
-      <c r="BO40" s="64"/>
-      <c r="BP40" s="64"/>
-      <c r="BQ40" s="64"/>
-      <c r="BR40" s="64"/>
-      <c r="BS40" s="64"/>
-      <c r="BT40" s="64"/>
-      <c r="BU40" s="64"/>
-      <c r="BV40" s="64"/>
-      <c r="BW40" s="64"/>
-      <c r="BX40" s="64"/>
-      <c r="BY40" s="65"/>
+      <c r="BH40" s="70"/>
+      <c r="BI40" s="70"/>
+      <c r="BJ40" s="70"/>
+      <c r="BK40" s="70"/>
+      <c r="BL40" s="70"/>
+      <c r="BM40" s="70"/>
+      <c r="BN40" s="70"/>
+      <c r="BO40" s="70"/>
+      <c r="BP40" s="70"/>
+      <c r="BQ40" s="70"/>
+      <c r="BR40" s="70"/>
+      <c r="BS40" s="70"/>
+      <c r="BT40" s="70"/>
+      <c r="BU40" s="70"/>
+      <c r="BV40" s="70"/>
+      <c r="BW40" s="70"/>
+      <c r="BX40" s="70"/>
+      <c r="BY40" s="71"/>
       <c r="BZ40" s="20"/>
-      <c r="CA40" s="57" t="s">
+      <c r="CA40" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="CB40" s="58"/>
-      <c r="CC40" s="58"/>
-      <c r="CD40" s="58"/>
-      <c r="CE40" s="59"/>
-      <c r="CG40" s="57" t="s">
+      <c r="CB40" s="61"/>
+      <c r="CC40" s="61"/>
+      <c r="CD40" s="61"/>
+      <c r="CE40" s="62"/>
+      <c r="CG40" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="CH40" s="58"/>
-      <c r="CI40" s="58"/>
-      <c r="CJ40" s="58"/>
-      <c r="CK40" s="59"/>
+      <c r="CH40" s="61"/>
+      <c r="CI40" s="61"/>
+      <c r="CJ40" s="61"/>
+      <c r="CK40" s="62"/>
       <c r="CL40" s="13"/>
       <c r="CM40" s="13"/>
       <c r="CN40" s="2">
@@ -4490,36 +4472,36 @@
       <c r="W41" s="12"/>
       <c r="BD41" s="13"/>
       <c r="BF41" s="12"/>
-      <c r="BG41" s="66"/>
-      <c r="BH41" s="67"/>
-      <c r="BI41" s="67"/>
-      <c r="BJ41" s="67"/>
-      <c r="BK41" s="67"/>
-      <c r="BL41" s="67"/>
-      <c r="BM41" s="67"/>
-      <c r="BN41" s="67"/>
-      <c r="BO41" s="67"/>
-      <c r="BP41" s="67"/>
-      <c r="BQ41" s="67"/>
-      <c r="BR41" s="67"/>
-      <c r="BS41" s="67"/>
-      <c r="BT41" s="67"/>
-      <c r="BU41" s="67"/>
-      <c r="BV41" s="67"/>
-      <c r="BW41" s="67"/>
-      <c r="BX41" s="67"/>
-      <c r="BY41" s="68"/>
+      <c r="BG41" s="72"/>
+      <c r="BH41" s="73"/>
+      <c r="BI41" s="73"/>
+      <c r="BJ41" s="73"/>
+      <c r="BK41" s="73"/>
+      <c r="BL41" s="73"/>
+      <c r="BM41" s="73"/>
+      <c r="BN41" s="73"/>
+      <c r="BO41" s="73"/>
+      <c r="BP41" s="73"/>
+      <c r="BQ41" s="73"/>
+      <c r="BR41" s="73"/>
+      <c r="BS41" s="73"/>
+      <c r="BT41" s="73"/>
+      <c r="BU41" s="73"/>
+      <c r="BV41" s="73"/>
+      <c r="BW41" s="73"/>
+      <c r="BX41" s="73"/>
+      <c r="BY41" s="74"/>
       <c r="BZ41" s="20"/>
-      <c r="CA41" s="60"/>
-      <c r="CB41" s="61"/>
-      <c r="CC41" s="61"/>
-      <c r="CD41" s="61"/>
-      <c r="CE41" s="62"/>
-      <c r="CG41" s="60"/>
-      <c r="CH41" s="61"/>
-      <c r="CI41" s="61"/>
-      <c r="CJ41" s="61"/>
-      <c r="CK41" s="62"/>
+      <c r="CA41" s="63"/>
+      <c r="CB41" s="64"/>
+      <c r="CC41" s="64"/>
+      <c r="CD41" s="64"/>
+      <c r="CE41" s="65"/>
+      <c r="CG41" s="63"/>
+      <c r="CH41" s="64"/>
+      <c r="CI41" s="64"/>
+      <c r="CJ41" s="64"/>
+      <c r="CK41" s="65"/>
       <c r="CL41" s="13"/>
       <c r="CM41" s="13"/>
       <c r="CN41" s="2">
@@ -4592,42 +4574,42 @@
       <c r="W43" s="12"/>
       <c r="BD43" s="13"/>
       <c r="BF43" s="12"/>
-      <c r="BG43" s="57" t="s">
+      <c r="BG43" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="BH43" s="58"/>
-      <c r="BI43" s="58"/>
-      <c r="BJ43" s="58"/>
-      <c r="BK43" s="58"/>
-      <c r="BL43" s="58"/>
-      <c r="BM43" s="58"/>
-      <c r="BN43" s="58"/>
-      <c r="BO43" s="58"/>
-      <c r="BP43" s="58"/>
-      <c r="BQ43" s="58"/>
-      <c r="BR43" s="58"/>
-      <c r="BS43" s="58"/>
-      <c r="BT43" s="58"/>
-      <c r="BU43" s="58"/>
-      <c r="BV43" s="58"/>
-      <c r="BW43" s="58"/>
-      <c r="BX43" s="58"/>
-      <c r="BY43" s="59"/>
+      <c r="BH43" s="61"/>
+      <c r="BI43" s="61"/>
+      <c r="BJ43" s="61"/>
+      <c r="BK43" s="61"/>
+      <c r="BL43" s="61"/>
+      <c r="BM43" s="61"/>
+      <c r="BN43" s="61"/>
+      <c r="BO43" s="61"/>
+      <c r="BP43" s="61"/>
+      <c r="BQ43" s="61"/>
+      <c r="BR43" s="61"/>
+      <c r="BS43" s="61"/>
+      <c r="BT43" s="61"/>
+      <c r="BU43" s="61"/>
+      <c r="BV43" s="61"/>
+      <c r="BW43" s="61"/>
+      <c r="BX43" s="61"/>
+      <c r="BY43" s="62"/>
       <c r="BZ43" s="20"/>
-      <c r="CA43" s="57" t="s">
+      <c r="CA43" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="CB43" s="58"/>
-      <c r="CC43" s="58"/>
-      <c r="CD43" s="58"/>
-      <c r="CE43" s="59"/>
-      <c r="CG43" s="57" t="s">
+      <c r="CB43" s="61"/>
+      <c r="CC43" s="61"/>
+      <c r="CD43" s="61"/>
+      <c r="CE43" s="62"/>
+      <c r="CG43" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="CH43" s="58"/>
-      <c r="CI43" s="58"/>
-      <c r="CJ43" s="58"/>
-      <c r="CK43" s="59"/>
+      <c r="CH43" s="61"/>
+      <c r="CI43" s="61"/>
+      <c r="CJ43" s="61"/>
+      <c r="CK43" s="62"/>
       <c r="CL43" s="13"/>
       <c r="CM43" s="13"/>
       <c r="CN43" s="2">
@@ -4664,36 +4646,36 @@
       <c r="W44" s="12"/>
       <c r="BD44" s="13"/>
       <c r="BF44" s="12"/>
-      <c r="BG44" s="60"/>
-      <c r="BH44" s="61"/>
-      <c r="BI44" s="61"/>
-      <c r="BJ44" s="61"/>
-      <c r="BK44" s="61"/>
-      <c r="BL44" s="61"/>
-      <c r="BM44" s="61"/>
-      <c r="BN44" s="61"/>
-      <c r="BO44" s="61"/>
-      <c r="BP44" s="61"/>
-      <c r="BQ44" s="61"/>
-      <c r="BR44" s="61"/>
-      <c r="BS44" s="61"/>
-      <c r="BT44" s="61"/>
-      <c r="BU44" s="61"/>
-      <c r="BV44" s="61"/>
-      <c r="BW44" s="61"/>
-      <c r="BX44" s="61"/>
-      <c r="BY44" s="62"/>
+      <c r="BG44" s="63"/>
+      <c r="BH44" s="64"/>
+      <c r="BI44" s="64"/>
+      <c r="BJ44" s="64"/>
+      <c r="BK44" s="64"/>
+      <c r="BL44" s="64"/>
+      <c r="BM44" s="64"/>
+      <c r="BN44" s="64"/>
+      <c r="BO44" s="64"/>
+      <c r="BP44" s="64"/>
+      <c r="BQ44" s="64"/>
+      <c r="BR44" s="64"/>
+      <c r="BS44" s="64"/>
+      <c r="BT44" s="64"/>
+      <c r="BU44" s="64"/>
+      <c r="BV44" s="64"/>
+      <c r="BW44" s="64"/>
+      <c r="BX44" s="64"/>
+      <c r="BY44" s="65"/>
       <c r="BZ44" s="20"/>
-      <c r="CA44" s="60"/>
-      <c r="CB44" s="61"/>
-      <c r="CC44" s="61"/>
-      <c r="CD44" s="61"/>
-      <c r="CE44" s="62"/>
-      <c r="CG44" s="60"/>
-      <c r="CH44" s="61"/>
-      <c r="CI44" s="61"/>
-      <c r="CJ44" s="61"/>
-      <c r="CK44" s="62"/>
+      <c r="CA44" s="63"/>
+      <c r="CB44" s="64"/>
+      <c r="CC44" s="64"/>
+      <c r="CD44" s="64"/>
+      <c r="CE44" s="65"/>
+      <c r="CG44" s="63"/>
+      <c r="CH44" s="64"/>
+      <c r="CI44" s="64"/>
+      <c r="CJ44" s="64"/>
+      <c r="CK44" s="65"/>
       <c r="CL44" s="13"/>
       <c r="CM44" s="13"/>
       <c r="CN44" s="2">
@@ -4766,25 +4748,25 @@
       <c r="W46" s="12"/>
       <c r="BD46" s="13"/>
       <c r="BF46" s="12"/>
-      <c r="BG46" s="63" t="s">
+      <c r="BG46" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="BH46" s="64"/>
-      <c r="BI46" s="64"/>
-      <c r="BJ46" s="64"/>
-      <c r="BK46" s="64"/>
-      <c r="BL46" s="64"/>
-      <c r="BM46" s="64"/>
-      <c r="BN46" s="64"/>
-      <c r="BO46" s="64"/>
-      <c r="BP46" s="65"/>
-      <c r="CA46" s="57" t="s">
+      <c r="BH46" s="70"/>
+      <c r="BI46" s="70"/>
+      <c r="BJ46" s="70"/>
+      <c r="BK46" s="70"/>
+      <c r="BL46" s="70"/>
+      <c r="BM46" s="70"/>
+      <c r="BN46" s="70"/>
+      <c r="BO46" s="70"/>
+      <c r="BP46" s="71"/>
+      <c r="CA46" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="CB46" s="58"/>
-      <c r="CC46" s="58"/>
-      <c r="CD46" s="58"/>
-      <c r="CE46" s="59"/>
+      <c r="CB46" s="61"/>
+      <c r="CC46" s="61"/>
+      <c r="CD46" s="61"/>
+      <c r="CE46" s="62"/>
       <c r="CG46" s="20"/>
       <c r="CH46" s="20"/>
       <c r="CI46" s="20"/>
@@ -4826,21 +4808,21 @@
       <c r="W47" s="12"/>
       <c r="BD47" s="13"/>
       <c r="BF47" s="12"/>
-      <c r="BG47" s="66"/>
-      <c r="BH47" s="67"/>
-      <c r="BI47" s="67"/>
-      <c r="BJ47" s="67"/>
-      <c r="BK47" s="67"/>
-      <c r="BL47" s="67"/>
-      <c r="BM47" s="67"/>
-      <c r="BN47" s="67"/>
-      <c r="BO47" s="67"/>
-      <c r="BP47" s="68"/>
-      <c r="CA47" s="60"/>
-      <c r="CB47" s="61"/>
-      <c r="CC47" s="61"/>
-      <c r="CD47" s="61"/>
-      <c r="CE47" s="62"/>
+      <c r="BG47" s="72"/>
+      <c r="BH47" s="73"/>
+      <c r="BI47" s="73"/>
+      <c r="BJ47" s="73"/>
+      <c r="BK47" s="73"/>
+      <c r="BL47" s="73"/>
+      <c r="BM47" s="73"/>
+      <c r="BN47" s="73"/>
+      <c r="BO47" s="73"/>
+      <c r="BP47" s="74"/>
+      <c r="CA47" s="63"/>
+      <c r="CB47" s="64"/>
+      <c r="CC47" s="64"/>
+      <c r="CD47" s="64"/>
+      <c r="CE47" s="65"/>
       <c r="CG47" s="20"/>
       <c r="CH47" s="20"/>
       <c r="CI47" s="20"/>
@@ -5015,18 +4997,18 @@
       <c r="V50" s="12"/>
       <c r="W50" s="12"/>
       <c r="BD50" s="13"/>
-      <c r="BF50" s="63" t="s">
+      <c r="BF50" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="BG50" s="64"/>
-      <c r="BH50" s="64"/>
-      <c r="BI50" s="64"/>
-      <c r="BJ50" s="64"/>
-      <c r="BK50" s="64"/>
-      <c r="BL50" s="64"/>
-      <c r="BM50" s="64"/>
-      <c r="BN50" s="64"/>
-      <c r="BO50" s="65"/>
+      <c r="BG50" s="70"/>
+      <c r="BH50" s="70"/>
+      <c r="BI50" s="70"/>
+      <c r="BJ50" s="70"/>
+      <c r="BK50" s="70"/>
+      <c r="BL50" s="70"/>
+      <c r="BM50" s="70"/>
+      <c r="BN50" s="70"/>
+      <c r="BO50" s="71"/>
       <c r="BP50" s="20"/>
       <c r="BQ50" s="20"/>
       <c r="BR50" s="20"/>
@@ -5035,22 +5017,22 @@
       <c r="BU50" s="20"/>
       <c r="BY50" s="20"/>
       <c r="BZ50" s="20"/>
-      <c r="CA50" s="57" t="s">
+      <c r="CA50" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="CB50" s="58"/>
-      <c r="CC50" s="58"/>
-      <c r="CD50" s="58"/>
-      <c r="CE50" s="58"/>
-      <c r="CF50" s="58"/>
-      <c r="CG50" s="59"/>
-      <c r="CH50" s="57" t="s">
+      <c r="CB50" s="61"/>
+      <c r="CC50" s="61"/>
+      <c r="CD50" s="61"/>
+      <c r="CE50" s="61"/>
+      <c r="CF50" s="61"/>
+      <c r="CG50" s="62"/>
+      <c r="CH50" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="CI50" s="58"/>
-      <c r="CJ50" s="58"/>
-      <c r="CK50" s="58"/>
-      <c r="CL50" s="59"/>
+      <c r="CI50" s="61"/>
+      <c r="CJ50" s="61"/>
+      <c r="CK50" s="61"/>
+      <c r="CL50" s="62"/>
       <c r="CM50" s="13"/>
       <c r="CN50" s="2">
         <f t="shared" si="7"/>
@@ -5085,16 +5067,16 @@
       <c r="V51" s="12"/>
       <c r="W51" s="12"/>
       <c r="BD51" s="13"/>
-      <c r="BF51" s="66"/>
-      <c r="BG51" s="67"/>
-      <c r="BH51" s="67"/>
-      <c r="BI51" s="67"/>
-      <c r="BJ51" s="67"/>
-      <c r="BK51" s="67"/>
-      <c r="BL51" s="67"/>
-      <c r="BM51" s="67"/>
-      <c r="BN51" s="67"/>
-      <c r="BO51" s="68"/>
+      <c r="BF51" s="72"/>
+      <c r="BG51" s="73"/>
+      <c r="BH51" s="73"/>
+      <c r="BI51" s="73"/>
+      <c r="BJ51" s="73"/>
+      <c r="BK51" s="73"/>
+      <c r="BL51" s="73"/>
+      <c r="BM51" s="73"/>
+      <c r="BN51" s="73"/>
+      <c r="BO51" s="74"/>
       <c r="BP51" s="20"/>
       <c r="BQ51" s="20"/>
       <c r="BR51" s="20"/>
@@ -5103,18 +5085,18 @@
       <c r="BU51" s="20"/>
       <c r="BY51" s="20"/>
       <c r="BZ51" s="20"/>
-      <c r="CA51" s="60"/>
-      <c r="CB51" s="61"/>
-      <c r="CC51" s="61"/>
-      <c r="CD51" s="61"/>
-      <c r="CE51" s="61"/>
-      <c r="CF51" s="61"/>
-      <c r="CG51" s="62"/>
-      <c r="CH51" s="60"/>
-      <c r="CI51" s="61"/>
-      <c r="CJ51" s="61"/>
-      <c r="CK51" s="61"/>
-      <c r="CL51" s="62"/>
+      <c r="CA51" s="63"/>
+      <c r="CB51" s="64"/>
+      <c r="CC51" s="64"/>
+      <c r="CD51" s="64"/>
+      <c r="CE51" s="64"/>
+      <c r="CF51" s="64"/>
+      <c r="CG51" s="65"/>
+      <c r="CH51" s="63"/>
+      <c r="CI51" s="64"/>
+      <c r="CJ51" s="64"/>
+      <c r="CK51" s="64"/>
+      <c r="CL51" s="65"/>
       <c r="CM51" s="13"/>
       <c r="CN51" s="2">
         <f t="shared" si="7"/>
@@ -5252,13 +5234,13 @@
       <c r="BD54" s="13"/>
       <c r="BF54" s="12"/>
       <c r="CE54" s="11"/>
-      <c r="CG54" s="57" t="s">
+      <c r="CG54" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="CH54" s="58"/>
-      <c r="CI54" s="58"/>
-      <c r="CJ54" s="58"/>
-      <c r="CK54" s="59"/>
+      <c r="CH54" s="61"/>
+      <c r="CI54" s="61"/>
+      <c r="CJ54" s="61"/>
+      <c r="CK54" s="62"/>
       <c r="CL54" s="13"/>
       <c r="CM54" s="13"/>
       <c r="CN54" s="2">
@@ -5296,11 +5278,11 @@
       <c r="BD55" s="13"/>
       <c r="BF55" s="12"/>
       <c r="CE55" s="11"/>
-      <c r="CG55" s="60"/>
-      <c r="CH55" s="61"/>
-      <c r="CI55" s="61"/>
-      <c r="CJ55" s="61"/>
-      <c r="CK55" s="62"/>
+      <c r="CG55" s="63"/>
+      <c r="CH55" s="64"/>
+      <c r="CI55" s="64"/>
+      <c r="CJ55" s="64"/>
+      <c r="CK55" s="65"/>
       <c r="CL55" s="13"/>
       <c r="CM55" s="13"/>
       <c r="CN55" s="2">
@@ -5375,13 +5357,13 @@
       <c r="BD57" s="13"/>
       <c r="BF57" s="12"/>
       <c r="CE57" s="11"/>
-      <c r="CG57" s="57" t="s">
+      <c r="CG57" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="CH57" s="58"/>
-      <c r="CI57" s="58"/>
-      <c r="CJ57" s="58"/>
-      <c r="CK57" s="59"/>
+      <c r="CH57" s="61"/>
+      <c r="CI57" s="61"/>
+      <c r="CJ57" s="61"/>
+      <c r="CK57" s="62"/>
       <c r="CL57" s="13"/>
       <c r="CM57" s="13"/>
       <c r="CN57" s="2">
@@ -5419,11 +5401,11 @@
       <c r="BD58" s="13"/>
       <c r="BF58" s="12"/>
       <c r="CE58" s="11"/>
-      <c r="CG58" s="60"/>
-      <c r="CH58" s="61"/>
-      <c r="CI58" s="61"/>
-      <c r="CJ58" s="61"/>
-      <c r="CK58" s="62"/>
+      <c r="CG58" s="63"/>
+      <c r="CH58" s="64"/>
+      <c r="CI58" s="64"/>
+      <c r="CJ58" s="64"/>
+      <c r="CK58" s="65"/>
       <c r="CL58" s="13"/>
       <c r="CM58" s="13"/>
       <c r="CN58" s="2">
@@ -5498,13 +5480,13 @@
       <c r="BD60" s="13"/>
       <c r="BF60" s="12"/>
       <c r="CE60" s="11"/>
-      <c r="CG60" s="57" t="s">
+      <c r="CG60" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="CH60" s="58"/>
-      <c r="CI60" s="58"/>
-      <c r="CJ60" s="58"/>
-      <c r="CK60" s="59"/>
+      <c r="CH60" s="61"/>
+      <c r="CI60" s="61"/>
+      <c r="CJ60" s="61"/>
+      <c r="CK60" s="62"/>
       <c r="CL60" s="13"/>
       <c r="CM60" s="13"/>
       <c r="CN60" s="2">
@@ -5542,11 +5524,11 @@
       <c r="BD61" s="13"/>
       <c r="BF61" s="12"/>
       <c r="CE61" s="11"/>
-      <c r="CG61" s="60"/>
-      <c r="CH61" s="61"/>
-      <c r="CI61" s="61"/>
-      <c r="CJ61" s="61"/>
-      <c r="CK61" s="62"/>
+      <c r="CG61" s="63"/>
+      <c r="CH61" s="64"/>
+      <c r="CI61" s="64"/>
+      <c r="CJ61" s="64"/>
+      <c r="CK61" s="65"/>
       <c r="CL61" s="13"/>
       <c r="CM61" s="13"/>
       <c r="CN61" s="2">
@@ -5621,13 +5603,13 @@
       <c r="BD63" s="13"/>
       <c r="BF63" s="12"/>
       <c r="CE63" s="11"/>
-      <c r="CG63" s="57" t="s">
+      <c r="CG63" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="CH63" s="58"/>
-      <c r="CI63" s="58"/>
-      <c r="CJ63" s="58"/>
-      <c r="CK63" s="59"/>
+      <c r="CH63" s="61"/>
+      <c r="CI63" s="61"/>
+      <c r="CJ63" s="61"/>
+      <c r="CK63" s="62"/>
       <c r="CL63" s="13"/>
       <c r="CM63" s="13"/>
       <c r="CN63" s="2">
@@ -5665,11 +5647,11 @@
       <c r="BD64" s="13"/>
       <c r="BF64" s="12"/>
       <c r="CE64" s="11"/>
-      <c r="CG64" s="60"/>
-      <c r="CH64" s="61"/>
-      <c r="CI64" s="61"/>
-      <c r="CJ64" s="61"/>
-      <c r="CK64" s="62"/>
+      <c r="CG64" s="63"/>
+      <c r="CH64" s="64"/>
+      <c r="CI64" s="64"/>
+      <c r="CJ64" s="64"/>
+      <c r="CK64" s="65"/>
       <c r="CL64" s="13"/>
       <c r="CM64" s="13"/>
       <c r="CN64" s="2">
@@ -5744,13 +5726,13 @@
       <c r="BD66" s="13"/>
       <c r="BF66" s="12"/>
       <c r="CE66" s="11"/>
-      <c r="CG66" s="57" t="s">
+      <c r="CG66" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="CH66" s="58"/>
-      <c r="CI66" s="58"/>
-      <c r="CJ66" s="58"/>
-      <c r="CK66" s="59"/>
+      <c r="CH66" s="61"/>
+      <c r="CI66" s="61"/>
+      <c r="CJ66" s="61"/>
+      <c r="CK66" s="62"/>
       <c r="CL66" s="13"/>
       <c r="CM66" s="13"/>
       <c r="CN66" s="2">
@@ -5788,11 +5770,11 @@
       <c r="BD67" s="13"/>
       <c r="BF67" s="12"/>
       <c r="CE67" s="11"/>
-      <c r="CG67" s="60"/>
-      <c r="CH67" s="61"/>
-      <c r="CI67" s="61"/>
-      <c r="CJ67" s="61"/>
-      <c r="CK67" s="62"/>
+      <c r="CG67" s="63"/>
+      <c r="CH67" s="64"/>
+      <c r="CI67" s="64"/>
+      <c r="CJ67" s="64"/>
+      <c r="CK67" s="65"/>
       <c r="CL67" s="13"/>
       <c r="CM67" s="13"/>
       <c r="CN67" s="2">
@@ -6697,14 +6679,14 @@
         <v>83</v>
       </c>
       <c r="V90" s="12"/>
-      <c r="W90" s="57" t="s">
+      <c r="W90" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="X90" s="58"/>
-      <c r="Y90" s="58"/>
-      <c r="Z90" s="58"/>
-      <c r="AA90" s="58"/>
-      <c r="AB90" s="59"/>
+      <c r="X90" s="61"/>
+      <c r="Y90" s="61"/>
+      <c r="Z90" s="61"/>
+      <c r="AA90" s="61"/>
+      <c r="AB90" s="62"/>
       <c r="CM90" s="13"/>
       <c r="CN90" s="2">
         <f t="shared" si="11"/>
@@ -6737,12 +6719,12 @@
         <v>84</v>
       </c>
       <c r="V91" s="12"/>
-      <c r="W91" s="60"/>
-      <c r="X91" s="61"/>
-      <c r="Y91" s="61"/>
-      <c r="Z91" s="61"/>
-      <c r="AA91" s="61"/>
-      <c r="AB91" s="62"/>
+      <c r="W91" s="63"/>
+      <c r="X91" s="64"/>
+      <c r="Y91" s="64"/>
+      <c r="Z91" s="64"/>
+      <c r="AA91" s="64"/>
+      <c r="AB91" s="65"/>
       <c r="AZ91" s="20"/>
       <c r="BA91" s="20"/>
       <c r="BB91" s="20"/>
@@ -6753,18 +6735,18 @@
       <c r="BG91" s="20"/>
       <c r="BH91" s="20"/>
       <c r="BI91" s="20"/>
-      <c r="CC91" s="57" t="s">
+      <c r="CC91" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="CD91" s="58"/>
-      <c r="CE91" s="58"/>
-      <c r="CF91" s="58"/>
-      <c r="CG91" s="58"/>
-      <c r="CH91" s="58"/>
-      <c r="CI91" s="58"/>
-      <c r="CJ91" s="58"/>
-      <c r="CK91" s="58"/>
-      <c r="CL91" s="59"/>
+      <c r="CD91" s="61"/>
+      <c r="CE91" s="61"/>
+      <c r="CF91" s="61"/>
+      <c r="CG91" s="61"/>
+      <c r="CH91" s="61"/>
+      <c r="CI91" s="61"/>
+      <c r="CJ91" s="61"/>
+      <c r="CK91" s="61"/>
+      <c r="CL91" s="62"/>
       <c r="CM91" s="13"/>
       <c r="CN91" s="2">
         <f t="shared" si="11"/>
@@ -6807,16 +6789,16 @@
       <c r="BG92" s="20"/>
       <c r="BH92" s="20"/>
       <c r="BI92" s="20"/>
-      <c r="CC92" s="69"/>
-      <c r="CD92" s="70"/>
-      <c r="CE92" s="70"/>
-      <c r="CF92" s="70"/>
-      <c r="CG92" s="70"/>
-      <c r="CH92" s="70"/>
-      <c r="CI92" s="70"/>
-      <c r="CJ92" s="70"/>
-      <c r="CK92" s="70"/>
-      <c r="CL92" s="71"/>
+      <c r="CC92" s="66"/>
+      <c r="CD92" s="67"/>
+      <c r="CE92" s="67"/>
+      <c r="CF92" s="67"/>
+      <c r="CG92" s="67"/>
+      <c r="CH92" s="67"/>
+      <c r="CI92" s="67"/>
+      <c r="CJ92" s="67"/>
+      <c r="CK92" s="67"/>
+      <c r="CL92" s="68"/>
       <c r="CM92" s="13"/>
       <c r="CN92" s="2">
         <f t="shared" si="11"/>
@@ -6859,16 +6841,16 @@
       <c r="BG93" s="20"/>
       <c r="BH93" s="20"/>
       <c r="BI93" s="20"/>
-      <c r="CC93" s="69"/>
-      <c r="CD93" s="70"/>
-      <c r="CE93" s="70"/>
-      <c r="CF93" s="70"/>
-      <c r="CG93" s="70"/>
-      <c r="CH93" s="70"/>
-      <c r="CI93" s="70"/>
-      <c r="CJ93" s="70"/>
-      <c r="CK93" s="70"/>
-      <c r="CL93" s="71"/>
+      <c r="CC93" s="66"/>
+      <c r="CD93" s="67"/>
+      <c r="CE93" s="67"/>
+      <c r="CF93" s="67"/>
+      <c r="CG93" s="67"/>
+      <c r="CH93" s="67"/>
+      <c r="CI93" s="67"/>
+      <c r="CJ93" s="67"/>
+      <c r="CK93" s="67"/>
+      <c r="CL93" s="68"/>
       <c r="CM93" s="13"/>
       <c r="CN93" s="2">
         <f t="shared" si="11"/>
@@ -6911,16 +6893,16 @@
       <c r="BG94" s="20"/>
       <c r="BH94" s="20"/>
       <c r="BI94" s="20"/>
-      <c r="CC94" s="60"/>
-      <c r="CD94" s="61"/>
-      <c r="CE94" s="61"/>
-      <c r="CF94" s="61"/>
-      <c r="CG94" s="61"/>
-      <c r="CH94" s="61"/>
-      <c r="CI94" s="61"/>
-      <c r="CJ94" s="61"/>
-      <c r="CK94" s="61"/>
-      <c r="CL94" s="62"/>
+      <c r="CC94" s="63"/>
+      <c r="CD94" s="64"/>
+      <c r="CE94" s="64"/>
+      <c r="CF94" s="64"/>
+      <c r="CG94" s="64"/>
+      <c r="CH94" s="64"/>
+      <c r="CI94" s="64"/>
+      <c r="CJ94" s="64"/>
+      <c r="CK94" s="64"/>
+      <c r="CL94" s="65"/>
       <c r="CM94" s="13"/>
       <c r="CN94" s="2">
         <f t="shared" si="11"/>
@@ -8649,40 +8631,6 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="W90:AB91"/>
-    <mergeCell ref="BY31:CK33"/>
-    <mergeCell ref="CC91:CL94"/>
-    <mergeCell ref="CA40:CE41"/>
-    <mergeCell ref="CA43:CE44"/>
-    <mergeCell ref="CA46:CE47"/>
-    <mergeCell ref="CG40:CK41"/>
-    <mergeCell ref="CG43:CK44"/>
-    <mergeCell ref="CG66:CK67"/>
-    <mergeCell ref="CH50:CL51"/>
-    <mergeCell ref="CG54:CK55"/>
-    <mergeCell ref="CG57:CK58"/>
-    <mergeCell ref="CG60:CK61"/>
-    <mergeCell ref="CG63:CK64"/>
-    <mergeCell ref="AP25:BU26"/>
-    <mergeCell ref="AP28:AY29"/>
-    <mergeCell ref="BG46:BP47"/>
-    <mergeCell ref="BG40:BY41"/>
-    <mergeCell ref="BG43:BY44"/>
-    <mergeCell ref="AT36:AV37"/>
-    <mergeCell ref="AP36:AQ37"/>
-    <mergeCell ref="BY22:CB23"/>
-    <mergeCell ref="CJ22:CK23"/>
-    <mergeCell ref="CF22:CG23"/>
-    <mergeCell ref="BY28:CD29"/>
-    <mergeCell ref="CF28:CK29"/>
-    <mergeCell ref="X22:AA23"/>
-    <mergeCell ref="AB22:AL23"/>
-    <mergeCell ref="X25:AA26"/>
-    <mergeCell ref="X28:AA29"/>
-    <mergeCell ref="X31:AA32"/>
-    <mergeCell ref="AB25:AL26"/>
-    <mergeCell ref="AB28:AL29"/>
-    <mergeCell ref="AB31:AL32"/>
     <mergeCell ref="BR18:BV19"/>
     <mergeCell ref="BL18:BQ19"/>
     <mergeCell ref="CA50:CG51"/>
@@ -8699,6 +8647,40 @@
     <mergeCell ref="AV31:BA32"/>
     <mergeCell ref="AH36:AJ37"/>
     <mergeCell ref="AK36:AN37"/>
+    <mergeCell ref="X22:AA23"/>
+    <mergeCell ref="AB22:AL23"/>
+    <mergeCell ref="X25:AA26"/>
+    <mergeCell ref="X28:AA29"/>
+    <mergeCell ref="X31:AA32"/>
+    <mergeCell ref="AB25:AL26"/>
+    <mergeCell ref="AB28:AL29"/>
+    <mergeCell ref="AB31:AL32"/>
+    <mergeCell ref="BY22:CB23"/>
+    <mergeCell ref="CJ22:CK23"/>
+    <mergeCell ref="CF22:CG23"/>
+    <mergeCell ref="BY28:CD29"/>
+    <mergeCell ref="CF28:CK29"/>
+    <mergeCell ref="AP25:BU26"/>
+    <mergeCell ref="AP28:AY29"/>
+    <mergeCell ref="BG46:BP47"/>
+    <mergeCell ref="BG40:BY41"/>
+    <mergeCell ref="BG43:BY44"/>
+    <mergeCell ref="AT36:AV37"/>
+    <mergeCell ref="AP36:AQ37"/>
+    <mergeCell ref="W90:AB91"/>
+    <mergeCell ref="BY31:CK33"/>
+    <mergeCell ref="CC91:CL94"/>
+    <mergeCell ref="CA40:CE41"/>
+    <mergeCell ref="CA43:CE44"/>
+    <mergeCell ref="CA46:CE47"/>
+    <mergeCell ref="CG40:CK41"/>
+    <mergeCell ref="CG43:CK44"/>
+    <mergeCell ref="CG66:CK67"/>
+    <mergeCell ref="CH50:CL51"/>
+    <mergeCell ref="CG54:CK55"/>
+    <mergeCell ref="CG57:CK58"/>
+    <mergeCell ref="CG60:CK61"/>
+    <mergeCell ref="CG63:CK64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12527,7 +12509,7 @@
         <f t="shared" si="106"/>
         <v>60</v>
       </c>
-      <c r="FX16" s="75">
+      <c r="FX16" s="2">
         <f t="shared" si="106"/>
         <v>61</v>
       </c>
@@ -12797,7 +12779,7 @@
       <c r="EX17" s="33"/>
       <c r="EY17" s="33"/>
       <c r="EZ17" s="33"/>
-      <c r="FA17" s="72"/>
+      <c r="FA17" s="9"/>
       <c r="FB17" s="33"/>
       <c r="FC17" s="33"/>
       <c r="FD17" s="33"/>
@@ -12820,7 +12802,7 @@
       <c r="FU17" s="33"/>
       <c r="FV17" s="33"/>
       <c r="FW17" s="33"/>
-      <c r="FX17" s="72"/>
+      <c r="FX17" s="9"/>
       <c r="FY17" s="33"/>
       <c r="FZ17" s="33"/>
       <c r="GA17" s="33"/>
@@ -12888,18 +12870,18 @@
         <v>11</v>
       </c>
       <c r="V18" s="12"/>
-      <c r="W18" s="63" t="s">
+      <c r="W18" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="X18" s="64"/>
-      <c r="Y18" s="64"/>
-      <c r="Z18" s="64"/>
-      <c r="AA18" s="64"/>
-      <c r="AB18" s="64"/>
-      <c r="AC18" s="64"/>
-      <c r="AD18" s="64"/>
-      <c r="AE18" s="64"/>
-      <c r="AF18" s="65"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="70"/>
+      <c r="AA18" s="70"/>
+      <c r="AB18" s="70"/>
+      <c r="AC18" s="70"/>
+      <c r="AD18" s="70"/>
+      <c r="AE18" s="70"/>
+      <c r="AF18" s="71"/>
       <c r="AG18" s="20"/>
       <c r="AH18" s="20"/>
       <c r="AI18" s="20"/>
@@ -12907,18 +12889,18 @@
       <c r="AK18" s="20"/>
       <c r="AL18" s="20"/>
       <c r="AM18" s="20"/>
-      <c r="AO18" s="63" t="s">
+      <c r="AO18" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="AP18" s="64"/>
-      <c r="AQ18" s="64"/>
-      <c r="AR18" s="64"/>
-      <c r="AS18" s="64"/>
-      <c r="AT18" s="64"/>
-      <c r="AU18" s="64"/>
-      <c r="AV18" s="64"/>
-      <c r="AW18" s="64"/>
-      <c r="AX18" s="65"/>
+      <c r="AP18" s="70"/>
+      <c r="AQ18" s="70"/>
+      <c r="AR18" s="70"/>
+      <c r="AS18" s="70"/>
+      <c r="AT18" s="70"/>
+      <c r="AU18" s="70"/>
+      <c r="AV18" s="70"/>
+      <c r="AW18" s="70"/>
+      <c r="AX18" s="71"/>
       <c r="AY18" s="20"/>
       <c r="AZ18" s="20"/>
       <c r="BA18" s="20"/>
@@ -12929,33 +12911,33 @@
       <c r="BF18" s="20"/>
       <c r="BG18" s="20"/>
       <c r="BK18" s="20"/>
-      <c r="BL18" s="57" t="s">
+      <c r="BL18" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="BM18" s="58"/>
-      <c r="BN18" s="58"/>
-      <c r="BO18" s="58"/>
-      <c r="BP18" s="58"/>
-      <c r="BQ18" s="59"/>
-      <c r="BR18" s="57" t="s">
+      <c r="BM18" s="61"/>
+      <c r="BN18" s="61"/>
+      <c r="BO18" s="61"/>
+      <c r="BP18" s="61"/>
+      <c r="BQ18" s="62"/>
+      <c r="BR18" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="BS18" s="58"/>
-      <c r="BT18" s="58"/>
-      <c r="BU18" s="58"/>
-      <c r="BV18" s="59"/>
-      <c r="BX18" s="63" t="s">
+      <c r="BS18" s="61"/>
+      <c r="BT18" s="61"/>
+      <c r="BU18" s="61"/>
+      <c r="BV18" s="62"/>
+      <c r="BX18" s="69" t="s">
         <v>4</v>
       </c>
-      <c r="BY18" s="64"/>
-      <c r="BZ18" s="64"/>
-      <c r="CA18" s="64"/>
-      <c r="CB18" s="64"/>
-      <c r="CC18" s="64"/>
-      <c r="CD18" s="64"/>
-      <c r="CE18" s="64"/>
-      <c r="CF18" s="64"/>
-      <c r="CG18" s="65"/>
+      <c r="BY18" s="70"/>
+      <c r="BZ18" s="70"/>
+      <c r="CA18" s="70"/>
+      <c r="CB18" s="70"/>
+      <c r="CC18" s="70"/>
+      <c r="CD18" s="70"/>
+      <c r="CE18" s="70"/>
+      <c r="CF18" s="70"/>
+      <c r="CG18" s="71"/>
       <c r="CH18" s="20"/>
       <c r="CI18" s="20"/>
       <c r="CJ18" s="20"/>
@@ -13030,7 +13012,7 @@
       <c r="EX18" s="50"/>
       <c r="EY18" s="50"/>
       <c r="EZ18" s="50"/>
-      <c r="FA18" s="73"/>
+      <c r="FA18" s="57"/>
       <c r="FB18" s="50"/>
       <c r="FC18" s="50"/>
       <c r="FD18" s="50"/>
@@ -13055,7 +13037,7 @@
       <c r="FU18" s="50"/>
       <c r="FV18" s="50"/>
       <c r="FW18" s="50"/>
-      <c r="FX18" s="73"/>
+      <c r="FX18" s="57"/>
       <c r="FY18" s="51"/>
       <c r="FZ18" s="49" t="s">
         <v>32</v>
@@ -13127,16 +13109,16 @@
         <v>12</v>
       </c>
       <c r="V19" s="12"/>
-      <c r="W19" s="66"/>
-      <c r="X19" s="67"/>
-      <c r="Y19" s="67"/>
-      <c r="Z19" s="67"/>
-      <c r="AA19" s="67"/>
-      <c r="AB19" s="67"/>
-      <c r="AC19" s="67"/>
-      <c r="AD19" s="67"/>
-      <c r="AE19" s="67"/>
-      <c r="AF19" s="68"/>
+      <c r="W19" s="72"/>
+      <c r="X19" s="73"/>
+      <c r="Y19" s="73"/>
+      <c r="Z19" s="73"/>
+      <c r="AA19" s="73"/>
+      <c r="AB19" s="73"/>
+      <c r="AC19" s="73"/>
+      <c r="AD19" s="73"/>
+      <c r="AE19" s="73"/>
+      <c r="AF19" s="74"/>
       <c r="AG19" s="20"/>
       <c r="AH19" s="20"/>
       <c r="AI19" s="20"/>
@@ -13144,16 +13126,16 @@
       <c r="AK19" s="20"/>
       <c r="AL19" s="20"/>
       <c r="AM19" s="20"/>
-      <c r="AO19" s="66"/>
-      <c r="AP19" s="67"/>
-      <c r="AQ19" s="67"/>
-      <c r="AR19" s="67"/>
-      <c r="AS19" s="67"/>
-      <c r="AT19" s="67"/>
-      <c r="AU19" s="67"/>
-      <c r="AV19" s="67"/>
-      <c r="AW19" s="67"/>
-      <c r="AX19" s="68"/>
+      <c r="AO19" s="72"/>
+      <c r="AP19" s="73"/>
+      <c r="AQ19" s="73"/>
+      <c r="AR19" s="73"/>
+      <c r="AS19" s="73"/>
+      <c r="AT19" s="73"/>
+      <c r="AU19" s="73"/>
+      <c r="AV19" s="73"/>
+      <c r="AW19" s="73"/>
+      <c r="AX19" s="74"/>
       <c r="AY19" s="20"/>
       <c r="AZ19" s="20"/>
       <c r="BA19" s="20"/>
@@ -13164,27 +13146,27 @@
       <c r="BF19" s="20"/>
       <c r="BG19" s="20"/>
       <c r="BK19" s="20"/>
-      <c r="BL19" s="60"/>
-      <c r="BM19" s="61"/>
-      <c r="BN19" s="61"/>
-      <c r="BO19" s="61"/>
-      <c r="BP19" s="61"/>
-      <c r="BQ19" s="62"/>
-      <c r="BR19" s="60"/>
-      <c r="BS19" s="61"/>
-      <c r="BT19" s="61"/>
-      <c r="BU19" s="61"/>
-      <c r="BV19" s="62"/>
-      <c r="BX19" s="66"/>
-      <c r="BY19" s="67"/>
-      <c r="BZ19" s="67"/>
-      <c r="CA19" s="67"/>
-      <c r="CB19" s="67"/>
-      <c r="CC19" s="67"/>
-      <c r="CD19" s="67"/>
-      <c r="CE19" s="67"/>
-      <c r="CF19" s="67"/>
-      <c r="CG19" s="68"/>
+      <c r="BL19" s="63"/>
+      <c r="BM19" s="64"/>
+      <c r="BN19" s="64"/>
+      <c r="BO19" s="64"/>
+      <c r="BP19" s="64"/>
+      <c r="BQ19" s="65"/>
+      <c r="BR19" s="63"/>
+      <c r="BS19" s="64"/>
+      <c r="BT19" s="64"/>
+      <c r="BU19" s="64"/>
+      <c r="BV19" s="65"/>
+      <c r="BX19" s="72"/>
+      <c r="BY19" s="73"/>
+      <c r="BZ19" s="73"/>
+      <c r="CA19" s="73"/>
+      <c r="CB19" s="73"/>
+      <c r="CC19" s="73"/>
+      <c r="CD19" s="73"/>
+      <c r="CE19" s="73"/>
+      <c r="CF19" s="73"/>
+      <c r="CG19" s="74"/>
       <c r="CH19" s="20"/>
       <c r="CI19" s="20"/>
       <c r="CJ19" s="20"/>
@@ -13255,7 +13237,7 @@
       <c r="EX19" s="53"/>
       <c r="EY19" s="53"/>
       <c r="EZ19" s="53"/>
-      <c r="FA19" s="74"/>
+      <c r="FA19" s="58"/>
       <c r="FB19" s="53"/>
       <c r="FC19" s="53"/>
       <c r="FD19" s="53"/>
@@ -13278,7 +13260,7 @@
       <c r="FU19" s="53"/>
       <c r="FV19" s="53"/>
       <c r="FW19" s="53"/>
-      <c r="FX19" s="74"/>
+      <c r="FX19" s="58"/>
       <c r="FY19" s="54"/>
       <c r="FZ19" s="52"/>
       <c r="GA19" s="53"/>
@@ -13411,7 +13393,6 @@
       <c r="EX20" s="37"/>
       <c r="EY20" s="37"/>
       <c r="EZ20" s="37"/>
-      <c r="FA20" s="75"/>
       <c r="FB20" s="37"/>
       <c r="FC20" s="37"/>
       <c r="FD20" s="37"/>
@@ -13434,7 +13415,6 @@
       <c r="FU20" s="37"/>
       <c r="FV20" s="37"/>
       <c r="FW20" s="37"/>
-      <c r="FX20" s="75"/>
       <c r="FY20" s="37"/>
       <c r="FZ20" s="37"/>
       <c r="GA20" s="37"/>
@@ -13633,7 +13613,7 @@
       <c r="EX21" s="33"/>
       <c r="EY21" s="33"/>
       <c r="EZ21" s="33"/>
-      <c r="FA21" s="72"/>
+      <c r="FA21" s="9"/>
       <c r="FB21" s="33"/>
       <c r="FC21" s="33"/>
       <c r="FD21" s="33"/>
@@ -13656,7 +13636,7 @@
       <c r="FU21" s="33"/>
       <c r="FV21" s="33"/>
       <c r="FW21" s="33"/>
-      <c r="FX21" s="72"/>
+      <c r="FX21" s="9"/>
       <c r="FY21" s="33"/>
       <c r="FZ21" s="33"/>
       <c r="GA21" s="33"/>
@@ -13725,64 +13705,64 @@
       </c>
       <c r="V22" s="12"/>
       <c r="W22" s="12"/>
-      <c r="X22" s="63" t="s">
+      <c r="X22" s="69" t="s">
         <v>12</v>
       </c>
-      <c r="Y22" s="64"/>
-      <c r="Z22" s="64"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="63" t="s">
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="70"/>
+      <c r="AA22" s="71"/>
+      <c r="AB22" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AC22" s="64"/>
-      <c r="AD22" s="64"/>
-      <c r="AE22" s="64"/>
-      <c r="AF22" s="64"/>
-      <c r="AG22" s="64"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="64"/>
-      <c r="AK22" s="64"/>
-      <c r="AL22" s="65"/>
+      <c r="AC22" s="70"/>
+      <c r="AD22" s="70"/>
+      <c r="AE22" s="70"/>
+      <c r="AF22" s="70"/>
+      <c r="AG22" s="70"/>
+      <c r="AH22" s="70"/>
+      <c r="AI22" s="70"/>
+      <c r="AJ22" s="70"/>
+      <c r="AK22" s="70"/>
+      <c r="AL22" s="71"/>
       <c r="AM22" s="13"/>
       <c r="AO22" s="12"/>
-      <c r="AP22" s="63" t="s">
+      <c r="AP22" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="AQ22" s="64"/>
-      <c r="AR22" s="64"/>
-      <c r="AS22" s="64"/>
-      <c r="AT22" s="64"/>
-      <c r="AU22" s="64"/>
-      <c r="AV22" s="64"/>
-      <c r="AW22" s="64"/>
-      <c r="AX22" s="64"/>
-      <c r="AY22" s="64"/>
-      <c r="AZ22" s="64"/>
-      <c r="BA22" s="64"/>
-      <c r="BB22" s="64"/>
-      <c r="BC22" s="64"/>
-      <c r="BD22" s="64"/>
-      <c r="BE22" s="64"/>
-      <c r="BF22" s="64"/>
-      <c r="BG22" s="64"/>
-      <c r="BH22" s="65"/>
+      <c r="AQ22" s="70"/>
+      <c r="AR22" s="70"/>
+      <c r="AS22" s="70"/>
+      <c r="AT22" s="70"/>
+      <c r="AU22" s="70"/>
+      <c r="AV22" s="70"/>
+      <c r="AW22" s="70"/>
+      <c r="AX22" s="70"/>
+      <c r="AY22" s="70"/>
+      <c r="AZ22" s="70"/>
+      <c r="BA22" s="70"/>
+      <c r="BB22" s="70"/>
+      <c r="BC22" s="70"/>
+      <c r="BD22" s="70"/>
+      <c r="BE22" s="70"/>
+      <c r="BF22" s="70"/>
+      <c r="BG22" s="70"/>
+      <c r="BH22" s="71"/>
       <c r="BV22" s="13"/>
       <c r="BX22" s="12"/>
-      <c r="BY22" s="63" t="s">
+      <c r="BY22" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="BZ22" s="64"/>
-      <c r="CA22" s="64"/>
-      <c r="CB22" s="65"/>
-      <c r="CF22" s="57" t="s">
+      <c r="BZ22" s="70"/>
+      <c r="CA22" s="70"/>
+      <c r="CB22" s="71"/>
+      <c r="CF22" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="CG22" s="59"/>
-      <c r="CJ22" s="57" t="s">
+      <c r="CG22" s="62"/>
+      <c r="CJ22" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="CK22" s="59"/>
+      <c r="CK22" s="62"/>
       <c r="CL22" s="13"/>
       <c r="CM22" s="13"/>
       <c r="CN22" s="2">
@@ -13855,7 +13835,7 @@
       </c>
       <c r="EY22" s="50"/>
       <c r="EZ22" s="50"/>
-      <c r="FA22" s="73"/>
+      <c r="FA22" s="57"/>
       <c r="FB22" s="50"/>
       <c r="FC22" s="50"/>
       <c r="FD22" s="50"/>
@@ -13878,7 +13858,6 @@
       <c r="FU22" s="37"/>
       <c r="FV22" s="37"/>
       <c r="FW22" s="37"/>
-      <c r="FX22" s="75"/>
       <c r="FY22" s="37"/>
       <c r="FZ22" s="37"/>
       <c r="GA22" s="37"/>
@@ -13953,52 +13932,52 @@
       </c>
       <c r="V23" s="12"/>
       <c r="W23" s="12"/>
-      <c r="X23" s="66"/>
-      <c r="Y23" s="67"/>
-      <c r="Z23" s="67"/>
-      <c r="AA23" s="68"/>
-      <c r="AB23" s="66"/>
-      <c r="AC23" s="67"/>
-      <c r="AD23" s="67"/>
-      <c r="AE23" s="67"/>
-      <c r="AF23" s="67"/>
-      <c r="AG23" s="67"/>
-      <c r="AH23" s="67"/>
-      <c r="AI23" s="67"/>
-      <c r="AJ23" s="67"/>
-      <c r="AK23" s="67"/>
-      <c r="AL23" s="68"/>
+      <c r="X23" s="72"/>
+      <c r="Y23" s="73"/>
+      <c r="Z23" s="73"/>
+      <c r="AA23" s="74"/>
+      <c r="AB23" s="72"/>
+      <c r="AC23" s="73"/>
+      <c r="AD23" s="73"/>
+      <c r="AE23" s="73"/>
+      <c r="AF23" s="73"/>
+      <c r="AG23" s="73"/>
+      <c r="AH23" s="73"/>
+      <c r="AI23" s="73"/>
+      <c r="AJ23" s="73"/>
+      <c r="AK23" s="73"/>
+      <c r="AL23" s="74"/>
       <c r="AM23" s="13"/>
       <c r="AO23" s="12"/>
-      <c r="AP23" s="66"/>
-      <c r="AQ23" s="67"/>
-      <c r="AR23" s="67"/>
-      <c r="AS23" s="67"/>
-      <c r="AT23" s="67"/>
-      <c r="AU23" s="67"/>
-      <c r="AV23" s="67"/>
-      <c r="AW23" s="67"/>
-      <c r="AX23" s="67"/>
-      <c r="AY23" s="67"/>
-      <c r="AZ23" s="67"/>
-      <c r="BA23" s="67"/>
-      <c r="BB23" s="67"/>
-      <c r="BC23" s="67"/>
-      <c r="BD23" s="67"/>
-      <c r="BE23" s="67"/>
-      <c r="BF23" s="67"/>
-      <c r="BG23" s="67"/>
-      <c r="BH23" s="68"/>
+      <c r="AP23" s="72"/>
+      <c r="AQ23" s="73"/>
+      <c r="AR23" s="73"/>
+      <c r="AS23" s="73"/>
+      <c r="AT23" s="73"/>
+      <c r="AU23" s="73"/>
+      <c r="AV23" s="73"/>
+      <c r="AW23" s="73"/>
+      <c r="AX23" s="73"/>
+      <c r="AY23" s="73"/>
+      <c r="AZ23" s="73"/>
+      <c r="BA23" s="73"/>
+      <c r="BB23" s="73"/>
+      <c r="BC23" s="73"/>
+      <c r="BD23" s="73"/>
+      <c r="BE23" s="73"/>
+      <c r="BF23" s="73"/>
+      <c r="BG23" s="73"/>
+      <c r="BH23" s="74"/>
       <c r="BV23" s="13"/>
       <c r="BX23" s="12"/>
-      <c r="BY23" s="66"/>
-      <c r="BZ23" s="67"/>
-      <c r="CA23" s="67"/>
-      <c r="CB23" s="68"/>
-      <c r="CF23" s="60"/>
-      <c r="CG23" s="62"/>
-      <c r="CJ23" s="60"/>
-      <c r="CK23" s="62"/>
+      <c r="BY23" s="72"/>
+      <c r="BZ23" s="73"/>
+      <c r="CA23" s="73"/>
+      <c r="CB23" s="74"/>
+      <c r="CF23" s="63"/>
+      <c r="CG23" s="65"/>
+      <c r="CJ23" s="63"/>
+      <c r="CK23" s="65"/>
       <c r="CL23" s="13"/>
       <c r="CM23" s="13"/>
       <c r="CN23" s="2">
@@ -14065,7 +14044,7 @@
       <c r="EX23" s="52"/>
       <c r="EY23" s="53"/>
       <c r="EZ23" s="53"/>
-      <c r="FA23" s="74"/>
+      <c r="FA23" s="58"/>
       <c r="FB23" s="53"/>
       <c r="FC23" s="53"/>
       <c r="FD23" s="53"/>
@@ -14088,7 +14067,6 @@
       <c r="FU23" s="37"/>
       <c r="FV23" s="37"/>
       <c r="FW23" s="37"/>
-      <c r="FX23" s="75"/>
       <c r="FY23" s="37"/>
       <c r="FZ23" s="37"/>
       <c r="GA23" s="37"/>
@@ -14227,7 +14205,6 @@
       <c r="EX24" s="37"/>
       <c r="EY24" s="37"/>
       <c r="EZ24" s="37"/>
-      <c r="FA24" s="75"/>
       <c r="FB24" s="37"/>
       <c r="FC24" s="37"/>
       <c r="FD24" s="37"/>
@@ -14250,7 +14227,6 @@
       <c r="FU24" s="37"/>
       <c r="FV24" s="37"/>
       <c r="FW24" s="37"/>
-      <c r="FX24" s="75"/>
       <c r="FY24" s="37"/>
       <c r="FZ24" s="37"/>
       <c r="GA24" s="37"/>
@@ -14319,61 +14295,61 @@
       </c>
       <c r="V25" s="12"/>
       <c r="W25" s="12"/>
-      <c r="X25" s="63" t="s">
+      <c r="X25" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="Y25" s="64"/>
-      <c r="Z25" s="64"/>
-      <c r="AA25" s="65"/>
-      <c r="AB25" s="63" t="s">
+      <c r="Y25" s="70"/>
+      <c r="Z25" s="70"/>
+      <c r="AA25" s="71"/>
+      <c r="AB25" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AC25" s="64"/>
-      <c r="AD25" s="64"/>
-      <c r="AE25" s="64"/>
-      <c r="AF25" s="64"/>
-      <c r="AG25" s="64"/>
-      <c r="AH25" s="64"/>
-      <c r="AI25" s="64"/>
-      <c r="AJ25" s="64"/>
-      <c r="AK25" s="64"/>
-      <c r="AL25" s="65"/>
+      <c r="AC25" s="70"/>
+      <c r="AD25" s="70"/>
+      <c r="AE25" s="70"/>
+      <c r="AF25" s="70"/>
+      <c r="AG25" s="70"/>
+      <c r="AH25" s="70"/>
+      <c r="AI25" s="70"/>
+      <c r="AJ25" s="70"/>
+      <c r="AK25" s="70"/>
+      <c r="AL25" s="71"/>
       <c r="AM25" s="13"/>
       <c r="AO25" s="12"/>
-      <c r="AP25" s="57" t="s">
+      <c r="AP25" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="AQ25" s="58"/>
-      <c r="AR25" s="58"/>
-      <c r="AS25" s="58"/>
-      <c r="AT25" s="58"/>
-      <c r="AU25" s="58"/>
-      <c r="AV25" s="58"/>
-      <c r="AW25" s="58"/>
-      <c r="AX25" s="58"/>
-      <c r="AY25" s="58"/>
-      <c r="AZ25" s="58"/>
-      <c r="BA25" s="58"/>
-      <c r="BB25" s="58"/>
-      <c r="BC25" s="58"/>
-      <c r="BD25" s="58"/>
-      <c r="BE25" s="58"/>
-      <c r="BF25" s="58"/>
-      <c r="BG25" s="58"/>
-      <c r="BH25" s="58"/>
-      <c r="BI25" s="58"/>
-      <c r="BJ25" s="58"/>
-      <c r="BK25" s="58"/>
-      <c r="BL25" s="58"/>
-      <c r="BM25" s="58"/>
-      <c r="BN25" s="58"/>
-      <c r="BO25" s="58"/>
-      <c r="BP25" s="58"/>
-      <c r="BQ25" s="58"/>
-      <c r="BR25" s="58"/>
-      <c r="BS25" s="58"/>
-      <c r="BT25" s="58"/>
-      <c r="BU25" s="59"/>
+      <c r="AQ25" s="61"/>
+      <c r="AR25" s="61"/>
+      <c r="AS25" s="61"/>
+      <c r="AT25" s="61"/>
+      <c r="AU25" s="61"/>
+      <c r="AV25" s="61"/>
+      <c r="AW25" s="61"/>
+      <c r="AX25" s="61"/>
+      <c r="AY25" s="61"/>
+      <c r="AZ25" s="61"/>
+      <c r="BA25" s="61"/>
+      <c r="BB25" s="61"/>
+      <c r="BC25" s="61"/>
+      <c r="BD25" s="61"/>
+      <c r="BE25" s="61"/>
+      <c r="BF25" s="61"/>
+      <c r="BG25" s="61"/>
+      <c r="BH25" s="61"/>
+      <c r="BI25" s="61"/>
+      <c r="BJ25" s="61"/>
+      <c r="BK25" s="61"/>
+      <c r="BL25" s="61"/>
+      <c r="BM25" s="61"/>
+      <c r="BN25" s="61"/>
+      <c r="BO25" s="61"/>
+      <c r="BP25" s="61"/>
+      <c r="BQ25" s="61"/>
+      <c r="BR25" s="61"/>
+      <c r="BS25" s="61"/>
+      <c r="BT25" s="61"/>
+      <c r="BU25" s="62"/>
       <c r="BV25" s="13"/>
       <c r="BX25" s="12"/>
       <c r="CL25" s="13"/>
@@ -14448,7 +14424,7 @@
       </c>
       <c r="EY25" s="50"/>
       <c r="EZ25" s="50"/>
-      <c r="FA25" s="73"/>
+      <c r="FA25" s="57"/>
       <c r="FB25" s="50"/>
       <c r="FC25" s="50"/>
       <c r="FD25" s="50"/>
@@ -14471,7 +14447,7 @@
       <c r="FU25" s="50"/>
       <c r="FV25" s="50"/>
       <c r="FW25" s="50"/>
-      <c r="FX25" s="73"/>
+      <c r="FX25" s="57"/>
       <c r="FY25" s="50"/>
       <c r="FZ25" s="50"/>
       <c r="GA25" s="50"/>
@@ -14540,55 +14516,55 @@
       </c>
       <c r="V26" s="12"/>
       <c r="W26" s="12"/>
-      <c r="X26" s="66"/>
-      <c r="Y26" s="67"/>
-      <c r="Z26" s="67"/>
-      <c r="AA26" s="68"/>
-      <c r="AB26" s="66"/>
-      <c r="AC26" s="67"/>
-      <c r="AD26" s="67"/>
-      <c r="AE26" s="67"/>
-      <c r="AF26" s="67"/>
-      <c r="AG26" s="67"/>
-      <c r="AH26" s="67"/>
-      <c r="AI26" s="67"/>
-      <c r="AJ26" s="67"/>
-      <c r="AK26" s="67"/>
-      <c r="AL26" s="68"/>
+      <c r="X26" s="72"/>
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="74"/>
+      <c r="AB26" s="72"/>
+      <c r="AC26" s="73"/>
+      <c r="AD26" s="73"/>
+      <c r="AE26" s="73"/>
+      <c r="AF26" s="73"/>
+      <c r="AG26" s="73"/>
+      <c r="AH26" s="73"/>
+      <c r="AI26" s="73"/>
+      <c r="AJ26" s="73"/>
+      <c r="AK26" s="73"/>
+      <c r="AL26" s="74"/>
       <c r="AM26" s="13"/>
       <c r="AO26" s="12"/>
-      <c r="AP26" s="60"/>
-      <c r="AQ26" s="61"/>
-      <c r="AR26" s="61"/>
-      <c r="AS26" s="61"/>
-      <c r="AT26" s="61"/>
-      <c r="AU26" s="61"/>
-      <c r="AV26" s="61"/>
-      <c r="AW26" s="61"/>
-      <c r="AX26" s="61"/>
-      <c r="AY26" s="61"/>
-      <c r="AZ26" s="61"/>
-      <c r="BA26" s="61"/>
-      <c r="BB26" s="61"/>
-      <c r="BC26" s="61"/>
-      <c r="BD26" s="61"/>
-      <c r="BE26" s="61"/>
-      <c r="BF26" s="61"/>
-      <c r="BG26" s="61"/>
-      <c r="BH26" s="61"/>
-      <c r="BI26" s="61"/>
-      <c r="BJ26" s="61"/>
-      <c r="BK26" s="61"/>
-      <c r="BL26" s="61"/>
-      <c r="BM26" s="61"/>
-      <c r="BN26" s="61"/>
-      <c r="BO26" s="61"/>
-      <c r="BP26" s="61"/>
-      <c r="BQ26" s="61"/>
-      <c r="BR26" s="61"/>
-      <c r="BS26" s="61"/>
-      <c r="BT26" s="61"/>
-      <c r="BU26" s="62"/>
+      <c r="AP26" s="63"/>
+      <c r="AQ26" s="64"/>
+      <c r="AR26" s="64"/>
+      <c r="AS26" s="64"/>
+      <c r="AT26" s="64"/>
+      <c r="AU26" s="64"/>
+      <c r="AV26" s="64"/>
+      <c r="AW26" s="64"/>
+      <c r="AX26" s="64"/>
+      <c r="AY26" s="64"/>
+      <c r="AZ26" s="64"/>
+      <c r="BA26" s="64"/>
+      <c r="BB26" s="64"/>
+      <c r="BC26" s="64"/>
+      <c r="BD26" s="64"/>
+      <c r="BE26" s="64"/>
+      <c r="BF26" s="64"/>
+      <c r="BG26" s="64"/>
+      <c r="BH26" s="64"/>
+      <c r="BI26" s="64"/>
+      <c r="BJ26" s="64"/>
+      <c r="BK26" s="64"/>
+      <c r="BL26" s="64"/>
+      <c r="BM26" s="64"/>
+      <c r="BN26" s="64"/>
+      <c r="BO26" s="64"/>
+      <c r="BP26" s="64"/>
+      <c r="BQ26" s="64"/>
+      <c r="BR26" s="64"/>
+      <c r="BS26" s="64"/>
+      <c r="BT26" s="64"/>
+      <c r="BU26" s="65"/>
       <c r="BV26" s="13"/>
       <c r="BX26" s="12"/>
       <c r="CL26" s="13"/>
@@ -14657,7 +14633,7 @@
       <c r="EX26" s="52"/>
       <c r="EY26" s="53"/>
       <c r="EZ26" s="53"/>
-      <c r="FA26" s="74"/>
+      <c r="FA26" s="58"/>
       <c r="FB26" s="53"/>
       <c r="FC26" s="53"/>
       <c r="FD26" s="53"/>
@@ -14680,7 +14656,7 @@
       <c r="FU26" s="53"/>
       <c r="FV26" s="53"/>
       <c r="FW26" s="53"/>
-      <c r="FX26" s="74"/>
+      <c r="FX26" s="58"/>
       <c r="FY26" s="53"/>
       <c r="FZ26" s="53"/>
       <c r="GA26" s="53"/>
@@ -14819,7 +14795,6 @@
       <c r="EX27" s="37"/>
       <c r="EY27" s="37"/>
       <c r="EZ27" s="37"/>
-      <c r="FA27" s="75"/>
       <c r="FB27" s="37"/>
       <c r="FC27" s="37"/>
       <c r="FD27" s="37"/>
@@ -14842,7 +14817,6 @@
       <c r="FU27" s="37"/>
       <c r="FV27" s="37"/>
       <c r="FW27" s="37"/>
-      <c r="FX27" s="75"/>
       <c r="FY27" s="37"/>
       <c r="FZ27" s="37"/>
       <c r="GA27" s="37"/>
@@ -14911,39 +14885,39 @@
       </c>
       <c r="V28" s="12"/>
       <c r="W28" s="12"/>
-      <c r="X28" s="63" t="s">
+      <c r="X28" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="Y28" s="64"/>
-      <c r="Z28" s="64"/>
-      <c r="AA28" s="65"/>
-      <c r="AB28" s="63" t="s">
+      <c r="Y28" s="70"/>
+      <c r="Z28" s="70"/>
+      <c r="AA28" s="71"/>
+      <c r="AB28" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AC28" s="64"/>
-      <c r="AD28" s="64"/>
-      <c r="AE28" s="64"/>
-      <c r="AF28" s="64"/>
-      <c r="AG28" s="64"/>
-      <c r="AH28" s="64"/>
-      <c r="AI28" s="64"/>
-      <c r="AJ28" s="64"/>
-      <c r="AK28" s="64"/>
-      <c r="AL28" s="65"/>
+      <c r="AC28" s="70"/>
+      <c r="AD28" s="70"/>
+      <c r="AE28" s="70"/>
+      <c r="AF28" s="70"/>
+      <c r="AG28" s="70"/>
+      <c r="AH28" s="70"/>
+      <c r="AI28" s="70"/>
+      <c r="AJ28" s="70"/>
+      <c r="AK28" s="70"/>
+      <c r="AL28" s="71"/>
       <c r="AM28" s="13"/>
       <c r="AO28" s="12"/>
-      <c r="AP28" s="63" t="s">
+      <c r="AP28" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="AQ28" s="64"/>
-      <c r="AR28" s="64"/>
-      <c r="AS28" s="64"/>
-      <c r="AT28" s="64"/>
-      <c r="AU28" s="64"/>
-      <c r="AV28" s="64"/>
-      <c r="AW28" s="64"/>
-      <c r="AX28" s="64"/>
-      <c r="AY28" s="65"/>
+      <c r="AQ28" s="70"/>
+      <c r="AR28" s="70"/>
+      <c r="AS28" s="70"/>
+      <c r="AT28" s="70"/>
+      <c r="AU28" s="70"/>
+      <c r="AV28" s="70"/>
+      <c r="AW28" s="70"/>
+      <c r="AX28" s="70"/>
+      <c r="AY28" s="71"/>
       <c r="AZ28" s="20"/>
       <c r="BB28" s="20"/>
       <c r="BC28" s="20"/>
@@ -14959,22 +14933,22 @@
       <c r="BN28" s="20"/>
       <c r="BV28" s="13"/>
       <c r="BX28" s="12"/>
-      <c r="BY28" s="57" t="s">
+      <c r="BY28" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="BZ28" s="58"/>
-      <c r="CA28" s="58"/>
-      <c r="CB28" s="58"/>
-      <c r="CC28" s="58"/>
-      <c r="CD28" s="59"/>
-      <c r="CF28" s="57" t="s">
+      <c r="BZ28" s="61"/>
+      <c r="CA28" s="61"/>
+      <c r="CB28" s="61"/>
+      <c r="CC28" s="61"/>
+      <c r="CD28" s="62"/>
+      <c r="CF28" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="CG28" s="58"/>
-      <c r="CH28" s="58"/>
-      <c r="CI28" s="58"/>
-      <c r="CJ28" s="58"/>
-      <c r="CK28" s="59"/>
+      <c r="CG28" s="61"/>
+      <c r="CH28" s="61"/>
+      <c r="CI28" s="61"/>
+      <c r="CJ28" s="61"/>
+      <c r="CK28" s="62"/>
       <c r="CL28" s="13"/>
       <c r="CM28" s="13"/>
       <c r="CN28" s="2">
@@ -15047,7 +15021,7 @@
       </c>
       <c r="EY28" s="50"/>
       <c r="EZ28" s="50"/>
-      <c r="FA28" s="73"/>
+      <c r="FA28" s="57"/>
       <c r="FB28" s="50"/>
       <c r="FC28" s="50"/>
       <c r="FD28" s="50"/>
@@ -15070,7 +15044,6 @@
       <c r="FU28" s="39"/>
       <c r="FV28" s="39"/>
       <c r="FW28" s="37"/>
-      <c r="FX28" s="75"/>
       <c r="FY28" s="37"/>
       <c r="FZ28" s="37"/>
       <c r="GA28" s="37"/>
@@ -15143,33 +15116,33 @@
       </c>
       <c r="V29" s="12"/>
       <c r="W29" s="12"/>
-      <c r="X29" s="66"/>
-      <c r="Y29" s="67"/>
-      <c r="Z29" s="67"/>
-      <c r="AA29" s="68"/>
-      <c r="AB29" s="66"/>
-      <c r="AC29" s="67"/>
-      <c r="AD29" s="67"/>
-      <c r="AE29" s="67"/>
-      <c r="AF29" s="67"/>
-      <c r="AG29" s="67"/>
-      <c r="AH29" s="67"/>
-      <c r="AI29" s="67"/>
-      <c r="AJ29" s="67"/>
-      <c r="AK29" s="67"/>
-      <c r="AL29" s="68"/>
+      <c r="X29" s="72"/>
+      <c r="Y29" s="73"/>
+      <c r="Z29" s="73"/>
+      <c r="AA29" s="74"/>
+      <c r="AB29" s="72"/>
+      <c r="AC29" s="73"/>
+      <c r="AD29" s="73"/>
+      <c r="AE29" s="73"/>
+      <c r="AF29" s="73"/>
+      <c r="AG29" s="73"/>
+      <c r="AH29" s="73"/>
+      <c r="AI29" s="73"/>
+      <c r="AJ29" s="73"/>
+      <c r="AK29" s="73"/>
+      <c r="AL29" s="74"/>
       <c r="AM29" s="13"/>
       <c r="AO29" s="12"/>
-      <c r="AP29" s="66"/>
-      <c r="AQ29" s="67"/>
-      <c r="AR29" s="67"/>
-      <c r="AS29" s="67"/>
-      <c r="AT29" s="67"/>
-      <c r="AU29" s="67"/>
-      <c r="AV29" s="67"/>
-      <c r="AW29" s="67"/>
-      <c r="AX29" s="67"/>
-      <c r="AY29" s="68"/>
+      <c r="AP29" s="72"/>
+      <c r="AQ29" s="73"/>
+      <c r="AR29" s="73"/>
+      <c r="AS29" s="73"/>
+      <c r="AT29" s="73"/>
+      <c r="AU29" s="73"/>
+      <c r="AV29" s="73"/>
+      <c r="AW29" s="73"/>
+      <c r="AX29" s="73"/>
+      <c r="AY29" s="74"/>
       <c r="AZ29" s="20"/>
       <c r="BB29" s="20"/>
       <c r="BC29" s="20"/>
@@ -15185,18 +15158,18 @@
       <c r="BN29" s="20"/>
       <c r="BV29" s="13"/>
       <c r="BX29" s="12"/>
-      <c r="BY29" s="60"/>
-      <c r="BZ29" s="61"/>
-      <c r="CA29" s="61"/>
-      <c r="CB29" s="61"/>
-      <c r="CC29" s="61"/>
-      <c r="CD29" s="62"/>
-      <c r="CF29" s="60"/>
-      <c r="CG29" s="61"/>
-      <c r="CH29" s="61"/>
-      <c r="CI29" s="61"/>
-      <c r="CJ29" s="61"/>
-      <c r="CK29" s="62"/>
+      <c r="BY29" s="63"/>
+      <c r="BZ29" s="64"/>
+      <c r="CA29" s="64"/>
+      <c r="CB29" s="64"/>
+      <c r="CC29" s="64"/>
+      <c r="CD29" s="65"/>
+      <c r="CF29" s="63"/>
+      <c r="CG29" s="64"/>
+      <c r="CH29" s="64"/>
+      <c r="CI29" s="64"/>
+      <c r="CJ29" s="64"/>
+      <c r="CK29" s="65"/>
       <c r="CL29" s="13"/>
       <c r="CM29" s="13"/>
       <c r="CN29" s="2">
@@ -15263,7 +15236,7 @@
       <c r="EX29" s="52"/>
       <c r="EY29" s="53"/>
       <c r="EZ29" s="53"/>
-      <c r="FA29" s="74"/>
+      <c r="FA29" s="58"/>
       <c r="FB29" s="53"/>
       <c r="FC29" s="53"/>
       <c r="FD29" s="53"/>
@@ -15286,7 +15259,6 @@
       <c r="FU29" s="39"/>
       <c r="FV29" s="39"/>
       <c r="FW29" s="37"/>
-      <c r="FX29" s="75"/>
       <c r="FY29" s="37"/>
       <c r="FZ29" s="37"/>
       <c r="GA29" s="37"/>
@@ -15443,7 +15415,6 @@
       <c r="EX30" s="37"/>
       <c r="EY30" s="37"/>
       <c r="EZ30" s="37"/>
-      <c r="FA30" s="75"/>
       <c r="FB30" s="37"/>
       <c r="FC30" s="39"/>
       <c r="FD30" s="39"/>
@@ -15466,7 +15437,6 @@
       <c r="FU30" s="39"/>
       <c r="FV30" s="39"/>
       <c r="FW30" s="37"/>
-      <c r="FX30" s="75"/>
       <c r="FY30" s="37"/>
       <c r="FZ30" s="37"/>
       <c r="GA30" s="37"/>
@@ -15535,76 +15505,76 @@
       </c>
       <c r="V31" s="12"/>
       <c r="W31" s="12"/>
-      <c r="X31" s="63" t="s">
+      <c r="X31" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="Y31" s="64"/>
-      <c r="Z31" s="64"/>
-      <c r="AA31" s="65"/>
-      <c r="AB31" s="63" t="s">
+      <c r="Y31" s="70"/>
+      <c r="Z31" s="70"/>
+      <c r="AA31" s="71"/>
+      <c r="AB31" s="69" t="s">
         <v>13</v>
       </c>
-      <c r="AC31" s="64"/>
-      <c r="AD31" s="64"/>
-      <c r="AE31" s="64"/>
-      <c r="AF31" s="64"/>
-      <c r="AG31" s="64"/>
-      <c r="AH31" s="64"/>
-      <c r="AI31" s="64"/>
-      <c r="AJ31" s="64"/>
-      <c r="AK31" s="64"/>
-      <c r="AL31" s="65"/>
+      <c r="AC31" s="70"/>
+      <c r="AD31" s="70"/>
+      <c r="AE31" s="70"/>
+      <c r="AF31" s="70"/>
+      <c r="AG31" s="70"/>
+      <c r="AH31" s="70"/>
+      <c r="AI31" s="70"/>
+      <c r="AJ31" s="70"/>
+      <c r="AK31" s="70"/>
+      <c r="AL31" s="71"/>
       <c r="AM31" s="13"/>
       <c r="AO31" s="12"/>
       <c r="AS31" s="20"/>
       <c r="AT31" s="20"/>
       <c r="AU31" s="20"/>
-      <c r="AV31" s="57" t="s">
+      <c r="AV31" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="AW31" s="58"/>
-      <c r="AX31" s="58"/>
-      <c r="AY31" s="58"/>
-      <c r="AZ31" s="58"/>
-      <c r="BA31" s="59"/>
+      <c r="AW31" s="61"/>
+      <c r="AX31" s="61"/>
+      <c r="AY31" s="61"/>
+      <c r="AZ31" s="61"/>
+      <c r="BA31" s="62"/>
       <c r="BB31" s="20"/>
-      <c r="BC31" s="57" t="s">
+      <c r="BC31" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="BD31" s="58"/>
-      <c r="BE31" s="58"/>
-      <c r="BF31" s="58"/>
-      <c r="BG31" s="58"/>
-      <c r="BH31" s="59"/>
+      <c r="BD31" s="61"/>
+      <c r="BE31" s="61"/>
+      <c r="BF31" s="61"/>
+      <c r="BG31" s="61"/>
+      <c r="BH31" s="62"/>
       <c r="BI31" s="20"/>
-      <c r="BJ31" s="57" t="s">
+      <c r="BJ31" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="BK31" s="58"/>
-      <c r="BL31" s="58"/>
-      <c r="BM31" s="58"/>
-      <c r="BN31" s="58"/>
-      <c r="BO31" s="59"/>
+      <c r="BK31" s="61"/>
+      <c r="BL31" s="61"/>
+      <c r="BM31" s="61"/>
+      <c r="BN31" s="61"/>
+      <c r="BO31" s="62"/>
       <c r="BP31" s="20"/>
       <c r="BQ31" s="20"/>
       <c r="BR31" s="20"/>
       <c r="BV31" s="13"/>
       <c r="BX31" s="12"/>
-      <c r="BY31" s="57" t="s">
+      <c r="BY31" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="BZ31" s="58"/>
-      <c r="CA31" s="58"/>
-      <c r="CB31" s="58"/>
-      <c r="CC31" s="58"/>
-      <c r="CD31" s="58"/>
-      <c r="CE31" s="58"/>
-      <c r="CF31" s="58"/>
-      <c r="CG31" s="58"/>
-      <c r="CH31" s="58"/>
-      <c r="CI31" s="58"/>
-      <c r="CJ31" s="58"/>
-      <c r="CK31" s="59"/>
+      <c r="BZ31" s="61"/>
+      <c r="CA31" s="61"/>
+      <c r="CB31" s="61"/>
+      <c r="CC31" s="61"/>
+      <c r="CD31" s="61"/>
+      <c r="CE31" s="61"/>
+      <c r="CF31" s="61"/>
+      <c r="CG31" s="61"/>
+      <c r="CH31" s="61"/>
+      <c r="CI31" s="61"/>
+      <c r="CJ31" s="61"/>
+      <c r="CK31" s="62"/>
       <c r="CL31" s="13"/>
       <c r="CM31" s="13"/>
       <c r="CN31" s="2">
@@ -15675,7 +15645,7 @@
       <c r="EX31" s="37"/>
       <c r="EY31" s="37"/>
       <c r="EZ31" s="37"/>
-      <c r="FA31" s="76"/>
+      <c r="FA31" s="20"/>
       <c r="FB31" s="39"/>
       <c r="FC31" s="39"/>
       <c r="FD31" s="49" t="s">
@@ -15704,7 +15674,7 @@
       <c r="FU31" s="50"/>
       <c r="FV31" s="50"/>
       <c r="FW31" s="51"/>
-      <c r="FX31" s="76"/>
+      <c r="FX31" s="20"/>
       <c r="FY31" s="39"/>
       <c r="FZ31" s="39"/>
       <c r="GA31" s="37"/>
@@ -15775,64 +15745,64 @@
       </c>
       <c r="V32" s="12"/>
       <c r="W32" s="12"/>
-      <c r="X32" s="66"/>
-      <c r="Y32" s="67"/>
-      <c r="Z32" s="67"/>
-      <c r="AA32" s="68"/>
-      <c r="AB32" s="66"/>
-      <c r="AC32" s="67"/>
-      <c r="AD32" s="67"/>
-      <c r="AE32" s="67"/>
-      <c r="AF32" s="67"/>
-      <c r="AG32" s="67"/>
-      <c r="AH32" s="67"/>
-      <c r="AI32" s="67"/>
-      <c r="AJ32" s="67"/>
-      <c r="AK32" s="67"/>
-      <c r="AL32" s="68"/>
+      <c r="X32" s="72"/>
+      <c r="Y32" s="73"/>
+      <c r="Z32" s="73"/>
+      <c r="AA32" s="74"/>
+      <c r="AB32" s="72"/>
+      <c r="AC32" s="73"/>
+      <c r="AD32" s="73"/>
+      <c r="AE32" s="73"/>
+      <c r="AF32" s="73"/>
+      <c r="AG32" s="73"/>
+      <c r="AH32" s="73"/>
+      <c r="AI32" s="73"/>
+      <c r="AJ32" s="73"/>
+      <c r="AK32" s="73"/>
+      <c r="AL32" s="74"/>
       <c r="AM32" s="13"/>
       <c r="AO32" s="12"/>
       <c r="AS32" s="20"/>
       <c r="AT32" s="20"/>
       <c r="AU32" s="20"/>
-      <c r="AV32" s="60"/>
-      <c r="AW32" s="61"/>
-      <c r="AX32" s="61"/>
-      <c r="AY32" s="61"/>
-      <c r="AZ32" s="61"/>
-      <c r="BA32" s="62"/>
+      <c r="AV32" s="63"/>
+      <c r="AW32" s="64"/>
+      <c r="AX32" s="64"/>
+      <c r="AY32" s="64"/>
+      <c r="AZ32" s="64"/>
+      <c r="BA32" s="65"/>
       <c r="BB32" s="20"/>
-      <c r="BC32" s="60"/>
-      <c r="BD32" s="61"/>
-      <c r="BE32" s="61"/>
-      <c r="BF32" s="61"/>
-      <c r="BG32" s="61"/>
-      <c r="BH32" s="62"/>
+      <c r="BC32" s="63"/>
+      <c r="BD32" s="64"/>
+      <c r="BE32" s="64"/>
+      <c r="BF32" s="64"/>
+      <c r="BG32" s="64"/>
+      <c r="BH32" s="65"/>
       <c r="BI32" s="20"/>
-      <c r="BJ32" s="60"/>
-      <c r="BK32" s="61"/>
-      <c r="BL32" s="61"/>
-      <c r="BM32" s="61"/>
-      <c r="BN32" s="61"/>
-      <c r="BO32" s="62"/>
+      <c r="BJ32" s="63"/>
+      <c r="BK32" s="64"/>
+      <c r="BL32" s="64"/>
+      <c r="BM32" s="64"/>
+      <c r="BN32" s="64"/>
+      <c r="BO32" s="65"/>
       <c r="BP32" s="20"/>
       <c r="BQ32" s="20"/>
       <c r="BR32" s="20"/>
       <c r="BV32" s="13"/>
       <c r="BX32" s="12"/>
-      <c r="BY32" s="69"/>
-      <c r="BZ32" s="70"/>
-      <c r="CA32" s="70"/>
-      <c r="CB32" s="70"/>
-      <c r="CC32" s="70"/>
-      <c r="CD32" s="70"/>
-      <c r="CE32" s="70"/>
-      <c r="CF32" s="70"/>
-      <c r="CG32" s="70"/>
-      <c r="CH32" s="70"/>
-      <c r="CI32" s="70"/>
-      <c r="CJ32" s="70"/>
-      <c r="CK32" s="71"/>
+      <c r="BY32" s="66"/>
+      <c r="BZ32" s="67"/>
+      <c r="CA32" s="67"/>
+      <c r="CB32" s="67"/>
+      <c r="CC32" s="67"/>
+      <c r="CD32" s="67"/>
+      <c r="CE32" s="67"/>
+      <c r="CF32" s="67"/>
+      <c r="CG32" s="67"/>
+      <c r="CH32" s="67"/>
+      <c r="CI32" s="67"/>
+      <c r="CJ32" s="67"/>
+      <c r="CK32" s="68"/>
       <c r="CL32" s="13"/>
       <c r="CM32" s="13"/>
       <c r="CN32" s="2">
@@ -15899,7 +15869,7 @@
       <c r="EX32" s="37"/>
       <c r="EY32" s="37"/>
       <c r="EZ32" s="37"/>
-      <c r="FA32" s="76"/>
+      <c r="FA32" s="20"/>
       <c r="FB32" s="39"/>
       <c r="FC32" s="39"/>
       <c r="FD32" s="52"/>
@@ -15922,7 +15892,7 @@
       <c r="FU32" s="53"/>
       <c r="FV32" s="53"/>
       <c r="FW32" s="54"/>
-      <c r="FX32" s="76"/>
+      <c r="FX32" s="20"/>
       <c r="FY32" s="39"/>
       <c r="FZ32" s="39"/>
       <c r="GA32" s="37"/>
@@ -15995,19 +15965,19 @@
       <c r="AO33" s="12"/>
       <c r="BV33" s="13"/>
       <c r="BX33" s="12"/>
-      <c r="BY33" s="60"/>
-      <c r="BZ33" s="61"/>
-      <c r="CA33" s="61"/>
-      <c r="CB33" s="61"/>
-      <c r="CC33" s="61"/>
-      <c r="CD33" s="61"/>
-      <c r="CE33" s="61"/>
-      <c r="CF33" s="61"/>
-      <c r="CG33" s="61"/>
-      <c r="CH33" s="61"/>
-      <c r="CI33" s="61"/>
-      <c r="CJ33" s="61"/>
-      <c r="CK33" s="62"/>
+      <c r="BY33" s="63"/>
+      <c r="BZ33" s="64"/>
+      <c r="CA33" s="64"/>
+      <c r="CB33" s="64"/>
+      <c r="CC33" s="64"/>
+      <c r="CD33" s="64"/>
+      <c r="CE33" s="64"/>
+      <c r="CF33" s="64"/>
+      <c r="CG33" s="64"/>
+      <c r="CH33" s="64"/>
+      <c r="CI33" s="64"/>
+      <c r="CJ33" s="64"/>
+      <c r="CK33" s="65"/>
       <c r="CL33" s="13"/>
       <c r="CM33" s="13"/>
       <c r="CN33" s="2">
@@ -16074,7 +16044,6 @@
       <c r="EX33" s="37"/>
       <c r="EY33" s="37"/>
       <c r="EZ33" s="37"/>
-      <c r="FA33" s="75"/>
       <c r="FB33" s="37"/>
       <c r="FC33" s="37"/>
       <c r="FD33" s="37"/>
@@ -16097,7 +16066,6 @@
       <c r="FU33" s="37"/>
       <c r="FV33" s="37"/>
       <c r="FW33" s="37"/>
-      <c r="FX33" s="75"/>
       <c r="FY33" s="37"/>
       <c r="FZ33" s="37"/>
       <c r="GA33" s="37"/>
@@ -16320,7 +16288,7 @@
       <c r="FV34" s="41"/>
       <c r="FW34" s="41"/>
       <c r="FX34" s="41"/>
-      <c r="FY34" s="77"/>
+      <c r="FY34" s="37"/>
       <c r="FZ34" s="41"/>
       <c r="GA34" s="41"/>
       <c r="GB34" s="41"/>
@@ -16430,18 +16398,6 @@
         <v>28</v>
       </c>
       <c r="ED35" s="12"/>
-      <c r="EN35" s="75"/>
-      <c r="EO35" s="75"/>
-      <c r="EP35" s="75"/>
-      <c r="EQ35" s="75"/>
-      <c r="ER35" s="75"/>
-      <c r="ES35" s="75"/>
-      <c r="ET35" s="75"/>
-      <c r="EU35" s="75"/>
-      <c r="EV35" s="75"/>
-      <c r="EW35" s="75"/>
-      <c r="EX35" s="75"/>
-      <c r="EY35" s="75"/>
       <c r="EZ35" s="37"/>
       <c r="FA35" s="24"/>
       <c r="FB35" s="21"/>
@@ -16467,7 +16423,7 @@
       <c r="FV35" s="21"/>
       <c r="FW35" s="21"/>
       <c r="FX35" s="25"/>
-      <c r="FY35" s="78"/>
+      <c r="FY35" s="39"/>
       <c r="FZ35" s="37"/>
       <c r="GA35" s="37"/>
       <c r="GB35" s="37"/>
@@ -16534,65 +16490,65 @@
         <v>29</v>
       </c>
       <c r="V36" s="12"/>
-      <c r="W36" s="63" t="s">
+      <c r="W36" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="X36" s="64"/>
-      <c r="Y36" s="64"/>
-      <c r="Z36" s="64"/>
-      <c r="AA36" s="64"/>
-      <c r="AB36" s="64"/>
-      <c r="AC36" s="64"/>
-      <c r="AD36" s="64"/>
-      <c r="AE36" s="64"/>
-      <c r="AF36" s="65"/>
-      <c r="AG36" s="20"/>
-      <c r="AH36" s="63" t="s">
+      <c r="X36" s="70"/>
+      <c r="Y36" s="70"/>
+      <c r="Z36" s="70"/>
+      <c r="AA36" s="70"/>
+      <c r="AB36" s="70"/>
+      <c r="AC36" s="71"/>
+      <c r="AE36" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="AI36" s="64"/>
-      <c r="AJ36" s="65"/>
-      <c r="AK36" s="57" t="s">
+      <c r="AF36" s="70"/>
+      <c r="AG36" s="71"/>
+      <c r="AH36" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="AL36" s="58"/>
-      <c r="AM36" s="58"/>
-      <c r="AN36" s="59"/>
-      <c r="AO36" s="20"/>
-      <c r="AP36" s="57" t="s">
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="61"/>
+      <c r="AK36" s="62"/>
+      <c r="AM36" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="AN36" s="70"/>
+      <c r="AO36" s="71"/>
+      <c r="AP36" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="AQ36" s="59"/>
-      <c r="AS36" s="63" t="s">
+      <c r="AQ36" s="62"/>
+      <c r="AS36" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="AT36" s="64"/>
-      <c r="AU36" s="65"/>
-      <c r="AV36" s="57" t="s">
+      <c r="AT36" s="70"/>
+      <c r="AU36" s="71"/>
+      <c r="AV36" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="AW36" s="58"/>
-      <c r="AX36" s="58"/>
-      <c r="AY36" s="58"/>
-      <c r="AZ36" s="58"/>
-      <c r="BA36" s="59"/>
+      <c r="AW36" s="61"/>
+      <c r="AX36" s="61"/>
+      <c r="AY36" s="61"/>
+      <c r="AZ36" s="61"/>
+      <c r="BA36" s="62"/>
       <c r="BB36" s="20"/>
-      <c r="BC36" s="57" t="s">
+      <c r="BC36" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="BD36" s="59"/>
-      <c r="BF36" s="63" t="s">
+      <c r="BD36" s="62"/>
+      <c r="BF36" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="BG36" s="64"/>
-      <c r="BH36" s="64"/>
-      <c r="BI36" s="64"/>
-      <c r="BJ36" s="64"/>
-      <c r="BK36" s="64"/>
-      <c r="BL36" s="64"/>
-      <c r="BM36" s="64"/>
-      <c r="BN36" s="64"/>
-      <c r="BO36" s="65"/>
+      <c r="BG36" s="70"/>
+      <c r="BH36" s="70"/>
+      <c r="BI36" s="70"/>
+      <c r="BJ36" s="70"/>
+      <c r="BK36" s="70"/>
+      <c r="BL36" s="70"/>
+      <c r="BM36" s="70"/>
+      <c r="BN36" s="70"/>
+      <c r="BO36" s="71"/>
       <c r="BP36" s="20"/>
       <c r="BQ36" s="20"/>
       <c r="BR36" s="20"/>
@@ -16684,34 +16640,34 @@
       <c r="EY36" s="37"/>
       <c r="EZ36" s="37"/>
       <c r="FA36" s="26"/>
-      <c r="FB36" s="63" t="s">
+      <c r="FB36" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="FC36" s="64"/>
-      <c r="FD36" s="64"/>
-      <c r="FE36" s="64"/>
-      <c r="FF36" s="64"/>
-      <c r="FG36" s="64"/>
-      <c r="FH36" s="64"/>
-      <c r="FI36" s="64"/>
-      <c r="FJ36" s="64"/>
-      <c r="FK36" s="65"/>
-      <c r="FL36" s="79"/>
-      <c r="FM36" s="79"/>
-      <c r="FN36" s="79"/>
-      <c r="FO36" s="79"/>
-      <c r="FP36" s="79"/>
-      <c r="FQ36" s="79"/>
-      <c r="FR36" s="79"/>
-      <c r="FS36" s="79"/>
-      <c r="FT36" s="79"/>
-      <c r="FU36" s="79"/>
-      <c r="FV36" s="57" t="s">
+      <c r="FC36" s="70"/>
+      <c r="FD36" s="70"/>
+      <c r="FE36" s="70"/>
+      <c r="FF36" s="70"/>
+      <c r="FG36" s="70"/>
+      <c r="FH36" s="70"/>
+      <c r="FI36" s="70"/>
+      <c r="FJ36" s="70"/>
+      <c r="FK36" s="71"/>
+      <c r="FL36" s="20"/>
+      <c r="FM36" s="20"/>
+      <c r="FN36" s="20"/>
+      <c r="FO36" s="20"/>
+      <c r="FP36" s="20"/>
+      <c r="FQ36" s="20"/>
+      <c r="FR36" s="20"/>
+      <c r="FS36" s="20"/>
+      <c r="FT36" s="20"/>
+      <c r="FU36" s="20"/>
+      <c r="FV36" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="FW36" s="59"/>
+      <c r="FW36" s="62"/>
       <c r="FX36" s="13"/>
-      <c r="FY36" s="78"/>
+      <c r="FY36" s="39"/>
       <c r="FZ36" s="39"/>
       <c r="GA36" s="39"/>
       <c r="GB36" s="39"/>
@@ -16778,49 +16734,47 @@
         <v>30</v>
       </c>
       <c r="V37" s="12"/>
-      <c r="W37" s="66"/>
-      <c r="X37" s="67"/>
-      <c r="Y37" s="67"/>
-      <c r="Z37" s="67"/>
-      <c r="AA37" s="67"/>
-      <c r="AB37" s="67"/>
-      <c r="AC37" s="67"/>
-      <c r="AD37" s="67"/>
-      <c r="AE37" s="67"/>
-      <c r="AF37" s="68"/>
-      <c r="AG37" s="20"/>
-      <c r="AH37" s="66"/>
-      <c r="AI37" s="67"/>
-      <c r="AJ37" s="68"/>
-      <c r="AK37" s="60"/>
-      <c r="AL37" s="61"/>
-      <c r="AM37" s="61"/>
-      <c r="AN37" s="62"/>
-      <c r="AO37" s="20"/>
-      <c r="AP37" s="60"/>
-      <c r="AQ37" s="62"/>
-      <c r="AS37" s="66"/>
-      <c r="AT37" s="67"/>
-      <c r="AU37" s="68"/>
-      <c r="AV37" s="60"/>
-      <c r="AW37" s="61"/>
-      <c r="AX37" s="61"/>
-      <c r="AY37" s="61"/>
-      <c r="AZ37" s="61"/>
-      <c r="BA37" s="62"/>
+      <c r="W37" s="72"/>
+      <c r="X37" s="73"/>
+      <c r="Y37" s="73"/>
+      <c r="Z37" s="73"/>
+      <c r="AA37" s="73"/>
+      <c r="AB37" s="73"/>
+      <c r="AC37" s="74"/>
+      <c r="AE37" s="72"/>
+      <c r="AF37" s="73"/>
+      <c r="AG37" s="74"/>
+      <c r="AH37" s="63"/>
+      <c r="AI37" s="64"/>
+      <c r="AJ37" s="64"/>
+      <c r="AK37" s="65"/>
+      <c r="AM37" s="72"/>
+      <c r="AN37" s="73"/>
+      <c r="AO37" s="74"/>
+      <c r="AP37" s="63"/>
+      <c r="AQ37" s="65"/>
+      <c r="AS37" s="72"/>
+      <c r="AT37" s="73"/>
+      <c r="AU37" s="74"/>
+      <c r="AV37" s="63"/>
+      <c r="AW37" s="64"/>
+      <c r="AX37" s="64"/>
+      <c r="AY37" s="64"/>
+      <c r="AZ37" s="64"/>
+      <c r="BA37" s="65"/>
       <c r="BB37" s="20"/>
-      <c r="BC37" s="60"/>
-      <c r="BD37" s="62"/>
-      <c r="BF37" s="66"/>
-      <c r="BG37" s="67"/>
-      <c r="BH37" s="67"/>
-      <c r="BI37" s="67"/>
-      <c r="BJ37" s="67"/>
-      <c r="BK37" s="67"/>
-      <c r="BL37" s="67"/>
-      <c r="BM37" s="67"/>
-      <c r="BN37" s="67"/>
-      <c r="BO37" s="68"/>
+      <c r="BC37" s="63"/>
+      <c r="BD37" s="65"/>
+      <c r="BF37" s="72"/>
+      <c r="BG37" s="73"/>
+      <c r="BH37" s="73"/>
+      <c r="BI37" s="73"/>
+      <c r="BJ37" s="73"/>
+      <c r="BK37" s="73"/>
+      <c r="BL37" s="73"/>
+      <c r="BM37" s="73"/>
+      <c r="BN37" s="73"/>
+      <c r="BO37" s="74"/>
       <c r="BP37" s="20"/>
       <c r="BQ37" s="20"/>
       <c r="BR37" s="20"/>
@@ -16910,30 +16864,30 @@
       <c r="EY37" s="37"/>
       <c r="EZ37" s="37"/>
       <c r="FA37" s="26"/>
-      <c r="FB37" s="66"/>
-      <c r="FC37" s="67"/>
-      <c r="FD37" s="67"/>
-      <c r="FE37" s="67"/>
-      <c r="FF37" s="67"/>
-      <c r="FG37" s="67"/>
-      <c r="FH37" s="67"/>
-      <c r="FI37" s="67"/>
-      <c r="FJ37" s="67"/>
-      <c r="FK37" s="68"/>
-      <c r="FL37" s="79"/>
-      <c r="FM37" s="79"/>
-      <c r="FN37" s="79"/>
-      <c r="FO37" s="79"/>
-      <c r="FP37" s="79"/>
-      <c r="FQ37" s="79"/>
-      <c r="FR37" s="79"/>
-      <c r="FS37" s="79"/>
-      <c r="FT37" s="79"/>
-      <c r="FU37" s="79"/>
-      <c r="FV37" s="60"/>
-      <c r="FW37" s="62"/>
+      <c r="FB37" s="72"/>
+      <c r="FC37" s="73"/>
+      <c r="FD37" s="73"/>
+      <c r="FE37" s="73"/>
+      <c r="FF37" s="73"/>
+      <c r="FG37" s="73"/>
+      <c r="FH37" s="73"/>
+      <c r="FI37" s="73"/>
+      <c r="FJ37" s="73"/>
+      <c r="FK37" s="74"/>
+      <c r="FL37" s="20"/>
+      <c r="FM37" s="20"/>
+      <c r="FN37" s="20"/>
+      <c r="FO37" s="20"/>
+      <c r="FP37" s="20"/>
+      <c r="FQ37" s="20"/>
+      <c r="FR37" s="20"/>
+      <c r="FS37" s="20"/>
+      <c r="FT37" s="20"/>
+      <c r="FU37" s="20"/>
+      <c r="FV37" s="63"/>
+      <c r="FW37" s="65"/>
       <c r="FX37" s="13"/>
-      <c r="FY37" s="78"/>
+      <c r="FY37" s="39"/>
       <c r="FZ37" s="39"/>
       <c r="GA37" s="39"/>
       <c r="GB37" s="39"/>
@@ -17066,30 +17020,30 @@
       <c r="EY38" s="37"/>
       <c r="EZ38" s="37"/>
       <c r="FA38" s="26"/>
-      <c r="FB38" s="81"/>
-      <c r="FC38" s="81"/>
-      <c r="FD38" s="81"/>
-      <c r="FE38" s="81"/>
-      <c r="FF38" s="81"/>
-      <c r="FG38" s="81"/>
-      <c r="FH38" s="81"/>
-      <c r="FI38" s="81"/>
-      <c r="FJ38" s="81"/>
-      <c r="FK38" s="81"/>
-      <c r="FL38" s="79"/>
-      <c r="FM38" s="79"/>
-      <c r="FN38" s="79"/>
-      <c r="FO38" s="79"/>
-      <c r="FP38" s="79"/>
-      <c r="FQ38" s="79"/>
-      <c r="FR38" s="79"/>
-      <c r="FS38" s="79"/>
-      <c r="FT38" s="79"/>
-      <c r="FU38" s="79"/>
-      <c r="FV38" s="79"/>
-      <c r="FW38" s="79"/>
+      <c r="FB38" s="59"/>
+      <c r="FC38" s="59"/>
+      <c r="FD38" s="59"/>
+      <c r="FE38" s="59"/>
+      <c r="FF38" s="59"/>
+      <c r="FG38" s="59"/>
+      <c r="FH38" s="59"/>
+      <c r="FI38" s="59"/>
+      <c r="FJ38" s="59"/>
+      <c r="FK38" s="59"/>
+      <c r="FL38" s="20"/>
+      <c r="FM38" s="20"/>
+      <c r="FN38" s="20"/>
+      <c r="FO38" s="20"/>
+      <c r="FP38" s="20"/>
+      <c r="FQ38" s="20"/>
+      <c r="FR38" s="20"/>
+      <c r="FS38" s="20"/>
+      <c r="FT38" s="20"/>
+      <c r="FU38" s="20"/>
+      <c r="FV38" s="20"/>
+      <c r="FW38" s="20"/>
       <c r="FX38" s="27"/>
-      <c r="FY38" s="78"/>
+      <c r="FY38" s="39"/>
       <c r="FZ38" s="37"/>
       <c r="GA38" s="37"/>
       <c r="GB38" s="37"/>
@@ -17289,30 +17243,18 @@
       <c r="EY39" s="37"/>
       <c r="EZ39" s="37"/>
       <c r="FA39" s="26"/>
-      <c r="FB39" s="81"/>
-      <c r="FC39" s="81"/>
-      <c r="FD39" s="81"/>
-      <c r="FE39" s="81"/>
-      <c r="FF39" s="81"/>
-      <c r="FG39" s="81"/>
-      <c r="FH39" s="81"/>
-      <c r="FI39" s="81"/>
-      <c r="FJ39" s="81"/>
-      <c r="FK39" s="81"/>
-      <c r="FL39" s="80"/>
-      <c r="FM39" s="80"/>
-      <c r="FN39" s="80"/>
-      <c r="FO39" s="80"/>
-      <c r="FP39" s="80"/>
-      <c r="FQ39" s="80"/>
-      <c r="FR39" s="80"/>
-      <c r="FS39" s="80"/>
-      <c r="FT39" s="80"/>
-      <c r="FU39" s="80"/>
-      <c r="FV39" s="80"/>
-      <c r="FW39" s="80"/>
+      <c r="FB39" s="59"/>
+      <c r="FC39" s="59"/>
+      <c r="FD39" s="59"/>
+      <c r="FE39" s="59"/>
+      <c r="FF39" s="59"/>
+      <c r="FG39" s="59"/>
+      <c r="FH39" s="59"/>
+      <c r="FI39" s="59"/>
+      <c r="FJ39" s="59"/>
+      <c r="FK39" s="59"/>
       <c r="FX39" s="27"/>
-      <c r="FY39" s="78"/>
+      <c r="FY39" s="39"/>
       <c r="FZ39" s="33"/>
       <c r="GA39" s="33"/>
       <c r="GB39" s="33"/>
@@ -17382,42 +17324,42 @@
       <c r="W40" s="12"/>
       <c r="BD40" s="13"/>
       <c r="BF40" s="12"/>
-      <c r="BG40" s="63" t="s">
+      <c r="BG40" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="BH40" s="64"/>
-      <c r="BI40" s="64"/>
-      <c r="BJ40" s="64"/>
-      <c r="BK40" s="64"/>
-      <c r="BL40" s="64"/>
-      <c r="BM40" s="64"/>
-      <c r="BN40" s="64"/>
-      <c r="BO40" s="64"/>
-      <c r="BP40" s="64"/>
-      <c r="BQ40" s="64"/>
-      <c r="BR40" s="64"/>
-      <c r="BS40" s="64"/>
-      <c r="BT40" s="64"/>
-      <c r="BU40" s="64"/>
-      <c r="BV40" s="64"/>
-      <c r="BW40" s="64"/>
-      <c r="BX40" s="64"/>
-      <c r="BY40" s="65"/>
+      <c r="BH40" s="70"/>
+      <c r="BI40" s="70"/>
+      <c r="BJ40" s="70"/>
+      <c r="BK40" s="70"/>
+      <c r="BL40" s="70"/>
+      <c r="BM40" s="70"/>
+      <c r="BN40" s="70"/>
+      <c r="BO40" s="70"/>
+      <c r="BP40" s="70"/>
+      <c r="BQ40" s="70"/>
+      <c r="BR40" s="70"/>
+      <c r="BS40" s="70"/>
+      <c r="BT40" s="70"/>
+      <c r="BU40" s="70"/>
+      <c r="BV40" s="70"/>
+      <c r="BW40" s="70"/>
+      <c r="BX40" s="70"/>
+      <c r="BY40" s="71"/>
       <c r="BZ40" s="20"/>
-      <c r="CA40" s="57" t="s">
+      <c r="CA40" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="CB40" s="58"/>
-      <c r="CC40" s="58"/>
-      <c r="CD40" s="58"/>
-      <c r="CE40" s="59"/>
-      <c r="CG40" s="57" t="s">
+      <c r="CB40" s="61"/>
+      <c r="CC40" s="61"/>
+      <c r="CD40" s="61"/>
+      <c r="CE40" s="62"/>
+      <c r="CG40" s="60" t="s">
         <v>29</v>
       </c>
-      <c r="CH40" s="58"/>
-      <c r="CI40" s="58"/>
-      <c r="CJ40" s="58"/>
-      <c r="CK40" s="59"/>
+      <c r="CH40" s="61"/>
+      <c r="CI40" s="61"/>
+      <c r="CJ40" s="61"/>
+      <c r="CK40" s="62"/>
       <c r="CL40" s="13"/>
       <c r="CM40" s="13"/>
       <c r="CN40" s="2">
@@ -17485,36 +17427,36 @@
       <c r="EY40" s="37"/>
       <c r="EZ40" s="37"/>
       <c r="FA40" s="26"/>
-      <c r="FB40" s="63" t="s">
+      <c r="FB40" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="FC40" s="64"/>
-      <c r="FD40" s="64"/>
-      <c r="FE40" s="64"/>
-      <c r="FF40" s="64"/>
-      <c r="FG40" s="64"/>
-      <c r="FH40" s="64"/>
-      <c r="FI40" s="64"/>
-      <c r="FJ40" s="64"/>
-      <c r="FK40" s="65"/>
-      <c r="FL40" s="79"/>
-      <c r="FM40" s="57" t="s">
+      <c r="FC40" s="70"/>
+      <c r="FD40" s="70"/>
+      <c r="FE40" s="70"/>
+      <c r="FF40" s="70"/>
+      <c r="FG40" s="70"/>
+      <c r="FH40" s="70"/>
+      <c r="FI40" s="70"/>
+      <c r="FJ40" s="70"/>
+      <c r="FK40" s="71"/>
+      <c r="FL40" s="20"/>
+      <c r="FM40" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="FN40" s="58"/>
-      <c r="FO40" s="58"/>
-      <c r="FP40" s="58"/>
-      <c r="FQ40" s="59"/>
-      <c r="FR40" s="79"/>
-      <c r="FS40" s="57" t="s">
+      <c r="FN40" s="61"/>
+      <c r="FO40" s="61"/>
+      <c r="FP40" s="61"/>
+      <c r="FQ40" s="62"/>
+      <c r="FR40" s="20"/>
+      <c r="FS40" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="FT40" s="58"/>
-      <c r="FU40" s="58"/>
-      <c r="FV40" s="58"/>
-      <c r="FW40" s="59"/>
+      <c r="FT40" s="61"/>
+      <c r="FU40" s="61"/>
+      <c r="FV40" s="61"/>
+      <c r="FW40" s="62"/>
       <c r="FX40" s="27"/>
-      <c r="FY40" s="78"/>
+      <c r="FY40" s="39"/>
       <c r="FZ40" s="50"/>
       <c r="GA40" s="50"/>
       <c r="GB40" s="50"/>
@@ -17588,36 +17530,36 @@
       <c r="W41" s="12"/>
       <c r="BD41" s="13"/>
       <c r="BF41" s="12"/>
-      <c r="BG41" s="66"/>
-      <c r="BH41" s="67"/>
-      <c r="BI41" s="67"/>
-      <c r="BJ41" s="67"/>
-      <c r="BK41" s="67"/>
-      <c r="BL41" s="67"/>
-      <c r="BM41" s="67"/>
-      <c r="BN41" s="67"/>
-      <c r="BO41" s="67"/>
-      <c r="BP41" s="67"/>
-      <c r="BQ41" s="67"/>
-      <c r="BR41" s="67"/>
-      <c r="BS41" s="67"/>
-      <c r="BT41" s="67"/>
-      <c r="BU41" s="67"/>
-      <c r="BV41" s="67"/>
-      <c r="BW41" s="67"/>
-      <c r="BX41" s="67"/>
-      <c r="BY41" s="68"/>
+      <c r="BG41" s="72"/>
+      <c r="BH41" s="73"/>
+      <c r="BI41" s="73"/>
+      <c r="BJ41" s="73"/>
+      <c r="BK41" s="73"/>
+      <c r="BL41" s="73"/>
+      <c r="BM41" s="73"/>
+      <c r="BN41" s="73"/>
+      <c r="BO41" s="73"/>
+      <c r="BP41" s="73"/>
+      <c r="BQ41" s="73"/>
+      <c r="BR41" s="73"/>
+      <c r="BS41" s="73"/>
+      <c r="BT41" s="73"/>
+      <c r="BU41" s="73"/>
+      <c r="BV41" s="73"/>
+      <c r="BW41" s="73"/>
+      <c r="BX41" s="73"/>
+      <c r="BY41" s="74"/>
       <c r="BZ41" s="20"/>
-      <c r="CA41" s="60"/>
-      <c r="CB41" s="61"/>
-      <c r="CC41" s="61"/>
-      <c r="CD41" s="61"/>
-      <c r="CE41" s="62"/>
-      <c r="CG41" s="60"/>
-      <c r="CH41" s="61"/>
-      <c r="CI41" s="61"/>
-      <c r="CJ41" s="61"/>
-      <c r="CK41" s="62"/>
+      <c r="CA41" s="63"/>
+      <c r="CB41" s="64"/>
+      <c r="CC41" s="64"/>
+      <c r="CD41" s="64"/>
+      <c r="CE41" s="65"/>
+      <c r="CG41" s="63"/>
+      <c r="CH41" s="64"/>
+      <c r="CI41" s="64"/>
+      <c r="CJ41" s="64"/>
+      <c r="CK41" s="65"/>
       <c r="CL41" s="13"/>
       <c r="CM41" s="13"/>
       <c r="CN41" s="2">
@@ -17685,30 +17627,30 @@
       <c r="EY41" s="37"/>
       <c r="EZ41" s="37"/>
       <c r="FA41" s="26"/>
-      <c r="FB41" s="66"/>
-      <c r="FC41" s="67"/>
-      <c r="FD41" s="67"/>
-      <c r="FE41" s="67"/>
-      <c r="FF41" s="67"/>
-      <c r="FG41" s="67"/>
-      <c r="FH41" s="67"/>
-      <c r="FI41" s="67"/>
-      <c r="FJ41" s="67"/>
-      <c r="FK41" s="68"/>
-      <c r="FL41" s="79"/>
-      <c r="FM41" s="60"/>
-      <c r="FN41" s="61"/>
-      <c r="FO41" s="61"/>
-      <c r="FP41" s="61"/>
-      <c r="FQ41" s="62"/>
-      <c r="FR41" s="79"/>
-      <c r="FS41" s="60"/>
-      <c r="FT41" s="61"/>
-      <c r="FU41" s="61"/>
-      <c r="FV41" s="61"/>
-      <c r="FW41" s="62"/>
+      <c r="FB41" s="72"/>
+      <c r="FC41" s="73"/>
+      <c r="FD41" s="73"/>
+      <c r="FE41" s="73"/>
+      <c r="FF41" s="73"/>
+      <c r="FG41" s="73"/>
+      <c r="FH41" s="73"/>
+      <c r="FI41" s="73"/>
+      <c r="FJ41" s="73"/>
+      <c r="FK41" s="74"/>
+      <c r="FL41" s="20"/>
+      <c r="FM41" s="63"/>
+      <c r="FN41" s="64"/>
+      <c r="FO41" s="64"/>
+      <c r="FP41" s="64"/>
+      <c r="FQ41" s="65"/>
+      <c r="FR41" s="20"/>
+      <c r="FS41" s="63"/>
+      <c r="FT41" s="64"/>
+      <c r="FU41" s="64"/>
+      <c r="FV41" s="64"/>
+      <c r="FW41" s="65"/>
       <c r="FX41" s="27"/>
-      <c r="FY41" s="78"/>
+      <c r="FY41" s="39"/>
       <c r="FZ41" s="53"/>
       <c r="GA41" s="53"/>
       <c r="GB41" s="53"/>
@@ -17845,30 +17787,24 @@
       <c r="EY42" s="37"/>
       <c r="EZ42" s="37"/>
       <c r="FA42" s="26"/>
-      <c r="FB42" s="81"/>
-      <c r="FC42" s="81"/>
-      <c r="FD42" s="81"/>
-      <c r="FE42" s="81"/>
-      <c r="FF42" s="81"/>
-      <c r="FG42" s="81"/>
-      <c r="FH42" s="81"/>
-      <c r="FI42" s="81"/>
-      <c r="FJ42" s="81"/>
-      <c r="FK42" s="81"/>
-      <c r="FL42" s="80"/>
-      <c r="FM42" s="80"/>
-      <c r="FN42" s="80"/>
-      <c r="FO42" s="80"/>
-      <c r="FP42" s="80"/>
-      <c r="FQ42" s="80"/>
-      <c r="FR42" s="79"/>
-      <c r="FS42" s="79"/>
-      <c r="FT42" s="79"/>
-      <c r="FU42" s="79"/>
-      <c r="FV42" s="79"/>
-      <c r="FW42" s="79"/>
+      <c r="FB42" s="59"/>
+      <c r="FC42" s="59"/>
+      <c r="FD42" s="59"/>
+      <c r="FE42" s="59"/>
+      <c r="FF42" s="59"/>
+      <c r="FG42" s="59"/>
+      <c r="FH42" s="59"/>
+      <c r="FI42" s="59"/>
+      <c r="FJ42" s="59"/>
+      <c r="FK42" s="59"/>
+      <c r="FR42" s="20"/>
+      <c r="FS42" s="20"/>
+      <c r="FT42" s="20"/>
+      <c r="FU42" s="20"/>
+      <c r="FV42" s="20"/>
+      <c r="FW42" s="20"/>
       <c r="FX42" s="27"/>
-      <c r="FY42" s="78"/>
+      <c r="FY42" s="39"/>
       <c r="FZ42" s="37"/>
       <c r="GA42" s="37"/>
       <c r="GB42" s="37"/>
@@ -17938,42 +17874,42 @@
       <c r="W43" s="12"/>
       <c r="BD43" s="13"/>
       <c r="BF43" s="12"/>
-      <c r="BG43" s="57" t="s">
+      <c r="BG43" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="BH43" s="58"/>
-      <c r="BI43" s="58"/>
-      <c r="BJ43" s="58"/>
-      <c r="BK43" s="58"/>
-      <c r="BL43" s="58"/>
-      <c r="BM43" s="58"/>
-      <c r="BN43" s="58"/>
-      <c r="BO43" s="58"/>
-      <c r="BP43" s="58"/>
-      <c r="BQ43" s="58"/>
-      <c r="BR43" s="58"/>
-      <c r="BS43" s="58"/>
-      <c r="BT43" s="58"/>
-      <c r="BU43" s="58"/>
-      <c r="BV43" s="58"/>
-      <c r="BW43" s="58"/>
-      <c r="BX43" s="58"/>
-      <c r="BY43" s="59"/>
+      <c r="BH43" s="61"/>
+      <c r="BI43" s="61"/>
+      <c r="BJ43" s="61"/>
+      <c r="BK43" s="61"/>
+      <c r="BL43" s="61"/>
+      <c r="BM43" s="61"/>
+      <c r="BN43" s="61"/>
+      <c r="BO43" s="61"/>
+      <c r="BP43" s="61"/>
+      <c r="BQ43" s="61"/>
+      <c r="BR43" s="61"/>
+      <c r="BS43" s="61"/>
+      <c r="BT43" s="61"/>
+      <c r="BU43" s="61"/>
+      <c r="BV43" s="61"/>
+      <c r="BW43" s="61"/>
+      <c r="BX43" s="61"/>
+      <c r="BY43" s="62"/>
       <c r="BZ43" s="20"/>
-      <c r="CA43" s="57" t="s">
+      <c r="CA43" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="CB43" s="58"/>
-      <c r="CC43" s="58"/>
-      <c r="CD43" s="58"/>
-      <c r="CE43" s="59"/>
-      <c r="CG43" s="57" t="s">
+      <c r="CB43" s="61"/>
+      <c r="CC43" s="61"/>
+      <c r="CD43" s="61"/>
+      <c r="CE43" s="62"/>
+      <c r="CG43" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="CH43" s="58"/>
-      <c r="CI43" s="58"/>
-      <c r="CJ43" s="58"/>
-      <c r="CK43" s="59"/>
+      <c r="CH43" s="61"/>
+      <c r="CI43" s="61"/>
+      <c r="CJ43" s="61"/>
+      <c r="CK43" s="62"/>
       <c r="CL43" s="13"/>
       <c r="CM43" s="13"/>
       <c r="CN43" s="2">
@@ -18041,34 +17977,34 @@
       <c r="EY43" s="37"/>
       <c r="EZ43" s="37"/>
       <c r="FA43" s="26"/>
-      <c r="FB43" s="63" t="s">
+      <c r="FB43" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="FC43" s="64"/>
-      <c r="FD43" s="64"/>
-      <c r="FE43" s="64"/>
-      <c r="FF43" s="64"/>
-      <c r="FG43" s="64"/>
-      <c r="FH43" s="64"/>
-      <c r="FI43" s="64"/>
-      <c r="FJ43" s="64"/>
-      <c r="FK43" s="65"/>
-      <c r="FL43" s="79"/>
-      <c r="FM43" s="57" t="s">
+      <c r="FC43" s="70"/>
+      <c r="FD43" s="70"/>
+      <c r="FE43" s="70"/>
+      <c r="FF43" s="70"/>
+      <c r="FG43" s="70"/>
+      <c r="FH43" s="70"/>
+      <c r="FI43" s="70"/>
+      <c r="FJ43" s="70"/>
+      <c r="FK43" s="71"/>
+      <c r="FL43" s="20"/>
+      <c r="FM43" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="FN43" s="58"/>
-      <c r="FO43" s="58"/>
-      <c r="FP43" s="58"/>
-      <c r="FQ43" s="59"/>
-      <c r="FR43" s="79"/>
-      <c r="FS43" s="79"/>
-      <c r="FT43" s="79"/>
-      <c r="FU43" s="79"/>
-      <c r="FV43" s="79"/>
-      <c r="FW43" s="79"/>
+      <c r="FN43" s="61"/>
+      <c r="FO43" s="61"/>
+      <c r="FP43" s="61"/>
+      <c r="FQ43" s="62"/>
+      <c r="FR43" s="20"/>
+      <c r="FS43" s="20"/>
+      <c r="FT43" s="20"/>
+      <c r="FU43" s="20"/>
+      <c r="FV43" s="20"/>
+      <c r="FW43" s="20"/>
       <c r="FX43" s="27"/>
-      <c r="FY43" s="78"/>
+      <c r="FY43" s="39"/>
       <c r="FZ43" s="50"/>
       <c r="GA43" s="50"/>
       <c r="GB43" s="50"/>
@@ -18142,36 +18078,36 @@
       <c r="W44" s="12"/>
       <c r="BD44" s="13"/>
       <c r="BF44" s="12"/>
-      <c r="BG44" s="60"/>
-      <c r="BH44" s="61"/>
-      <c r="BI44" s="61"/>
-      <c r="BJ44" s="61"/>
-      <c r="BK44" s="61"/>
-      <c r="BL44" s="61"/>
-      <c r="BM44" s="61"/>
-      <c r="BN44" s="61"/>
-      <c r="BO44" s="61"/>
-      <c r="BP44" s="61"/>
-      <c r="BQ44" s="61"/>
-      <c r="BR44" s="61"/>
-      <c r="BS44" s="61"/>
-      <c r="BT44" s="61"/>
-      <c r="BU44" s="61"/>
-      <c r="BV44" s="61"/>
-      <c r="BW44" s="61"/>
-      <c r="BX44" s="61"/>
-      <c r="BY44" s="62"/>
+      <c r="BG44" s="63"/>
+      <c r="BH44" s="64"/>
+      <c r="BI44" s="64"/>
+      <c r="BJ44" s="64"/>
+      <c r="BK44" s="64"/>
+      <c r="BL44" s="64"/>
+      <c r="BM44" s="64"/>
+      <c r="BN44" s="64"/>
+      <c r="BO44" s="64"/>
+      <c r="BP44" s="64"/>
+      <c r="BQ44" s="64"/>
+      <c r="BR44" s="64"/>
+      <c r="BS44" s="64"/>
+      <c r="BT44" s="64"/>
+      <c r="BU44" s="64"/>
+      <c r="BV44" s="64"/>
+      <c r="BW44" s="64"/>
+      <c r="BX44" s="64"/>
+      <c r="BY44" s="65"/>
       <c r="BZ44" s="20"/>
-      <c r="CA44" s="60"/>
-      <c r="CB44" s="61"/>
-      <c r="CC44" s="61"/>
-      <c r="CD44" s="61"/>
-      <c r="CE44" s="62"/>
-      <c r="CG44" s="60"/>
-      <c r="CH44" s="61"/>
-      <c r="CI44" s="61"/>
-      <c r="CJ44" s="61"/>
-      <c r="CK44" s="62"/>
+      <c r="CA44" s="63"/>
+      <c r="CB44" s="64"/>
+      <c r="CC44" s="64"/>
+      <c r="CD44" s="64"/>
+      <c r="CE44" s="65"/>
+      <c r="CG44" s="63"/>
+      <c r="CH44" s="64"/>
+      <c r="CI44" s="64"/>
+      <c r="CJ44" s="64"/>
+      <c r="CK44" s="65"/>
       <c r="CL44" s="13"/>
       <c r="CM44" s="13"/>
       <c r="CN44" s="2">
@@ -18239,30 +18175,30 @@
       <c r="EY44" s="37"/>
       <c r="EZ44" s="37"/>
       <c r="FA44" s="26"/>
-      <c r="FB44" s="66"/>
-      <c r="FC44" s="67"/>
-      <c r="FD44" s="67"/>
-      <c r="FE44" s="67"/>
-      <c r="FF44" s="67"/>
-      <c r="FG44" s="67"/>
-      <c r="FH44" s="67"/>
-      <c r="FI44" s="67"/>
-      <c r="FJ44" s="67"/>
-      <c r="FK44" s="68"/>
-      <c r="FL44" s="79"/>
-      <c r="FM44" s="60"/>
-      <c r="FN44" s="61"/>
-      <c r="FO44" s="61"/>
-      <c r="FP44" s="61"/>
-      <c r="FQ44" s="62"/>
-      <c r="FR44" s="79"/>
-      <c r="FS44" s="79"/>
-      <c r="FT44" s="79"/>
-      <c r="FU44" s="79"/>
-      <c r="FV44" s="79"/>
-      <c r="FW44" s="79"/>
+      <c r="FB44" s="72"/>
+      <c r="FC44" s="73"/>
+      <c r="FD44" s="73"/>
+      <c r="FE44" s="73"/>
+      <c r="FF44" s="73"/>
+      <c r="FG44" s="73"/>
+      <c r="FH44" s="73"/>
+      <c r="FI44" s="73"/>
+      <c r="FJ44" s="73"/>
+      <c r="FK44" s="74"/>
+      <c r="FL44" s="20"/>
+      <c r="FM44" s="63"/>
+      <c r="FN44" s="64"/>
+      <c r="FO44" s="64"/>
+      <c r="FP44" s="64"/>
+      <c r="FQ44" s="65"/>
+      <c r="FR44" s="20"/>
+      <c r="FS44" s="20"/>
+      <c r="FT44" s="20"/>
+      <c r="FU44" s="20"/>
+      <c r="FV44" s="20"/>
+      <c r="FW44" s="20"/>
       <c r="FX44" s="27"/>
-      <c r="FY44" s="78"/>
+      <c r="FY44" s="39"/>
       <c r="FZ44" s="53"/>
       <c r="GA44" s="53"/>
       <c r="GB44" s="53"/>
@@ -18399,30 +18335,24 @@
       <c r="EY45" s="37"/>
       <c r="EZ45" s="37"/>
       <c r="FA45" s="26"/>
-      <c r="FB45" s="81"/>
-      <c r="FC45" s="81"/>
-      <c r="FD45" s="81"/>
-      <c r="FE45" s="81"/>
-      <c r="FF45" s="81"/>
-      <c r="FG45" s="81"/>
-      <c r="FH45" s="81"/>
-      <c r="FI45" s="81"/>
-      <c r="FJ45" s="81"/>
-      <c r="FK45" s="81"/>
-      <c r="FL45" s="80"/>
-      <c r="FM45" s="80"/>
-      <c r="FN45" s="80"/>
-      <c r="FO45" s="80"/>
-      <c r="FP45" s="80"/>
-      <c r="FQ45" s="80"/>
-      <c r="FR45" s="79"/>
-      <c r="FS45" s="79"/>
-      <c r="FT45" s="79"/>
-      <c r="FU45" s="79"/>
-      <c r="FV45" s="79"/>
-      <c r="FW45" s="79"/>
+      <c r="FB45" s="59"/>
+      <c r="FC45" s="59"/>
+      <c r="FD45" s="59"/>
+      <c r="FE45" s="59"/>
+      <c r="FF45" s="59"/>
+      <c r="FG45" s="59"/>
+      <c r="FH45" s="59"/>
+      <c r="FI45" s="59"/>
+      <c r="FJ45" s="59"/>
+      <c r="FK45" s="59"/>
+      <c r="FR45" s="20"/>
+      <c r="FS45" s="20"/>
+      <c r="FT45" s="20"/>
+      <c r="FU45" s="20"/>
+      <c r="FV45" s="20"/>
+      <c r="FW45" s="20"/>
       <c r="FX45" s="27"/>
-      <c r="FY45" s="78"/>
+      <c r="FY45" s="39"/>
       <c r="FZ45" s="37"/>
       <c r="GA45" s="37"/>
       <c r="GB45" s="37"/>
@@ -18492,25 +18422,25 @@
       <c r="W46" s="12"/>
       <c r="BD46" s="13"/>
       <c r="BF46" s="12"/>
-      <c r="BG46" s="63" t="s">
+      <c r="BG46" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="BH46" s="64"/>
-      <c r="BI46" s="64"/>
-      <c r="BJ46" s="64"/>
-      <c r="BK46" s="64"/>
-      <c r="BL46" s="64"/>
-      <c r="BM46" s="64"/>
-      <c r="BN46" s="64"/>
-      <c r="BO46" s="64"/>
-      <c r="BP46" s="65"/>
-      <c r="CA46" s="57" t="s">
+      <c r="BH46" s="70"/>
+      <c r="BI46" s="70"/>
+      <c r="BJ46" s="70"/>
+      <c r="BK46" s="70"/>
+      <c r="BL46" s="70"/>
+      <c r="BM46" s="70"/>
+      <c r="BN46" s="70"/>
+      <c r="BO46" s="70"/>
+      <c r="BP46" s="71"/>
+      <c r="CA46" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="CB46" s="58"/>
-      <c r="CC46" s="58"/>
-      <c r="CD46" s="58"/>
-      <c r="CE46" s="59"/>
+      <c r="CB46" s="61"/>
+      <c r="CC46" s="61"/>
+      <c r="CD46" s="61"/>
+      <c r="CE46" s="62"/>
       <c r="CG46" s="20"/>
       <c r="CH46" s="20"/>
       <c r="CI46" s="20"/>
@@ -18583,34 +18513,34 @@
       <c r="EY46" s="37"/>
       <c r="EZ46" s="37"/>
       <c r="FA46" s="26"/>
-      <c r="FB46" s="63" t="s">
+      <c r="FB46" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="FC46" s="64"/>
-      <c r="FD46" s="64"/>
-      <c r="FE46" s="64"/>
-      <c r="FF46" s="64"/>
-      <c r="FG46" s="64"/>
-      <c r="FH46" s="64"/>
-      <c r="FI46" s="64"/>
-      <c r="FJ46" s="64"/>
-      <c r="FK46" s="65"/>
-      <c r="FL46" s="79"/>
-      <c r="FM46" s="57" t="s">
+      <c r="FC46" s="70"/>
+      <c r="FD46" s="70"/>
+      <c r="FE46" s="70"/>
+      <c r="FF46" s="70"/>
+      <c r="FG46" s="70"/>
+      <c r="FH46" s="70"/>
+      <c r="FI46" s="70"/>
+      <c r="FJ46" s="70"/>
+      <c r="FK46" s="71"/>
+      <c r="FL46" s="20"/>
+      <c r="FM46" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="FN46" s="58"/>
-      <c r="FO46" s="58"/>
-      <c r="FP46" s="58"/>
-      <c r="FQ46" s="59"/>
-      <c r="FR46" s="79"/>
-      <c r="FS46" s="79"/>
-      <c r="FT46" s="79"/>
-      <c r="FU46" s="79"/>
-      <c r="FV46" s="79"/>
-      <c r="FW46" s="79"/>
+      <c r="FN46" s="61"/>
+      <c r="FO46" s="61"/>
+      <c r="FP46" s="61"/>
+      <c r="FQ46" s="62"/>
+      <c r="FR46" s="20"/>
+      <c r="FS46" s="20"/>
+      <c r="FT46" s="20"/>
+      <c r="FU46" s="20"/>
+      <c r="FV46" s="20"/>
+      <c r="FW46" s="20"/>
       <c r="FX46" s="27"/>
-      <c r="FY46" s="78"/>
+      <c r="FY46" s="39"/>
       <c r="FZ46" s="37"/>
       <c r="GA46" s="37"/>
       <c r="GB46" s="37"/>
@@ -18682,21 +18612,21 @@
       <c r="W47" s="12"/>
       <c r="BD47" s="13"/>
       <c r="BF47" s="12"/>
-      <c r="BG47" s="66"/>
-      <c r="BH47" s="67"/>
-      <c r="BI47" s="67"/>
-      <c r="BJ47" s="67"/>
-      <c r="BK47" s="67"/>
-      <c r="BL47" s="67"/>
-      <c r="BM47" s="67"/>
-      <c r="BN47" s="67"/>
-      <c r="BO47" s="67"/>
-      <c r="BP47" s="68"/>
-      <c r="CA47" s="60"/>
-      <c r="CB47" s="61"/>
-      <c r="CC47" s="61"/>
-      <c r="CD47" s="61"/>
-      <c r="CE47" s="62"/>
+      <c r="BG47" s="72"/>
+      <c r="BH47" s="73"/>
+      <c r="BI47" s="73"/>
+      <c r="BJ47" s="73"/>
+      <c r="BK47" s="73"/>
+      <c r="BL47" s="73"/>
+      <c r="BM47" s="73"/>
+      <c r="BN47" s="73"/>
+      <c r="BO47" s="73"/>
+      <c r="BP47" s="74"/>
+      <c r="CA47" s="63"/>
+      <c r="CB47" s="64"/>
+      <c r="CC47" s="64"/>
+      <c r="CD47" s="64"/>
+      <c r="CE47" s="65"/>
       <c r="CG47" s="20"/>
       <c r="CH47" s="20"/>
       <c r="CI47" s="20"/>
@@ -18769,30 +18699,30 @@
       <c r="EY47" s="37"/>
       <c r="EZ47" s="37"/>
       <c r="FA47" s="26"/>
-      <c r="FB47" s="66"/>
-      <c r="FC47" s="67"/>
-      <c r="FD47" s="67"/>
-      <c r="FE47" s="67"/>
-      <c r="FF47" s="67"/>
-      <c r="FG47" s="67"/>
-      <c r="FH47" s="67"/>
-      <c r="FI47" s="67"/>
-      <c r="FJ47" s="67"/>
-      <c r="FK47" s="68"/>
-      <c r="FL47" s="79"/>
-      <c r="FM47" s="60"/>
-      <c r="FN47" s="61"/>
-      <c r="FO47" s="61"/>
-      <c r="FP47" s="61"/>
-      <c r="FQ47" s="62"/>
-      <c r="FR47" s="79"/>
-      <c r="FS47" s="79"/>
-      <c r="FT47" s="79"/>
-      <c r="FU47" s="79"/>
-      <c r="FV47" s="79"/>
-      <c r="FW47" s="79"/>
+      <c r="FB47" s="72"/>
+      <c r="FC47" s="73"/>
+      <c r="FD47" s="73"/>
+      <c r="FE47" s="73"/>
+      <c r="FF47" s="73"/>
+      <c r="FG47" s="73"/>
+      <c r="FH47" s="73"/>
+      <c r="FI47" s="73"/>
+      <c r="FJ47" s="73"/>
+      <c r="FK47" s="74"/>
+      <c r="FL47" s="20"/>
+      <c r="FM47" s="63"/>
+      <c r="FN47" s="64"/>
+      <c r="FO47" s="64"/>
+      <c r="FP47" s="64"/>
+      <c r="FQ47" s="65"/>
+      <c r="FR47" s="20"/>
+      <c r="FS47" s="20"/>
+      <c r="FT47" s="20"/>
+      <c r="FU47" s="20"/>
+      <c r="FV47" s="20"/>
+      <c r="FW47" s="20"/>
       <c r="FX47" s="27"/>
-      <c r="FY47" s="78"/>
+      <c r="FY47" s="39"/>
       <c r="FZ47" s="37"/>
       <c r="GA47" s="37"/>
       <c r="GB47" s="37"/>
@@ -18938,18 +18868,6 @@
       </c>
       <c r="ED48" s="12"/>
       <c r="EE48" s="12"/>
-      <c r="EN48" s="75"/>
-      <c r="EO48" s="75"/>
-      <c r="EP48" s="75"/>
-      <c r="EQ48" s="75"/>
-      <c r="ER48" s="75"/>
-      <c r="ES48" s="75"/>
-      <c r="ET48" s="75"/>
-      <c r="EU48" s="75"/>
-      <c r="EV48" s="75"/>
-      <c r="EW48" s="75"/>
-      <c r="EX48" s="75"/>
-      <c r="EY48" s="75"/>
       <c r="EZ48" s="37"/>
       <c r="FA48" s="14"/>
       <c r="FB48" s="15"/>
@@ -18975,7 +18893,7 @@
       <c r="FV48" s="15"/>
       <c r="FW48" s="15"/>
       <c r="FX48" s="16"/>
-      <c r="FY48" s="77"/>
+      <c r="FY48" s="37"/>
       <c r="FZ48" s="41"/>
       <c r="GA48" s="41"/>
       <c r="GB48" s="41"/>
@@ -19166,7 +19084,7 @@
       <c r="FV49" s="43"/>
       <c r="FW49" s="43"/>
       <c r="FX49" s="43"/>
-      <c r="FY49" s="78"/>
+      <c r="FY49" s="39"/>
       <c r="FZ49" s="43"/>
       <c r="GA49" s="43"/>
       <c r="GB49" s="43"/>
@@ -19235,18 +19153,18 @@
       <c r="V50" s="12"/>
       <c r="W50" s="12"/>
       <c r="BD50" s="13"/>
-      <c r="BF50" s="63" t="s">
+      <c r="BF50" s="69" t="s">
         <v>6</v>
       </c>
-      <c r="BG50" s="64"/>
-      <c r="BH50" s="64"/>
-      <c r="BI50" s="64"/>
-      <c r="BJ50" s="64"/>
-      <c r="BK50" s="64"/>
-      <c r="BL50" s="64"/>
-      <c r="BM50" s="64"/>
-      <c r="BN50" s="64"/>
-      <c r="BO50" s="65"/>
+      <c r="BG50" s="70"/>
+      <c r="BH50" s="70"/>
+      <c r="BI50" s="70"/>
+      <c r="BJ50" s="70"/>
+      <c r="BK50" s="70"/>
+      <c r="BL50" s="70"/>
+      <c r="BM50" s="70"/>
+      <c r="BN50" s="70"/>
+      <c r="BO50" s="71"/>
       <c r="BP50" s="20"/>
       <c r="BQ50" s="20"/>
       <c r="BR50" s="20"/>
@@ -19255,22 +19173,22 @@
       <c r="BU50" s="20"/>
       <c r="BY50" s="20"/>
       <c r="BZ50" s="20"/>
-      <c r="CA50" s="57" t="s">
+      <c r="CA50" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="CB50" s="58"/>
-      <c r="CC50" s="58"/>
-      <c r="CD50" s="58"/>
-      <c r="CE50" s="58"/>
-      <c r="CF50" s="58"/>
-      <c r="CG50" s="59"/>
-      <c r="CH50" s="57" t="s">
+      <c r="CB50" s="61"/>
+      <c r="CC50" s="61"/>
+      <c r="CD50" s="61"/>
+      <c r="CE50" s="61"/>
+      <c r="CF50" s="61"/>
+      <c r="CG50" s="62"/>
+      <c r="CH50" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="CI50" s="58"/>
-      <c r="CJ50" s="58"/>
-      <c r="CK50" s="58"/>
-      <c r="CL50" s="59"/>
+      <c r="CI50" s="61"/>
+      <c r="CJ50" s="61"/>
+      <c r="CK50" s="61"/>
+      <c r="CL50" s="62"/>
       <c r="CM50" s="13"/>
       <c r="CN50" s="2">
         <f t="shared" si="109"/>
@@ -19435,16 +19353,16 @@
       <c r="V51" s="12"/>
       <c r="W51" s="12"/>
       <c r="BD51" s="13"/>
-      <c r="BF51" s="66"/>
-      <c r="BG51" s="67"/>
-      <c r="BH51" s="67"/>
-      <c r="BI51" s="67"/>
-      <c r="BJ51" s="67"/>
-      <c r="BK51" s="67"/>
-      <c r="BL51" s="67"/>
-      <c r="BM51" s="67"/>
-      <c r="BN51" s="67"/>
-      <c r="BO51" s="68"/>
+      <c r="BF51" s="72"/>
+      <c r="BG51" s="73"/>
+      <c r="BH51" s="73"/>
+      <c r="BI51" s="73"/>
+      <c r="BJ51" s="73"/>
+      <c r="BK51" s="73"/>
+      <c r="BL51" s="73"/>
+      <c r="BM51" s="73"/>
+      <c r="BN51" s="73"/>
+      <c r="BO51" s="74"/>
       <c r="BP51" s="20"/>
       <c r="BQ51" s="20"/>
       <c r="BR51" s="20"/>
@@ -19453,18 +19371,18 @@
       <c r="BU51" s="20"/>
       <c r="BY51" s="20"/>
       <c r="BZ51" s="20"/>
-      <c r="CA51" s="60"/>
-      <c r="CB51" s="61"/>
-      <c r="CC51" s="61"/>
-      <c r="CD51" s="61"/>
-      <c r="CE51" s="61"/>
-      <c r="CF51" s="61"/>
-      <c r="CG51" s="62"/>
-      <c r="CH51" s="60"/>
-      <c r="CI51" s="61"/>
-      <c r="CJ51" s="61"/>
-      <c r="CK51" s="61"/>
-      <c r="CL51" s="62"/>
+      <c r="CA51" s="63"/>
+      <c r="CB51" s="64"/>
+      <c r="CC51" s="64"/>
+      <c r="CD51" s="64"/>
+      <c r="CE51" s="64"/>
+      <c r="CF51" s="64"/>
+      <c r="CG51" s="65"/>
+      <c r="CH51" s="63"/>
+      <c r="CI51" s="64"/>
+      <c r="CJ51" s="64"/>
+      <c r="CK51" s="64"/>
+      <c r="CL51" s="65"/>
       <c r="CM51" s="13"/>
       <c r="CN51" s="2">
         <f t="shared" si="109"/>
@@ -19974,13 +19892,13 @@
       <c r="BD54" s="13"/>
       <c r="BF54" s="12"/>
       <c r="CE54" s="11"/>
-      <c r="CG54" s="57" t="s">
+      <c r="CG54" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="CH54" s="58"/>
-      <c r="CI54" s="58"/>
-      <c r="CJ54" s="58"/>
-      <c r="CK54" s="59"/>
+      <c r="CH54" s="61"/>
+      <c r="CI54" s="61"/>
+      <c r="CJ54" s="61"/>
+      <c r="CK54" s="62"/>
       <c r="CL54" s="13"/>
       <c r="CM54" s="13"/>
       <c r="CN54" s="2">
@@ -20144,11 +20062,11 @@
       <c r="BD55" s="13"/>
       <c r="BF55" s="12"/>
       <c r="CE55" s="11"/>
-      <c r="CG55" s="60"/>
-      <c r="CH55" s="61"/>
-      <c r="CI55" s="61"/>
-      <c r="CJ55" s="61"/>
-      <c r="CK55" s="62"/>
+      <c r="CG55" s="63"/>
+      <c r="CH55" s="64"/>
+      <c r="CI55" s="64"/>
+      <c r="CJ55" s="64"/>
+      <c r="CK55" s="65"/>
       <c r="CL55" s="13"/>
       <c r="CM55" s="13"/>
       <c r="CN55" s="2">
@@ -20471,13 +20389,13 @@
       <c r="BD57" s="13"/>
       <c r="BF57" s="12"/>
       <c r="CE57" s="11"/>
-      <c r="CG57" s="57" t="s">
+      <c r="CG57" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="CH57" s="58"/>
-      <c r="CI57" s="58"/>
-      <c r="CJ57" s="58"/>
-      <c r="CK57" s="59"/>
+      <c r="CH57" s="61"/>
+      <c r="CI57" s="61"/>
+      <c r="CJ57" s="61"/>
+      <c r="CK57" s="62"/>
       <c r="CL57" s="13"/>
       <c r="CM57" s="13"/>
       <c r="CN57" s="2">
@@ -20641,11 +20559,11 @@
       <c r="BD58" s="13"/>
       <c r="BF58" s="12"/>
       <c r="CE58" s="11"/>
-      <c r="CG58" s="60"/>
-      <c r="CH58" s="61"/>
-      <c r="CI58" s="61"/>
-      <c r="CJ58" s="61"/>
-      <c r="CK58" s="62"/>
+      <c r="CG58" s="63"/>
+      <c r="CH58" s="64"/>
+      <c r="CI58" s="64"/>
+      <c r="CJ58" s="64"/>
+      <c r="CK58" s="65"/>
       <c r="CL58" s="13"/>
       <c r="CM58" s="13"/>
       <c r="CN58" s="2">
@@ -20968,13 +20886,13 @@
       <c r="BD60" s="13"/>
       <c r="BF60" s="12"/>
       <c r="CE60" s="11"/>
-      <c r="CG60" s="57" t="s">
+      <c r="CG60" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="CH60" s="58"/>
-      <c r="CI60" s="58"/>
-      <c r="CJ60" s="58"/>
-      <c r="CK60" s="59"/>
+      <c r="CH60" s="61"/>
+      <c r="CI60" s="61"/>
+      <c r="CJ60" s="61"/>
+      <c r="CK60" s="62"/>
       <c r="CL60" s="13"/>
       <c r="CM60" s="13"/>
       <c r="CN60" s="2">
@@ -21138,11 +21056,11 @@
       <c r="BD61" s="13"/>
       <c r="BF61" s="12"/>
       <c r="CE61" s="11"/>
-      <c r="CG61" s="60"/>
-      <c r="CH61" s="61"/>
-      <c r="CI61" s="61"/>
-      <c r="CJ61" s="61"/>
-      <c r="CK61" s="62"/>
+      <c r="CG61" s="63"/>
+      <c r="CH61" s="64"/>
+      <c r="CI61" s="64"/>
+      <c r="CJ61" s="64"/>
+      <c r="CK61" s="65"/>
       <c r="CL61" s="13"/>
       <c r="CM61" s="13"/>
       <c r="CN61" s="2">
@@ -21465,13 +21383,13 @@
       <c r="BD63" s="13"/>
       <c r="BF63" s="12"/>
       <c r="CE63" s="11"/>
-      <c r="CG63" s="57" t="s">
+      <c r="CG63" s="60" t="s">
         <v>34</v>
       </c>
-      <c r="CH63" s="58"/>
-      <c r="CI63" s="58"/>
-      <c r="CJ63" s="58"/>
-      <c r="CK63" s="59"/>
+      <c r="CH63" s="61"/>
+      <c r="CI63" s="61"/>
+      <c r="CJ63" s="61"/>
+      <c r="CK63" s="62"/>
       <c r="CL63" s="13"/>
       <c r="CM63" s="13"/>
       <c r="CN63" s="2">
@@ -21635,11 +21553,11 @@
       <c r="BD64" s="13"/>
       <c r="BF64" s="12"/>
       <c r="CE64" s="11"/>
-      <c r="CG64" s="60"/>
-      <c r="CH64" s="61"/>
-      <c r="CI64" s="61"/>
-      <c r="CJ64" s="61"/>
-      <c r="CK64" s="62"/>
+      <c r="CG64" s="63"/>
+      <c r="CH64" s="64"/>
+      <c r="CI64" s="64"/>
+      <c r="CJ64" s="64"/>
+      <c r="CK64" s="65"/>
       <c r="CL64" s="13"/>
       <c r="CM64" s="13"/>
       <c r="CN64" s="2">
@@ -21962,13 +21880,13 @@
       <c r="BD66" s="13"/>
       <c r="BF66" s="12"/>
       <c r="CE66" s="11"/>
-      <c r="CG66" s="57" t="s">
+      <c r="CG66" s="60" t="s">
         <v>35</v>
       </c>
-      <c r="CH66" s="58"/>
-      <c r="CI66" s="58"/>
-      <c r="CJ66" s="58"/>
-      <c r="CK66" s="59"/>
+      <c r="CH66" s="61"/>
+      <c r="CI66" s="61"/>
+      <c r="CJ66" s="61"/>
+      <c r="CK66" s="62"/>
       <c r="CL66" s="13"/>
       <c r="CM66" s="13"/>
       <c r="CN66" s="2">
@@ -22132,11 +22050,11 @@
       <c r="BD67" s="13"/>
       <c r="BF67" s="12"/>
       <c r="CE67" s="11"/>
-      <c r="CG67" s="60"/>
-      <c r="CH67" s="61"/>
-      <c r="CI67" s="61"/>
-      <c r="CJ67" s="61"/>
-      <c r="CK67" s="62"/>
+      <c r="CG67" s="63"/>
+      <c r="CH67" s="64"/>
+      <c r="CI67" s="64"/>
+      <c r="CJ67" s="64"/>
+      <c r="CK67" s="65"/>
       <c r="CL67" s="13"/>
       <c r="CM67" s="13"/>
       <c r="CN67" s="2">
@@ -22943,13 +22861,13 @@
       <c r="BD72" s="13"/>
       <c r="BF72" s="12"/>
       <c r="CE72" s="11"/>
-      <c r="CG72" s="57" t="s">
+      <c r="CG72" s="60" t="s">
         <v>40</v>
       </c>
-      <c r="CH72" s="58"/>
-      <c r="CI72" s="58"/>
-      <c r="CJ72" s="58"/>
-      <c r="CK72" s="59"/>
+      <c r="CH72" s="61"/>
+      <c r="CI72" s="61"/>
+      <c r="CJ72" s="61"/>
+      <c r="CK72" s="62"/>
       <c r="CL72" s="13"/>
       <c r="CM72" s="13"/>
       <c r="CN72" s="2">
@@ -23113,11 +23031,11 @@
       <c r="BD73" s="13"/>
       <c r="BF73" s="12"/>
       <c r="CE73" s="11"/>
-      <c r="CG73" s="60"/>
-      <c r="CH73" s="61"/>
-      <c r="CI73" s="61"/>
-      <c r="CJ73" s="61"/>
-      <c r="CK73" s="62"/>
+      <c r="CG73" s="63"/>
+      <c r="CH73" s="64"/>
+      <c r="CI73" s="64"/>
+      <c r="CJ73" s="64"/>
+      <c r="CK73" s="65"/>
       <c r="CL73" s="13"/>
       <c r="CM73" s="13"/>
       <c r="CN73" s="2">
@@ -25908,26 +25826,26 @@
         <v>83</v>
       </c>
       <c r="V90" s="12"/>
-      <c r="W90" s="57" t="s">
+      <c r="W90" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="X90" s="58"/>
-      <c r="Y90" s="58"/>
-      <c r="Z90" s="58"/>
-      <c r="AA90" s="58"/>
-      <c r="AB90" s="58"/>
-      <c r="AC90" s="58"/>
-      <c r="AD90" s="59"/>
-      <c r="AF90" s="57" t="s">
+      <c r="X90" s="61"/>
+      <c r="Y90" s="61"/>
+      <c r="Z90" s="61"/>
+      <c r="AA90" s="61"/>
+      <c r="AB90" s="61"/>
+      <c r="AC90" s="61"/>
+      <c r="AD90" s="62"/>
+      <c r="AF90" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="AG90" s="58"/>
-      <c r="AH90" s="58"/>
-      <c r="AI90" s="58"/>
-      <c r="AJ90" s="58"/>
-      <c r="AK90" s="58"/>
-      <c r="AL90" s="58"/>
-      <c r="AM90" s="59"/>
+      <c r="AG90" s="61"/>
+      <c r="AH90" s="61"/>
+      <c r="AI90" s="61"/>
+      <c r="AJ90" s="61"/>
+      <c r="AK90" s="61"/>
+      <c r="AL90" s="61"/>
+      <c r="AM90" s="62"/>
       <c r="CM90" s="13"/>
       <c r="CN90" s="2">
         <f t="shared" si="117"/>
@@ -26086,22 +26004,22 @@
         <v>84</v>
       </c>
       <c r="V91" s="12"/>
-      <c r="W91" s="60"/>
-      <c r="X91" s="61"/>
-      <c r="Y91" s="61"/>
-      <c r="Z91" s="61"/>
-      <c r="AA91" s="61"/>
-      <c r="AB91" s="61"/>
-      <c r="AC91" s="61"/>
-      <c r="AD91" s="62"/>
-      <c r="AF91" s="60"/>
-      <c r="AG91" s="61"/>
-      <c r="AH91" s="61"/>
-      <c r="AI91" s="61"/>
-      <c r="AJ91" s="61"/>
-      <c r="AK91" s="61"/>
-      <c r="AL91" s="61"/>
-      <c r="AM91" s="62"/>
+      <c r="W91" s="63"/>
+      <c r="X91" s="64"/>
+      <c r="Y91" s="64"/>
+      <c r="Z91" s="64"/>
+      <c r="AA91" s="64"/>
+      <c r="AB91" s="64"/>
+      <c r="AC91" s="64"/>
+      <c r="AD91" s="65"/>
+      <c r="AF91" s="63"/>
+      <c r="AG91" s="64"/>
+      <c r="AH91" s="64"/>
+      <c r="AI91" s="64"/>
+      <c r="AJ91" s="64"/>
+      <c r="AK91" s="64"/>
+      <c r="AL91" s="64"/>
+      <c r="AM91" s="65"/>
       <c r="AZ91" s="20"/>
       <c r="BA91" s="20"/>
       <c r="BB91" s="20"/>
@@ -26112,18 +26030,18 @@
       <c r="BG91" s="20"/>
       <c r="BH91" s="20"/>
       <c r="BI91" s="20"/>
-      <c r="CC91" s="57" t="s">
+      <c r="CC91" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="CD91" s="58"/>
-      <c r="CE91" s="58"/>
-      <c r="CF91" s="58"/>
-      <c r="CG91" s="58"/>
-      <c r="CH91" s="58"/>
-      <c r="CI91" s="58"/>
-      <c r="CJ91" s="58"/>
-      <c r="CK91" s="58"/>
-      <c r="CL91" s="59"/>
+      <c r="CD91" s="61"/>
+      <c r="CE91" s="61"/>
+      <c r="CF91" s="61"/>
+      <c r="CG91" s="61"/>
+      <c r="CH91" s="61"/>
+      <c r="CI91" s="61"/>
+      <c r="CJ91" s="61"/>
+      <c r="CK91" s="61"/>
+      <c r="CL91" s="62"/>
       <c r="CM91" s="13"/>
       <c r="CN91" s="2">
         <f t="shared" si="117"/>
@@ -26292,16 +26210,16 @@
       <c r="BG92" s="20"/>
       <c r="BH92" s="20"/>
       <c r="BI92" s="20"/>
-      <c r="CC92" s="69"/>
-      <c r="CD92" s="70"/>
-      <c r="CE92" s="70"/>
-      <c r="CF92" s="70"/>
-      <c r="CG92" s="70"/>
-      <c r="CH92" s="70"/>
-      <c r="CI92" s="70"/>
-      <c r="CJ92" s="70"/>
-      <c r="CK92" s="70"/>
-      <c r="CL92" s="71"/>
+      <c r="CC92" s="66"/>
+      <c r="CD92" s="67"/>
+      <c r="CE92" s="67"/>
+      <c r="CF92" s="67"/>
+      <c r="CG92" s="67"/>
+      <c r="CH92" s="67"/>
+      <c r="CI92" s="67"/>
+      <c r="CJ92" s="67"/>
+      <c r="CK92" s="67"/>
+      <c r="CL92" s="68"/>
       <c r="CM92" s="13"/>
       <c r="CN92" s="2">
         <f t="shared" si="117"/>
@@ -26468,16 +26386,16 @@
       <c r="BG93" s="20"/>
       <c r="BH93" s="20"/>
       <c r="BI93" s="20"/>
-      <c r="CC93" s="69"/>
-      <c r="CD93" s="70"/>
-      <c r="CE93" s="70"/>
-      <c r="CF93" s="70"/>
-      <c r="CG93" s="70"/>
-      <c r="CH93" s="70"/>
-      <c r="CI93" s="70"/>
-      <c r="CJ93" s="70"/>
-      <c r="CK93" s="70"/>
-      <c r="CL93" s="71"/>
+      <c r="CC93" s="66"/>
+      <c r="CD93" s="67"/>
+      <c r="CE93" s="67"/>
+      <c r="CF93" s="67"/>
+      <c r="CG93" s="67"/>
+      <c r="CH93" s="67"/>
+      <c r="CI93" s="67"/>
+      <c r="CJ93" s="67"/>
+      <c r="CK93" s="67"/>
+      <c r="CL93" s="68"/>
       <c r="CM93" s="13"/>
       <c r="CN93" s="2">
         <f t="shared" si="117"/>
@@ -26644,16 +26562,16 @@
       <c r="BG94" s="20"/>
       <c r="BH94" s="20"/>
       <c r="BI94" s="20"/>
-      <c r="CC94" s="60"/>
-      <c r="CD94" s="61"/>
-      <c r="CE94" s="61"/>
-      <c r="CF94" s="61"/>
-      <c r="CG94" s="61"/>
-      <c r="CH94" s="61"/>
-      <c r="CI94" s="61"/>
-      <c r="CJ94" s="61"/>
-      <c r="CK94" s="61"/>
-      <c r="CL94" s="62"/>
+      <c r="CC94" s="63"/>
+      <c r="CD94" s="64"/>
+      <c r="CE94" s="64"/>
+      <c r="CF94" s="64"/>
+      <c r="CG94" s="64"/>
+      <c r="CH94" s="64"/>
+      <c r="CI94" s="64"/>
+      <c r="CJ94" s="64"/>
+      <c r="CK94" s="64"/>
+      <c r="CL94" s="65"/>
       <c r="CM94" s="13"/>
       <c r="CN94" s="2">
         <f t="shared" si="117"/>
@@ -31111,13 +31029,48 @@
       <c r="HP112" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="62">
-    <mergeCell ref="CG57:CK58"/>
-    <mergeCell ref="CG60:CK61"/>
-    <mergeCell ref="CG63:CK64"/>
-    <mergeCell ref="CG66:CK67"/>
-    <mergeCell ref="CC91:CL94"/>
-    <mergeCell ref="CG72:CK73"/>
+  <mergeCells count="63">
+    <mergeCell ref="FS40:FW41"/>
+    <mergeCell ref="FB40:FK41"/>
+    <mergeCell ref="FB43:FK44"/>
+    <mergeCell ref="FB46:FK47"/>
+    <mergeCell ref="FM46:FQ47"/>
+    <mergeCell ref="FM43:FQ44"/>
+    <mergeCell ref="FM40:FQ41"/>
+    <mergeCell ref="FV36:FW37"/>
+    <mergeCell ref="FB36:FK37"/>
+    <mergeCell ref="W18:AF19"/>
+    <mergeCell ref="AO18:AX19"/>
+    <mergeCell ref="BL18:BQ19"/>
+    <mergeCell ref="BR18:BV19"/>
+    <mergeCell ref="BX18:CG19"/>
+    <mergeCell ref="BJ31:BO32"/>
+    <mergeCell ref="BY31:CK33"/>
+    <mergeCell ref="CJ22:CK23"/>
+    <mergeCell ref="X25:AA26"/>
+    <mergeCell ref="AB25:AL26"/>
+    <mergeCell ref="AP25:BU26"/>
+    <mergeCell ref="X28:AA29"/>
+    <mergeCell ref="AB28:AL29"/>
+    <mergeCell ref="AP28:AY29"/>
+    <mergeCell ref="BY28:CD29"/>
+    <mergeCell ref="CF28:CK29"/>
+    <mergeCell ref="X22:AA23"/>
+    <mergeCell ref="AB22:AL23"/>
+    <mergeCell ref="AP22:BH23"/>
+    <mergeCell ref="BY22:CB23"/>
+    <mergeCell ref="CF22:CG23"/>
+    <mergeCell ref="AV36:BA37"/>
+    <mergeCell ref="X31:AA32"/>
+    <mergeCell ref="AB31:AL32"/>
+    <mergeCell ref="AV31:BA32"/>
+    <mergeCell ref="BC31:BH32"/>
+    <mergeCell ref="AE36:AG37"/>
+    <mergeCell ref="AH36:AK37"/>
+    <mergeCell ref="AP36:AQ37"/>
+    <mergeCell ref="AS36:AU37"/>
+    <mergeCell ref="AM36:AO37"/>
+    <mergeCell ref="W36:AC37"/>
     <mergeCell ref="W90:AD91"/>
     <mergeCell ref="AF90:AM91"/>
     <mergeCell ref="CG54:CK55"/>
@@ -31134,46 +31087,12 @@
     <mergeCell ref="CA50:CG51"/>
     <mergeCell ref="CH50:CL51"/>
     <mergeCell ref="BC36:BD37"/>
-    <mergeCell ref="AV36:BA37"/>
-    <mergeCell ref="X31:AA32"/>
-    <mergeCell ref="AB31:AL32"/>
-    <mergeCell ref="AV31:BA32"/>
-    <mergeCell ref="BC31:BH32"/>
-    <mergeCell ref="W36:AF37"/>
-    <mergeCell ref="AH36:AJ37"/>
-    <mergeCell ref="AK36:AN37"/>
-    <mergeCell ref="AP36:AQ37"/>
-    <mergeCell ref="AS36:AU37"/>
-    <mergeCell ref="BY28:CD29"/>
-    <mergeCell ref="CF28:CK29"/>
-    <mergeCell ref="X22:AA23"/>
-    <mergeCell ref="AB22:AL23"/>
-    <mergeCell ref="AP22:BH23"/>
-    <mergeCell ref="BY22:CB23"/>
-    <mergeCell ref="CF22:CG23"/>
-    <mergeCell ref="FV36:FW37"/>
-    <mergeCell ref="FB36:FK37"/>
-    <mergeCell ref="W18:AF19"/>
-    <mergeCell ref="AO18:AX19"/>
-    <mergeCell ref="BL18:BQ19"/>
-    <mergeCell ref="BR18:BV19"/>
-    <mergeCell ref="BX18:CG19"/>
-    <mergeCell ref="BJ31:BO32"/>
-    <mergeCell ref="BY31:CK33"/>
-    <mergeCell ref="CJ22:CK23"/>
-    <mergeCell ref="X25:AA26"/>
-    <mergeCell ref="AB25:AL26"/>
-    <mergeCell ref="AP25:BU26"/>
-    <mergeCell ref="X28:AA29"/>
-    <mergeCell ref="AB28:AL29"/>
-    <mergeCell ref="AP28:AY29"/>
-    <mergeCell ref="FS40:FW41"/>
-    <mergeCell ref="FB40:FK41"/>
-    <mergeCell ref="FB43:FK44"/>
-    <mergeCell ref="FB46:FK47"/>
-    <mergeCell ref="FM46:FQ47"/>
-    <mergeCell ref="FM43:FQ44"/>
-    <mergeCell ref="FM40:FQ41"/>
+    <mergeCell ref="CG57:CK58"/>
+    <mergeCell ref="CG60:CK61"/>
+    <mergeCell ref="CG63:CK64"/>
+    <mergeCell ref="CG66:CK67"/>
+    <mergeCell ref="CC91:CL94"/>
+    <mergeCell ref="CG72:CK73"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
